--- a/products.xlsx
+++ b/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="243">
   <si>
     <t>الحالة</t>
   </si>
@@ -34,73 +34,715 @@
     <t>الوحدة</t>
   </si>
   <si>
-    <t>images/sugar.png</t>
-  </si>
-  <si>
-    <t>images/rice.png</t>
-  </si>
-  <si>
-    <t>images/tomato.png</t>
-  </si>
-  <si>
-    <t>images/cucumber.png</t>
-  </si>
-  <si>
-    <t>images/cheese.png</t>
-  </si>
-  <si>
-    <t>images/chips.png</t>
-  </si>
-  <si>
-    <t>images/cat-snacks-nuts.png</t>
-  </si>
-  <si>
-    <t>images/onion.png</t>
+    <t>images/placeholder.png</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات</t>
+  </si>
+  <si>
+    <t>المشروبات</t>
   </si>
   <si>
     <t>البقالة</t>
   </si>
   <si>
-    <t>الفواكه والخضار</t>
-  </si>
-  <si>
     <t>الألبان</t>
   </si>
   <si>
-    <t>التسالي والمكسرات</t>
-  </si>
-  <si>
-    <t>سكر أبيض</t>
-  </si>
-  <si>
-    <t>أرز أبيض</t>
-  </si>
-  <si>
-    <t>طماطم بلدي</t>
-  </si>
-  <si>
-    <t>خيار</t>
-  </si>
-  <si>
-    <t>جبنة بيضاء</t>
-  </si>
-  <si>
-    <t>شيبسي</t>
-  </si>
-  <si>
-    <t>مكسرات مشكلة</t>
-  </si>
-  <si>
-    <t>بصل</t>
+    <t>المخبوزات</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي</t>
+  </si>
+  <si>
+    <t>المنظفات</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 1</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 2</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 3</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 4</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 5</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 6</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 7</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 8</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 9</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 10</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 11</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 12</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 13</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 14</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 15</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 16</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 17</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 18</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 19</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 20</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 21</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 22</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 23</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 24</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 25</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 1</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 2</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 3</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 4</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 5</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 6</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 7</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 8</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 9</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 10</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 11</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 12</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 13</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 14</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 15</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 16</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 17</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 18</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 19</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 20</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 21</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 22</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 23</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 24</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 25</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 1</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 2</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 3</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 4</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 5</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 6</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 7</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 8</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 9</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 10</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 11</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 12</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 13</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 14</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 15</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 16</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 17</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 18</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 19</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 20</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 21</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 22</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 23</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 24</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 25</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 1</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 2</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 3</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 4</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 5</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 6</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 7</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 8</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 9</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 10</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 11</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 12</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 13</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 14</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 15</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 16</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 17</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 18</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 19</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 20</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 21</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 22</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 23</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 24</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 25</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 1</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 2</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 3</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 4</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 5</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 6</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 7</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 8</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 9</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 10</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 11</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 12</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 13</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 14</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 15</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 16</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 17</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 18</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 19</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 20</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 21</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 22</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 23</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 24</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 25</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 1</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 2</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 3</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 4</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 5</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 6</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 7</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 8</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 9</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 10</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 11</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 12</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 13</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 14</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 15</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 16</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 17</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 18</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 19</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 20</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 21</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 22</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 23</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 24</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 25</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 1</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 2</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 3</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 4</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 5</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 6</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 7</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 8</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 9</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 10</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 11</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 12</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 13</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 14</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 15</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 16</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 17</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 18</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 19</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 20</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 21</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 22</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 23</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 24</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 25</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 1</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 2</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 3</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 4</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 5</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 6</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 7</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 8</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 9</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 10</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 11</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 12</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 13</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 14</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 15</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 16</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 17</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 18</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 19</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 20</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 21</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 22</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 23</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 24</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 25</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 1</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 2</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 3</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 4</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 5</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 6</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 7</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 8</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 9</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 10</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 11</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 12</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 13</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 14</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 15</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 16</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 17</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 18</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 19</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 20</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 21</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 22</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 23</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 24</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 25</t>
   </si>
   <si>
     <t>كيلو</t>
   </si>
   <si>
-    <t>عبوة</t>
-  </si>
-  <si>
-    <t>كيس</t>
+    <t>قطعة</t>
   </si>
 </sst>
 </file>
@@ -458,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -489,16 +1131,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -506,19 +1148,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
       <c r="D3">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -526,19 +1168,19 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D4">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -546,19 +1188,19 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -566,19 +1208,19 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -586,19 +1228,19 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -606,39 +1248,4379 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8">
         <v>17</v>
       </c>
-      <c r="D8">
-        <v>45</v>
-      </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26">
+        <v>35</v>
+      </c>
+      <c r="E26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31">
         <v>15</v>
       </c>
-      <c r="D9">
+      <c r="E31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <v>19</v>
+      </c>
+      <c r="E35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>21</v>
+      </c>
+      <c r="E37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38">
+        <v>22</v>
+      </c>
+      <c r="E38" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39">
+        <v>23</v>
+      </c>
+      <c r="E39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40">
+        <v>24</v>
+      </c>
+      <c r="E40" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>55</v>
+      </c>
+      <c r="F41" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42">
+        <v>26</v>
+      </c>
+      <c r="E42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F42" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>27</v>
+      </c>
+      <c r="E43" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>1</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44">
+        <v>28</v>
+      </c>
+      <c r="E44" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>1</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45">
+        <v>29</v>
+      </c>
+      <c r="E45" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>1</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46">
+        <v>30</v>
+      </c>
+      <c r="E46" t="s">
+        <v>60</v>
+      </c>
+      <c r="F46" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47">
+        <v>31</v>
+      </c>
+      <c r="E47" t="s">
+        <v>61</v>
+      </c>
+      <c r="F47" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>1</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48">
+        <v>32</v>
+      </c>
+      <c r="E48" t="s">
+        <v>62</v>
+      </c>
+      <c r="F48" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>1</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <v>33</v>
+      </c>
+      <c r="E49" t="s">
+        <v>63</v>
+      </c>
+      <c r="F49" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>1</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <v>34</v>
+      </c>
+      <c r="E50" t="s">
+        <v>64</v>
+      </c>
+      <c r="F50" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51">
+        <v>35</v>
+      </c>
+      <c r="E51" t="s">
+        <v>65</v>
+      </c>
+      <c r="F51" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>66</v>
+      </c>
+      <c r="F52" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>1</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>67</v>
+      </c>
+      <c r="F53" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>68</v>
+      </c>
+      <c r="F54" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>1</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s">
+        <v>69</v>
+      </c>
+      <c r="F55" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>1</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56">
         <v>15</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E56" t="s">
+        <v>70</v>
+      </c>
+      <c r="F56" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>1</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58">
+        <v>17</v>
+      </c>
+      <c r="E58" t="s">
+        <v>72</v>
+      </c>
+      <c r="F58" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>73</v>
+      </c>
+      <c r="F59" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>1</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60">
+        <v>19</v>
+      </c>
+      <c r="E60" t="s">
+        <v>74</v>
+      </c>
+      <c r="F60" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>1</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>75</v>
+      </c>
+      <c r="F61" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>1</v>
+      </c>
+      <c r="B62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62">
+        <v>21</v>
+      </c>
+      <c r="E62" t="s">
+        <v>76</v>
+      </c>
+      <c r="F62" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>1</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63">
+        <v>22</v>
+      </c>
+      <c r="E63" t="s">
+        <v>77</v>
+      </c>
+      <c r="F63" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>1</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64">
+        <v>23</v>
+      </c>
+      <c r="E64" t="s">
+        <v>78</v>
+      </c>
+      <c r="F64" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65">
+        <v>24</v>
+      </c>
+      <c r="E65" t="s">
+        <v>79</v>
+      </c>
+      <c r="F65" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>1</v>
+      </c>
+      <c r="B66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66">
         <v>25</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E66" t="s">
+        <v>80</v>
+      </c>
+      <c r="F66" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>1</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67">
         <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>81</v>
+      </c>
+      <c r="F67" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68">
+        <v>1</v>
+      </c>
+      <c r="B68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68">
+        <v>27</v>
+      </c>
+      <c r="E68" t="s">
+        <v>82</v>
+      </c>
+      <c r="F68" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69">
+        <v>1</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69">
+        <v>28</v>
+      </c>
+      <c r="E69" t="s">
+        <v>83</v>
+      </c>
+      <c r="F69" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70">
+        <v>1</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70">
+        <v>29</v>
+      </c>
+      <c r="E70" t="s">
+        <v>84</v>
+      </c>
+      <c r="F70" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71">
+        <v>1</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71">
+        <v>30</v>
+      </c>
+      <c r="E71" t="s">
+        <v>85</v>
+      </c>
+      <c r="F71" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72">
+        <v>1</v>
+      </c>
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72">
+        <v>31</v>
+      </c>
+      <c r="E72" t="s">
+        <v>86</v>
+      </c>
+      <c r="F72" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73">
+        <v>1</v>
+      </c>
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73">
+        <v>32</v>
+      </c>
+      <c r="E73" t="s">
+        <v>87</v>
+      </c>
+      <c r="F73" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>1</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74">
+        <v>33</v>
+      </c>
+      <c r="E74" t="s">
+        <v>88</v>
+      </c>
+      <c r="F74" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75">
+        <v>1</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75">
+        <v>34</v>
+      </c>
+      <c r="E75" t="s">
+        <v>89</v>
+      </c>
+      <c r="F75" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76">
+        <v>35</v>
+      </c>
+      <c r="E76" t="s">
+        <v>90</v>
+      </c>
+      <c r="F76" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77">
+        <v>1</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78">
+        <v>1</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>92</v>
+      </c>
+      <c r="F78" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>1</v>
+      </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>93</v>
+      </c>
+      <c r="F79" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80">
+        <v>1</v>
+      </c>
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80">
+        <v>14</v>
+      </c>
+      <c r="E80" t="s">
+        <v>94</v>
+      </c>
+      <c r="F80" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81">
+        <v>1</v>
+      </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81">
+        <v>15</v>
+      </c>
+      <c r="E81" t="s">
+        <v>95</v>
+      </c>
+      <c r="F81" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82">
+        <v>1</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82">
+        <v>16</v>
+      </c>
+      <c r="E82" t="s">
+        <v>96</v>
+      </c>
+      <c r="F82" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83">
+        <v>1</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83">
+        <v>17</v>
+      </c>
+      <c r="E83" t="s">
+        <v>97</v>
+      </c>
+      <c r="F83" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>1</v>
+      </c>
+      <c r="B84" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84">
+        <v>18</v>
+      </c>
+      <c r="E84" t="s">
+        <v>98</v>
+      </c>
+      <c r="F84" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85">
+        <v>1</v>
+      </c>
+      <c r="B85" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85">
+        <v>19</v>
+      </c>
+      <c r="E85" t="s">
+        <v>99</v>
+      </c>
+      <c r="F85" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86">
+        <v>1</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86">
+        <v>20</v>
+      </c>
+      <c r="E86" t="s">
+        <v>100</v>
+      </c>
+      <c r="F86" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87">
+        <v>1</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87">
+        <v>21</v>
+      </c>
+      <c r="E87" t="s">
+        <v>101</v>
+      </c>
+      <c r="F87" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>1</v>
+      </c>
+      <c r="B88" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88">
+        <v>22</v>
+      </c>
+      <c r="E88" t="s">
+        <v>102</v>
+      </c>
+      <c r="F88" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89">
+        <v>1</v>
+      </c>
+      <c r="B89" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89">
+        <v>23</v>
+      </c>
+      <c r="E89" t="s">
+        <v>103</v>
+      </c>
+      <c r="F89" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90">
+        <v>1</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90">
+        <v>24</v>
+      </c>
+      <c r="E90" t="s">
+        <v>104</v>
+      </c>
+      <c r="F90" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91">
+        <v>1</v>
+      </c>
+      <c r="B91" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91">
+        <v>25</v>
+      </c>
+      <c r="E91" t="s">
+        <v>105</v>
+      </c>
+      <c r="F91" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>1</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92">
+        <v>26</v>
+      </c>
+      <c r="E92" t="s">
+        <v>106</v>
+      </c>
+      <c r="F92" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93">
+        <v>1</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93">
+        <v>27</v>
+      </c>
+      <c r="E93" t="s">
+        <v>107</v>
+      </c>
+      <c r="F93" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94">
+        <v>1</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94">
+        <v>28</v>
+      </c>
+      <c r="E94" t="s">
+        <v>108</v>
+      </c>
+      <c r="F94" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95">
+        <v>29</v>
+      </c>
+      <c r="E95" t="s">
+        <v>109</v>
+      </c>
+      <c r="F95" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96">
+        <v>1</v>
+      </c>
+      <c r="B96" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96">
+        <v>30</v>
+      </c>
+      <c r="E96" t="s">
+        <v>110</v>
+      </c>
+      <c r="F96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97">
+        <v>1</v>
+      </c>
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97">
+        <v>31</v>
+      </c>
+      <c r="E97" t="s">
+        <v>111</v>
+      </c>
+      <c r="F97" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>1</v>
+      </c>
+      <c r="B98" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98">
+        <v>32</v>
+      </c>
+      <c r="E98" t="s">
+        <v>112</v>
+      </c>
+      <c r="F98" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99">
+        <v>1</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99">
+        <v>33</v>
+      </c>
+      <c r="E99" t="s">
+        <v>113</v>
+      </c>
+      <c r="F99" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100">
+        <v>1</v>
+      </c>
+      <c r="B100" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100">
+        <v>34</v>
+      </c>
+      <c r="E100" t="s">
+        <v>114</v>
+      </c>
+      <c r="F100" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101">
+        <v>1</v>
+      </c>
+      <c r="B101" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101">
+        <v>35</v>
+      </c>
+      <c r="E101" t="s">
+        <v>115</v>
+      </c>
+      <c r="F101" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102">
+        <v>1</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102">
+        <v>11</v>
+      </c>
+      <c r="E102" t="s">
+        <v>116</v>
+      </c>
+      <c r="F102" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103">
+        <v>1</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103">
+        <v>12</v>
+      </c>
+      <c r="E103" t="s">
+        <v>117</v>
+      </c>
+      <c r="F103" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104">
+        <v>1</v>
+      </c>
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>118</v>
+      </c>
+      <c r="F104" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105">
+        <v>1</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s">
+        <v>119</v>
+      </c>
+      <c r="F105" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106">
+        <v>1</v>
+      </c>
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106">
+        <v>15</v>
+      </c>
+      <c r="E106" t="s">
+        <v>120</v>
+      </c>
+      <c r="F106" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107">
+        <v>1</v>
+      </c>
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>121</v>
+      </c>
+      <c r="F107" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108">
+        <v>1</v>
+      </c>
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108">
+        <v>17</v>
+      </c>
+      <c r="E108" t="s">
+        <v>122</v>
+      </c>
+      <c r="F108" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109">
+        <v>1</v>
+      </c>
+      <c r="B109" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109">
+        <v>18</v>
+      </c>
+      <c r="E109" t="s">
+        <v>123</v>
+      </c>
+      <c r="F109" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110">
+        <v>1</v>
+      </c>
+      <c r="B110" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110">
+        <v>19</v>
+      </c>
+      <c r="E110" t="s">
+        <v>124</v>
+      </c>
+      <c r="F110" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111">
+        <v>1</v>
+      </c>
+      <c r="B111" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111">
+        <v>20</v>
+      </c>
+      <c r="E111" t="s">
+        <v>125</v>
+      </c>
+      <c r="F111" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112">
+        <v>1</v>
+      </c>
+      <c r="B112" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112">
+        <v>21</v>
+      </c>
+      <c r="E112" t="s">
+        <v>126</v>
+      </c>
+      <c r="F112" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113">
+        <v>1</v>
+      </c>
+      <c r="B113" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113">
+        <v>22</v>
+      </c>
+      <c r="E113" t="s">
+        <v>127</v>
+      </c>
+      <c r="F113" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114">
+        <v>1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114">
+        <v>23</v>
+      </c>
+      <c r="E114" t="s">
+        <v>128</v>
+      </c>
+      <c r="F114" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115">
+        <v>1</v>
+      </c>
+      <c r="B115" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115">
+        <v>24</v>
+      </c>
+      <c r="E115" t="s">
+        <v>129</v>
+      </c>
+      <c r="F115" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116">
+        <v>1</v>
+      </c>
+      <c r="B116" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116">
+        <v>25</v>
+      </c>
+      <c r="E116" t="s">
+        <v>130</v>
+      </c>
+      <c r="F116" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117">
+        <v>1</v>
+      </c>
+      <c r="B117" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117">
+        <v>26</v>
+      </c>
+      <c r="E117" t="s">
+        <v>131</v>
+      </c>
+      <c r="F117" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118">
+        <v>1</v>
+      </c>
+      <c r="B118" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118">
+        <v>27</v>
+      </c>
+      <c r="E118" t="s">
+        <v>132</v>
+      </c>
+      <c r="F118" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119">
+        <v>1</v>
+      </c>
+      <c r="B119" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119">
+        <v>28</v>
+      </c>
+      <c r="E119" t="s">
+        <v>133</v>
+      </c>
+      <c r="F119" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120">
+        <v>1</v>
+      </c>
+      <c r="B120" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120">
+        <v>29</v>
+      </c>
+      <c r="E120" t="s">
+        <v>134</v>
+      </c>
+      <c r="F120" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121">
+        <v>1</v>
+      </c>
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121">
+        <v>30</v>
+      </c>
+      <c r="E121" t="s">
+        <v>135</v>
+      </c>
+      <c r="F121" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122">
+        <v>1</v>
+      </c>
+      <c r="B122" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122">
+        <v>31</v>
+      </c>
+      <c r="E122" t="s">
+        <v>136</v>
+      </c>
+      <c r="F122" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123">
+        <v>1</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123">
+        <v>32</v>
+      </c>
+      <c r="E123" t="s">
+        <v>137</v>
+      </c>
+      <c r="F123" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124">
+        <v>1</v>
+      </c>
+      <c r="B124" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124">
+        <v>33</v>
+      </c>
+      <c r="E124" t="s">
+        <v>138</v>
+      </c>
+      <c r="F124" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125">
+        <v>1</v>
+      </c>
+      <c r="B125" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125">
+        <v>34</v>
+      </c>
+      <c r="E125" t="s">
+        <v>139</v>
+      </c>
+      <c r="F125" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126">
+        <v>1</v>
+      </c>
+      <c r="B126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126">
+        <v>35</v>
+      </c>
+      <c r="E126" t="s">
+        <v>140</v>
+      </c>
+      <c r="F126" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127">
+        <v>1</v>
+      </c>
+      <c r="B127" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127">
+        <v>11</v>
+      </c>
+      <c r="E127" t="s">
+        <v>141</v>
+      </c>
+      <c r="F127" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128">
+        <v>1</v>
+      </c>
+      <c r="B128" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128">
+        <v>12</v>
+      </c>
+      <c r="E128" t="s">
+        <v>142</v>
+      </c>
+      <c r="F128" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129">
+        <v>1</v>
+      </c>
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129">
+        <v>13</v>
+      </c>
+      <c r="E129" t="s">
+        <v>143</v>
+      </c>
+      <c r="F129" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130">
+        <v>1</v>
+      </c>
+      <c r="B130" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130">
+        <v>14</v>
+      </c>
+      <c r="E130" t="s">
+        <v>144</v>
+      </c>
+      <c r="F130" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131">
+        <v>1</v>
+      </c>
+      <c r="B131" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131">
+        <v>15</v>
+      </c>
+      <c r="E131" t="s">
+        <v>145</v>
+      </c>
+      <c r="F131" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132">
+        <v>1</v>
+      </c>
+      <c r="B132" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132">
+        <v>16</v>
+      </c>
+      <c r="E132" t="s">
+        <v>146</v>
+      </c>
+      <c r="F132" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133">
+        <v>1</v>
+      </c>
+      <c r="B133" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133">
+        <v>17</v>
+      </c>
+      <c r="E133" t="s">
+        <v>147</v>
+      </c>
+      <c r="F133" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134">
+        <v>1</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134">
+        <v>18</v>
+      </c>
+      <c r="E134" t="s">
+        <v>148</v>
+      </c>
+      <c r="F134" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135">
+        <v>1</v>
+      </c>
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135">
+        <v>19</v>
+      </c>
+      <c r="E135" t="s">
+        <v>149</v>
+      </c>
+      <c r="F135" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136">
+        <v>1</v>
+      </c>
+      <c r="B136" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136">
+        <v>20</v>
+      </c>
+      <c r="E136" t="s">
+        <v>150</v>
+      </c>
+      <c r="F136" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137">
+        <v>1</v>
+      </c>
+      <c r="B137" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137">
+        <v>21</v>
+      </c>
+      <c r="E137" t="s">
+        <v>151</v>
+      </c>
+      <c r="F137" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138">
+        <v>1</v>
+      </c>
+      <c r="B138" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138">
+        <v>22</v>
+      </c>
+      <c r="E138" t="s">
+        <v>152</v>
+      </c>
+      <c r="F138" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139">
+        <v>1</v>
+      </c>
+      <c r="B139" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139">
+        <v>23</v>
+      </c>
+      <c r="E139" t="s">
+        <v>153</v>
+      </c>
+      <c r="F139" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140">
+        <v>1</v>
+      </c>
+      <c r="B140" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140">
+        <v>24</v>
+      </c>
+      <c r="E140" t="s">
+        <v>154</v>
+      </c>
+      <c r="F140" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141">
+        <v>1</v>
+      </c>
+      <c r="B141" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141">
+        <v>25</v>
+      </c>
+      <c r="E141" t="s">
+        <v>155</v>
+      </c>
+      <c r="F141" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142">
+        <v>1</v>
+      </c>
+      <c r="B142" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142">
+        <v>26</v>
+      </c>
+      <c r="E142" t="s">
+        <v>156</v>
+      </c>
+      <c r="F142" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143">
+        <v>1</v>
+      </c>
+      <c r="B143" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" t="s">
+        <v>12</v>
+      </c>
+      <c r="D143">
+        <v>27</v>
+      </c>
+      <c r="E143" t="s">
+        <v>157</v>
+      </c>
+      <c r="F143" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144">
+        <v>1</v>
+      </c>
+      <c r="B144" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144">
+        <v>28</v>
+      </c>
+      <c r="E144" t="s">
+        <v>158</v>
+      </c>
+      <c r="F144" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145">
+        <v>1</v>
+      </c>
+      <c r="B145" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145">
+        <v>29</v>
+      </c>
+      <c r="E145" t="s">
+        <v>159</v>
+      </c>
+      <c r="F145" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146">
+        <v>1</v>
+      </c>
+      <c r="B146" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146">
+        <v>30</v>
+      </c>
+      <c r="E146" t="s">
+        <v>160</v>
+      </c>
+      <c r="F146" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147">
+        <v>1</v>
+      </c>
+      <c r="B147" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" t="s">
+        <v>12</v>
+      </c>
+      <c r="D147">
+        <v>31</v>
+      </c>
+      <c r="E147" t="s">
+        <v>161</v>
+      </c>
+      <c r="F147" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148">
+        <v>1</v>
+      </c>
+      <c r="B148" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148">
+        <v>32</v>
+      </c>
+      <c r="E148" t="s">
+        <v>162</v>
+      </c>
+      <c r="F148" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149">
+        <v>1</v>
+      </c>
+      <c r="B149" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149">
+        <v>33</v>
+      </c>
+      <c r="E149" t="s">
+        <v>163</v>
+      </c>
+      <c r="F149" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150">
+        <v>1</v>
+      </c>
+      <c r="B150" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150">
+        <v>34</v>
+      </c>
+      <c r="E150" t="s">
+        <v>164</v>
+      </c>
+      <c r="F150" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151">
+        <v>1</v>
+      </c>
+      <c r="B151" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151">
+        <v>35</v>
+      </c>
+      <c r="E151" t="s">
+        <v>165</v>
+      </c>
+      <c r="F151" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152">
+        <v>1</v>
+      </c>
+      <c r="B152" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152">
+        <v>11</v>
+      </c>
+      <c r="E152" t="s">
+        <v>166</v>
+      </c>
+      <c r="F152" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153">
+        <v>1</v>
+      </c>
+      <c r="B153" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" t="s">
+        <v>13</v>
+      </c>
+      <c r="D153">
+        <v>12</v>
+      </c>
+      <c r="E153" t="s">
+        <v>167</v>
+      </c>
+      <c r="F153" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154">
+        <v>1</v>
+      </c>
+      <c r="B154" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" t="s">
+        <v>13</v>
+      </c>
+      <c r="D154">
+        <v>13</v>
+      </c>
+      <c r="E154" t="s">
+        <v>168</v>
+      </c>
+      <c r="F154" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155">
+        <v>1</v>
+      </c>
+      <c r="B155" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" t="s">
+        <v>13</v>
+      </c>
+      <c r="D155">
+        <v>14</v>
+      </c>
+      <c r="E155" t="s">
+        <v>169</v>
+      </c>
+      <c r="F155" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156">
+        <v>1</v>
+      </c>
+      <c r="B156" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" t="s">
+        <v>13</v>
+      </c>
+      <c r="D156">
+        <v>15</v>
+      </c>
+      <c r="E156" t="s">
+        <v>170</v>
+      </c>
+      <c r="F156" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157">
+        <v>1</v>
+      </c>
+      <c r="B157" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" t="s">
+        <v>13</v>
+      </c>
+      <c r="D157">
+        <v>16</v>
+      </c>
+      <c r="E157" t="s">
+        <v>171</v>
+      </c>
+      <c r="F157" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158">
+        <v>1</v>
+      </c>
+      <c r="B158" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" t="s">
+        <v>13</v>
+      </c>
+      <c r="D158">
+        <v>17</v>
+      </c>
+      <c r="E158" t="s">
+        <v>172</v>
+      </c>
+      <c r="F158" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159">
+        <v>1</v>
+      </c>
+      <c r="B159" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159">
+        <v>18</v>
+      </c>
+      <c r="E159" t="s">
+        <v>173</v>
+      </c>
+      <c r="F159" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160">
+        <v>1</v>
+      </c>
+      <c r="B160" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" t="s">
+        <v>13</v>
+      </c>
+      <c r="D160">
+        <v>19</v>
+      </c>
+      <c r="E160" t="s">
+        <v>174</v>
+      </c>
+      <c r="F160" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161">
+        <v>1</v>
+      </c>
+      <c r="B161" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161">
+        <v>20</v>
+      </c>
+      <c r="E161" t="s">
+        <v>175</v>
+      </c>
+      <c r="F161" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162">
+        <v>1</v>
+      </c>
+      <c r="B162" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" t="s">
+        <v>13</v>
+      </c>
+      <c r="D162">
+        <v>21</v>
+      </c>
+      <c r="E162" t="s">
+        <v>176</v>
+      </c>
+      <c r="F162" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163">
+        <v>1</v>
+      </c>
+      <c r="B163" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163">
+        <v>22</v>
+      </c>
+      <c r="E163" t="s">
+        <v>177</v>
+      </c>
+      <c r="F163" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164">
+        <v>1</v>
+      </c>
+      <c r="B164" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164">
+        <v>23</v>
+      </c>
+      <c r="E164" t="s">
+        <v>178</v>
+      </c>
+      <c r="F164" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165">
+        <v>1</v>
+      </c>
+      <c r="B165" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" t="s">
+        <v>13</v>
+      </c>
+      <c r="D165">
+        <v>24</v>
+      </c>
+      <c r="E165" t="s">
+        <v>179</v>
+      </c>
+      <c r="F165" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166">
+        <v>1</v>
+      </c>
+      <c r="B166" t="s">
+        <v>6</v>
+      </c>
+      <c r="C166" t="s">
+        <v>13</v>
+      </c>
+      <c r="D166">
+        <v>25</v>
+      </c>
+      <c r="E166" t="s">
+        <v>180</v>
+      </c>
+      <c r="F166" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167">
+        <v>1</v>
+      </c>
+      <c r="B167" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167">
+        <v>26</v>
+      </c>
+      <c r="E167" t="s">
+        <v>181</v>
+      </c>
+      <c r="F167" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168">
+        <v>1</v>
+      </c>
+      <c r="B168" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" t="s">
+        <v>13</v>
+      </c>
+      <c r="D168">
+        <v>27</v>
+      </c>
+      <c r="E168" t="s">
+        <v>182</v>
+      </c>
+      <c r="F168" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169">
+        <v>1</v>
+      </c>
+      <c r="B169" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" t="s">
+        <v>13</v>
+      </c>
+      <c r="D169">
+        <v>28</v>
+      </c>
+      <c r="E169" t="s">
+        <v>183</v>
+      </c>
+      <c r="F169" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170">
+        <v>1</v>
+      </c>
+      <c r="B170" t="s">
+        <v>6</v>
+      </c>
+      <c r="C170" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170">
+        <v>29</v>
+      </c>
+      <c r="E170" t="s">
+        <v>184</v>
+      </c>
+      <c r="F170" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171">
+        <v>1</v>
+      </c>
+      <c r="B171" t="s">
+        <v>6</v>
+      </c>
+      <c r="C171" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171">
+        <v>30</v>
+      </c>
+      <c r="E171" t="s">
+        <v>185</v>
+      </c>
+      <c r="F171" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172">
+        <v>1</v>
+      </c>
+      <c r="B172" t="s">
+        <v>6</v>
+      </c>
+      <c r="C172" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172">
+        <v>31</v>
+      </c>
+      <c r="E172" t="s">
+        <v>186</v>
+      </c>
+      <c r="F172" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173">
+        <v>1</v>
+      </c>
+      <c r="B173" t="s">
+        <v>6</v>
+      </c>
+      <c r="C173" t="s">
+        <v>13</v>
+      </c>
+      <c r="D173">
+        <v>32</v>
+      </c>
+      <c r="E173" t="s">
+        <v>187</v>
+      </c>
+      <c r="F173" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174">
+        <v>1</v>
+      </c>
+      <c r="B174" t="s">
+        <v>6</v>
+      </c>
+      <c r="C174" t="s">
+        <v>13</v>
+      </c>
+      <c r="D174">
+        <v>33</v>
+      </c>
+      <c r="E174" t="s">
+        <v>188</v>
+      </c>
+      <c r="F174" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175">
+        <v>1</v>
+      </c>
+      <c r="B175" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175" t="s">
+        <v>13</v>
+      </c>
+      <c r="D175">
+        <v>34</v>
+      </c>
+      <c r="E175" t="s">
+        <v>189</v>
+      </c>
+      <c r="F175" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176">
+        <v>1</v>
+      </c>
+      <c r="B176" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" t="s">
+        <v>13</v>
+      </c>
+      <c r="D176">
+        <v>35</v>
+      </c>
+      <c r="E176" t="s">
+        <v>190</v>
+      </c>
+      <c r="F176" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177">
+        <v>1</v>
+      </c>
+      <c r="B177" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" t="s">
+        <v>14</v>
+      </c>
+      <c r="D177">
+        <v>11</v>
+      </c>
+      <c r="E177" t="s">
+        <v>191</v>
+      </c>
+      <c r="F177" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178">
+        <v>1</v>
+      </c>
+      <c r="B178" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178">
+        <v>12</v>
+      </c>
+      <c r="E178" t="s">
+        <v>192</v>
+      </c>
+      <c r="F178" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179">
+        <v>1</v>
+      </c>
+      <c r="B179" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179">
+        <v>13</v>
+      </c>
+      <c r="E179" t="s">
+        <v>193</v>
+      </c>
+      <c r="F179" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180">
+        <v>1</v>
+      </c>
+      <c r="B180" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180">
+        <v>14</v>
+      </c>
+      <c r="E180" t="s">
+        <v>194</v>
+      </c>
+      <c r="F180" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181">
+        <v>1</v>
+      </c>
+      <c r="B181" t="s">
+        <v>6</v>
+      </c>
+      <c r="C181" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181">
+        <v>15</v>
+      </c>
+      <c r="E181" t="s">
+        <v>195</v>
+      </c>
+      <c r="F181" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182">
+        <v>1</v>
+      </c>
+      <c r="B182" t="s">
+        <v>6</v>
+      </c>
+      <c r="C182" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182">
+        <v>16</v>
+      </c>
+      <c r="E182" t="s">
+        <v>196</v>
+      </c>
+      <c r="F182" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183">
+        <v>1</v>
+      </c>
+      <c r="B183" t="s">
+        <v>6</v>
+      </c>
+      <c r="C183" t="s">
+        <v>14</v>
+      </c>
+      <c r="D183">
+        <v>17</v>
+      </c>
+      <c r="E183" t="s">
+        <v>197</v>
+      </c>
+      <c r="F183" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184">
+        <v>1</v>
+      </c>
+      <c r="B184" t="s">
+        <v>6</v>
+      </c>
+      <c r="C184" t="s">
+        <v>14</v>
+      </c>
+      <c r="D184">
+        <v>18</v>
+      </c>
+      <c r="E184" t="s">
+        <v>198</v>
+      </c>
+      <c r="F184" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185">
+        <v>1</v>
+      </c>
+      <c r="B185" t="s">
+        <v>6</v>
+      </c>
+      <c r="C185" t="s">
+        <v>14</v>
+      </c>
+      <c r="D185">
+        <v>19</v>
+      </c>
+      <c r="E185" t="s">
+        <v>199</v>
+      </c>
+      <c r="F185" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186">
+        <v>1</v>
+      </c>
+      <c r="B186" t="s">
+        <v>6</v>
+      </c>
+      <c r="C186" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186">
+        <v>20</v>
+      </c>
+      <c r="E186" t="s">
+        <v>200</v>
+      </c>
+      <c r="F186" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187">
+        <v>1</v>
+      </c>
+      <c r="B187" t="s">
+        <v>6</v>
+      </c>
+      <c r="C187" t="s">
+        <v>14</v>
+      </c>
+      <c r="D187">
+        <v>21</v>
+      </c>
+      <c r="E187" t="s">
+        <v>201</v>
+      </c>
+      <c r="F187" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188">
+        <v>1</v>
+      </c>
+      <c r="B188" t="s">
+        <v>6</v>
+      </c>
+      <c r="C188" t="s">
+        <v>14</v>
+      </c>
+      <c r="D188">
+        <v>22</v>
+      </c>
+      <c r="E188" t="s">
+        <v>202</v>
+      </c>
+      <c r="F188" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189">
+        <v>1</v>
+      </c>
+      <c r="B189" t="s">
+        <v>6</v>
+      </c>
+      <c r="C189" t="s">
+        <v>14</v>
+      </c>
+      <c r="D189">
+        <v>23</v>
+      </c>
+      <c r="E189" t="s">
+        <v>203</v>
+      </c>
+      <c r="F189" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190">
+        <v>1</v>
+      </c>
+      <c r="B190" t="s">
+        <v>6</v>
+      </c>
+      <c r="C190" t="s">
+        <v>14</v>
+      </c>
+      <c r="D190">
+        <v>24</v>
+      </c>
+      <c r="E190" t="s">
+        <v>204</v>
+      </c>
+      <c r="F190" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191">
+        <v>1</v>
+      </c>
+      <c r="B191" t="s">
+        <v>6</v>
+      </c>
+      <c r="C191" t="s">
+        <v>14</v>
+      </c>
+      <c r="D191">
+        <v>25</v>
+      </c>
+      <c r="E191" t="s">
+        <v>205</v>
+      </c>
+      <c r="F191" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192">
+        <v>1</v>
+      </c>
+      <c r="B192" t="s">
+        <v>6</v>
+      </c>
+      <c r="C192" t="s">
+        <v>14</v>
+      </c>
+      <c r="D192">
+        <v>26</v>
+      </c>
+      <c r="E192" t="s">
+        <v>206</v>
+      </c>
+      <c r="F192" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193">
+        <v>1</v>
+      </c>
+      <c r="B193" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" t="s">
+        <v>14</v>
+      </c>
+      <c r="D193">
+        <v>27</v>
+      </c>
+      <c r="E193" t="s">
+        <v>207</v>
+      </c>
+      <c r="F193" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194">
+        <v>1</v>
+      </c>
+      <c r="B194" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" t="s">
+        <v>14</v>
+      </c>
+      <c r="D194">
+        <v>28</v>
+      </c>
+      <c r="E194" t="s">
+        <v>208</v>
+      </c>
+      <c r="F194" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195">
+        <v>1</v>
+      </c>
+      <c r="B195" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" t="s">
+        <v>14</v>
+      </c>
+      <c r="D195">
+        <v>29</v>
+      </c>
+      <c r="E195" t="s">
+        <v>209</v>
+      </c>
+      <c r="F195" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196">
+        <v>1</v>
+      </c>
+      <c r="B196" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" t="s">
+        <v>14</v>
+      </c>
+      <c r="D196">
+        <v>30</v>
+      </c>
+      <c r="E196" t="s">
+        <v>210</v>
+      </c>
+      <c r="F196" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197">
+        <v>1</v>
+      </c>
+      <c r="B197" t="s">
+        <v>6</v>
+      </c>
+      <c r="C197" t="s">
+        <v>14</v>
+      </c>
+      <c r="D197">
+        <v>31</v>
+      </c>
+      <c r="E197" t="s">
+        <v>211</v>
+      </c>
+      <c r="F197" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198">
+        <v>1</v>
+      </c>
+      <c r="B198" t="s">
+        <v>6</v>
+      </c>
+      <c r="C198" t="s">
+        <v>14</v>
+      </c>
+      <c r="D198">
+        <v>32</v>
+      </c>
+      <c r="E198" t="s">
+        <v>212</v>
+      </c>
+      <c r="F198" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199">
+        <v>1</v>
+      </c>
+      <c r="B199" t="s">
+        <v>6</v>
+      </c>
+      <c r="C199" t="s">
+        <v>14</v>
+      </c>
+      <c r="D199">
+        <v>33</v>
+      </c>
+      <c r="E199" t="s">
+        <v>213</v>
+      </c>
+      <c r="F199" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200">
+        <v>1</v>
+      </c>
+      <c r="B200" t="s">
+        <v>6</v>
+      </c>
+      <c r="C200" t="s">
+        <v>14</v>
+      </c>
+      <c r="D200">
+        <v>34</v>
+      </c>
+      <c r="E200" t="s">
+        <v>214</v>
+      </c>
+      <c r="F200" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201">
+        <v>1</v>
+      </c>
+      <c r="B201" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" t="s">
+        <v>14</v>
+      </c>
+      <c r="D201">
+        <v>35</v>
+      </c>
+      <c r="E201" t="s">
+        <v>215</v>
+      </c>
+      <c r="F201" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202">
+        <v>1</v>
+      </c>
+      <c r="B202" t="s">
+        <v>6</v>
+      </c>
+      <c r="C202" t="s">
+        <v>15</v>
+      </c>
+      <c r="D202">
+        <v>11</v>
+      </c>
+      <c r="E202" t="s">
+        <v>216</v>
+      </c>
+      <c r="F202" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203">
+        <v>1</v>
+      </c>
+      <c r="B203" t="s">
+        <v>6</v>
+      </c>
+      <c r="C203" t="s">
+        <v>15</v>
+      </c>
+      <c r="D203">
+        <v>12</v>
+      </c>
+      <c r="E203" t="s">
+        <v>217</v>
+      </c>
+      <c r="F203" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204">
+        <v>1</v>
+      </c>
+      <c r="B204" t="s">
+        <v>6</v>
+      </c>
+      <c r="C204" t="s">
+        <v>15</v>
+      </c>
+      <c r="D204">
+        <v>13</v>
+      </c>
+      <c r="E204" t="s">
+        <v>218</v>
+      </c>
+      <c r="F204" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205">
+        <v>1</v>
+      </c>
+      <c r="B205" t="s">
+        <v>6</v>
+      </c>
+      <c r="C205" t="s">
+        <v>15</v>
+      </c>
+      <c r="D205">
+        <v>14</v>
+      </c>
+      <c r="E205" t="s">
+        <v>219</v>
+      </c>
+      <c r="F205" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206">
+        <v>1</v>
+      </c>
+      <c r="B206" t="s">
+        <v>6</v>
+      </c>
+      <c r="C206" t="s">
+        <v>15</v>
+      </c>
+      <c r="D206">
+        <v>15</v>
+      </c>
+      <c r="E206" t="s">
+        <v>220</v>
+      </c>
+      <c r="F206" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207">
+        <v>1</v>
+      </c>
+      <c r="B207" t="s">
+        <v>6</v>
+      </c>
+      <c r="C207" t="s">
+        <v>15</v>
+      </c>
+      <c r="D207">
+        <v>16</v>
+      </c>
+      <c r="E207" t="s">
+        <v>221</v>
+      </c>
+      <c r="F207" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208">
+        <v>1</v>
+      </c>
+      <c r="B208" t="s">
+        <v>6</v>
+      </c>
+      <c r="C208" t="s">
+        <v>15</v>
+      </c>
+      <c r="D208">
+        <v>17</v>
+      </c>
+      <c r="E208" t="s">
+        <v>222</v>
+      </c>
+      <c r="F208" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209">
+        <v>1</v>
+      </c>
+      <c r="B209" t="s">
+        <v>6</v>
+      </c>
+      <c r="C209" t="s">
+        <v>15</v>
+      </c>
+      <c r="D209">
+        <v>18</v>
+      </c>
+      <c r="E209" t="s">
+        <v>223</v>
+      </c>
+      <c r="F209" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210">
+        <v>1</v>
+      </c>
+      <c r="B210" t="s">
+        <v>6</v>
+      </c>
+      <c r="C210" t="s">
+        <v>15</v>
+      </c>
+      <c r="D210">
+        <v>19</v>
+      </c>
+      <c r="E210" t="s">
+        <v>224</v>
+      </c>
+      <c r="F210" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211">
+        <v>1</v>
+      </c>
+      <c r="B211" t="s">
+        <v>6</v>
+      </c>
+      <c r="C211" t="s">
+        <v>15</v>
+      </c>
+      <c r="D211">
+        <v>20</v>
+      </c>
+      <c r="E211" t="s">
+        <v>225</v>
+      </c>
+      <c r="F211" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212">
+        <v>1</v>
+      </c>
+      <c r="B212" t="s">
+        <v>6</v>
+      </c>
+      <c r="C212" t="s">
+        <v>15</v>
+      </c>
+      <c r="D212">
+        <v>21</v>
+      </c>
+      <c r="E212" t="s">
+        <v>226</v>
+      </c>
+      <c r="F212" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213">
+        <v>1</v>
+      </c>
+      <c r="B213" t="s">
+        <v>6</v>
+      </c>
+      <c r="C213" t="s">
+        <v>15</v>
+      </c>
+      <c r="D213">
+        <v>22</v>
+      </c>
+      <c r="E213" t="s">
+        <v>227</v>
+      </c>
+      <c r="F213" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214">
+        <v>1</v>
+      </c>
+      <c r="B214" t="s">
+        <v>6</v>
+      </c>
+      <c r="C214" t="s">
+        <v>15</v>
+      </c>
+      <c r="D214">
+        <v>23</v>
+      </c>
+      <c r="E214" t="s">
+        <v>228</v>
+      </c>
+      <c r="F214" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215">
+        <v>1</v>
+      </c>
+      <c r="B215" t="s">
+        <v>6</v>
+      </c>
+      <c r="C215" t="s">
+        <v>15</v>
+      </c>
+      <c r="D215">
+        <v>24</v>
+      </c>
+      <c r="E215" t="s">
+        <v>229</v>
+      </c>
+      <c r="F215" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216">
+        <v>1</v>
+      </c>
+      <c r="B216" t="s">
+        <v>6</v>
+      </c>
+      <c r="C216" t="s">
+        <v>15</v>
+      </c>
+      <c r="D216">
+        <v>25</v>
+      </c>
+      <c r="E216" t="s">
+        <v>230</v>
+      </c>
+      <c r="F216" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217">
+        <v>1</v>
+      </c>
+      <c r="B217" t="s">
+        <v>6</v>
+      </c>
+      <c r="C217" t="s">
+        <v>15</v>
+      </c>
+      <c r="D217">
+        <v>26</v>
+      </c>
+      <c r="E217" t="s">
+        <v>231</v>
+      </c>
+      <c r="F217" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218">
+        <v>1</v>
+      </c>
+      <c r="B218" t="s">
+        <v>6</v>
+      </c>
+      <c r="C218" t="s">
+        <v>15</v>
+      </c>
+      <c r="D218">
+        <v>27</v>
+      </c>
+      <c r="E218" t="s">
+        <v>232</v>
+      </c>
+      <c r="F218" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219">
+        <v>1</v>
+      </c>
+      <c r="B219" t="s">
+        <v>6</v>
+      </c>
+      <c r="C219" t="s">
+        <v>15</v>
+      </c>
+      <c r="D219">
+        <v>28</v>
+      </c>
+      <c r="E219" t="s">
+        <v>233</v>
+      </c>
+      <c r="F219" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220">
+        <v>1</v>
+      </c>
+      <c r="B220" t="s">
+        <v>6</v>
+      </c>
+      <c r="C220" t="s">
+        <v>15</v>
+      </c>
+      <c r="D220">
+        <v>29</v>
+      </c>
+      <c r="E220" t="s">
+        <v>234</v>
+      </c>
+      <c r="F220" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221">
+        <v>1</v>
+      </c>
+      <c r="B221" t="s">
+        <v>6</v>
+      </c>
+      <c r="C221" t="s">
+        <v>15</v>
+      </c>
+      <c r="D221">
+        <v>30</v>
+      </c>
+      <c r="E221" t="s">
+        <v>235</v>
+      </c>
+      <c r="F221" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222">
+        <v>1</v>
+      </c>
+      <c r="B222" t="s">
+        <v>6</v>
+      </c>
+      <c r="C222" t="s">
+        <v>15</v>
+      </c>
+      <c r="D222">
+        <v>31</v>
+      </c>
+      <c r="E222" t="s">
+        <v>236</v>
+      </c>
+      <c r="F222" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223">
+        <v>1</v>
+      </c>
+      <c r="B223" t="s">
+        <v>6</v>
+      </c>
+      <c r="C223" t="s">
+        <v>15</v>
+      </c>
+      <c r="D223">
+        <v>32</v>
+      </c>
+      <c r="E223" t="s">
+        <v>237</v>
+      </c>
+      <c r="F223" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224">
+        <v>1</v>
+      </c>
+      <c r="B224" t="s">
+        <v>6</v>
+      </c>
+      <c r="C224" t="s">
+        <v>15</v>
+      </c>
+      <c r="D224">
+        <v>33</v>
+      </c>
+      <c r="E224" t="s">
+        <v>238</v>
+      </c>
+      <c r="F224" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225">
+        <v>1</v>
+      </c>
+      <c r="B225" t="s">
+        <v>6</v>
+      </c>
+      <c r="C225" t="s">
+        <v>15</v>
+      </c>
+      <c r="D225">
+        <v>34</v>
+      </c>
+      <c r="E225" t="s">
+        <v>239</v>
+      </c>
+      <c r="F225" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226">
+        <v>1</v>
+      </c>
+      <c r="B226" t="s">
+        <v>6</v>
+      </c>
+      <c r="C226" t="s">
+        <v>15</v>
+      </c>
+      <c r="D226">
+        <v>35</v>
+      </c>
+      <c r="E226" t="s">
+        <v>240</v>
+      </c>
+      <c r="F226" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -14,69 +14,1416 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
-  <si>
-    <t>الحالة</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="470">
+  <si>
+    <t>الاسم</t>
+  </si>
+  <si>
+    <t>القسم</t>
+  </si>
+  <si>
+    <t>السعر الأساسي</t>
+  </si>
+  <si>
+    <t>السعر بعد الخصم</t>
+  </si>
+  <si>
+    <t>الوحدة</t>
   </si>
   <si>
     <t>الصورة</t>
   </si>
   <si>
-    <t>القسم</t>
-  </si>
-  <si>
-    <t>الاسم</t>
-  </si>
-  <si>
-    <t>السعر الأساسي</t>
-  </si>
-  <si>
-    <t>السعر بعد الخصم</t>
-  </si>
-  <si>
-    <t>الوحدة</t>
-  </si>
-  <si>
-    <t>images/tomato.png</t>
-  </si>
-  <si>
-    <t>images/sugar.png</t>
-  </si>
-  <si>
-    <t>images/cheese.png</t>
-  </si>
-  <si>
-    <t>images/chips.png</t>
+    <t>متوفر</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 1</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 2</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 3</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 4</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 5</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 6</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 7</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 8</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 9</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 10</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 11</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 12</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 13</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 14</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 15</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 16</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 17</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 18</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 19</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 20</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 21</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 22</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 23</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 24</t>
+  </si>
+  <si>
+    <t>الفواكه والخضار - منتج 25</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 1</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 2</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 3</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 4</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 5</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 6</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 7</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 8</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 9</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 10</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 11</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 12</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 13</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 14</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 15</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 16</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 17</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 18</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 19</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 20</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 21</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 22</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 23</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 24</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات - منتج 25</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 1</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 2</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 3</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 4</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 5</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 6</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 7</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 8</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 9</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 10</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 11</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 12</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 13</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 14</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 15</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 16</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 17</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 18</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 19</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 20</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 21</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 22</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 23</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 24</t>
+  </si>
+  <si>
+    <t>المشروبات - منتج 25</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 1</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 2</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 3</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 4</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 5</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 6</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 7</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 8</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 9</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 10</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 11</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 12</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 13</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 14</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 15</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 16</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 17</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 18</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 19</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 20</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 21</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 22</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 23</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 24</t>
+  </si>
+  <si>
+    <t>البقالة - منتج 25</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 1</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 2</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 3</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 4</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 5</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 6</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 7</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 8</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 9</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 10</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 11</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 12</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 13</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 14</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 15</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 16</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 17</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 18</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 19</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 20</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 21</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 22</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 23</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 24</t>
+  </si>
+  <si>
+    <t>الألبان - منتج 25</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 1</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 2</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 3</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 4</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 5</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 6</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 7</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 8</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 9</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 10</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 11</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 12</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 13</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 14</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 15</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 16</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 17</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 18</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 19</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 20</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 21</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 22</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 23</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 24</t>
+  </si>
+  <si>
+    <t>المخبوزات - منتج 25</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 1</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 2</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 3</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 4</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 5</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 6</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 7</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 8</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 9</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 10</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 11</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 12</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 13</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 14</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 15</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 16</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 17</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 18</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 19</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 20</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 21</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 22</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 23</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 24</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات - منتج 25</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 1</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 2</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 3</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 4</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 5</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 6</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 7</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 8</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 9</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 10</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 11</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 12</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 13</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 14</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 15</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 16</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 17</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 18</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 19</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 20</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 21</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 22</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 23</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 24</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي - منتج 25</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 1</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 2</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 3</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 4</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 5</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 6</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 7</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 8</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 9</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 10</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 11</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 12</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 13</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 14</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 15</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 16</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 17</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 18</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 19</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 20</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 21</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 22</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 23</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 24</t>
+  </si>
+  <si>
+    <t>المنظفات - منتج 25</t>
   </si>
   <si>
     <t>الفواكه والخضار</t>
   </si>
   <si>
+    <t>التسالي والمكسرات</t>
+  </si>
+  <si>
+    <t>المشروبات</t>
+  </si>
+  <si>
     <t>البقالة</t>
   </si>
   <si>
     <t>الألبان</t>
   </si>
   <si>
-    <t>التسالي والمكسرات</t>
-  </si>
-  <si>
-    <t>طماطم بلدي</t>
-  </si>
-  <si>
-    <t>سكر أبيض</t>
-  </si>
-  <si>
-    <t>جبنة بيضاء</t>
-  </si>
-  <si>
-    <t>شيبسي عائلي</t>
+    <t>المخبوزات</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي</t>
+  </si>
+  <si>
+    <t>المنظفات</t>
   </si>
   <si>
     <t>كيلو</t>
   </si>
   <si>
-    <t>كيس</t>
+    <t>قطعة</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_1.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_2.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_3.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_4.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_5.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_6.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_7.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_8.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_9.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_10.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_11.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_12.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_13.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_14.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_15.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_16.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_17.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_18.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_19.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_20.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_21.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_22.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_23.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_24.png</t>
+  </si>
+  <si>
+    <t>images/الفواكه والخضار_prod_25.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_1.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_2.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_3.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_4.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_5.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_6.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_7.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_8.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_9.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_10.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_11.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_12.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_13.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_14.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_15.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_16.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_17.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_18.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_19.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_20.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_21.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_22.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_23.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_24.png</t>
+  </si>
+  <si>
+    <t>images/التسالي والمكسرات_prod_25.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_1.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_2.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_3.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_4.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_5.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_6.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_7.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_8.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_9.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_10.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_11.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_12.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_13.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_14.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_15.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_16.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_17.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_18.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_19.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_20.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_21.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_22.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_23.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_24.png</t>
+  </si>
+  <si>
+    <t>images/المشروبات_prod_25.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_1.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_2.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_3.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_4.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_5.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_6.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_7.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_8.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_9.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_10.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_11.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_12.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_13.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_14.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_15.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_16.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_17.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_18.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_19.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_20.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_21.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_22.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_23.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_24.png</t>
+  </si>
+  <si>
+    <t>images/البقالة_prod_25.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_1.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_2.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_3.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_4.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_5.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_6.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_7.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_8.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_9.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_10.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_11.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_12.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_13.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_14.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_15.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_16.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_17.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_18.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_19.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_20.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_21.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_22.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_23.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_24.png</t>
+  </si>
+  <si>
+    <t>images/الألبان_prod_25.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_1.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_2.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_3.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_4.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_5.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_6.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_7.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_8.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_9.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_10.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_11.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_12.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_13.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_14.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_15.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_16.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_17.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_18.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_19.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_20.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_21.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_22.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_23.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_24.png</t>
+  </si>
+  <si>
+    <t>images/المخبوزات_prod_25.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_1.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_2.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_3.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_4.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_5.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_6.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_7.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_8.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_9.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_10.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_11.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_12.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_13.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_14.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_15.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_16.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_17.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_18.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_19.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_20.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_21.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_22.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_23.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_24.png</t>
+  </si>
+  <si>
+    <t>images/التوابل والبهارات_prod_25.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_1.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_2.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_3.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_4.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_5.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_6.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_7.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_8.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_9.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_10.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_11.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_12.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_13.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_14.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_15.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_16.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_17.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_18.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_19.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_20.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_21.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_22.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_23.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_24.png</t>
+  </si>
+  <si>
+    <t>images/الحلويات والكاندي_prod_25.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_1.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_2.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_3.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_4.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_5.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_6.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_7.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_8.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_9.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_10.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_11.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_12.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_13.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_14.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_15.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_16.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_17.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_18.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_19.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_20.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_21.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_22.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_23.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_24.png</t>
+  </si>
+  <si>
+    <t>images/المنظفات_prod_25.png</t>
+  </si>
+  <si>
+    <t>نعم</t>
+  </si>
+  <si>
+    <t>لا</t>
   </si>
 </sst>
 </file>
@@ -434,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -461,89 +1808,4638 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G5" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6">
         <v>15</v>
       </c>
-      <c r="E2">
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F6" t="s">
+        <v>247</v>
+      </c>
+      <c r="G6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F8" t="s">
+        <v>249</v>
+      </c>
+      <c r="G8" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>241</v>
+      </c>
+      <c r="F9" t="s">
+        <v>250</v>
+      </c>
+      <c r="G9" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" t="s">
+        <v>251</v>
+      </c>
+      <c r="G10" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="D11">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>241</v>
+      </c>
+      <c r="F11" t="s">
+        <v>252</v>
+      </c>
+      <c r="G11" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>241</v>
+      </c>
+      <c r="F12" t="s">
+        <v>253</v>
+      </c>
+      <c r="G12" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F13" t="s">
+        <v>254</v>
+      </c>
+      <c r="G13" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" t="s">
+        <v>255</v>
+      </c>
+      <c r="G14" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>241</v>
+      </c>
+      <c r="F15" t="s">
+        <v>256</v>
+      </c>
+      <c r="G15" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>232</v>
+      </c>
+      <c r="C16">
+        <v>25</v>
+      </c>
+      <c r="D16">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" t="s">
+        <v>257</v>
+      </c>
+      <c r="G16" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>241</v>
+      </c>
+      <c r="F17" t="s">
+        <v>258</v>
+      </c>
+      <c r="G17" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>232</v>
+      </c>
+      <c r="C18">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F18" t="s">
+        <v>259</v>
+      </c>
+      <c r="G18" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C19">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>241</v>
+      </c>
+      <c r="F19" t="s">
+        <v>260</v>
+      </c>
+      <c r="G19" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>232</v>
+      </c>
+      <c r="C20">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>241</v>
+      </c>
+      <c r="F20" t="s">
+        <v>261</v>
+      </c>
+      <c r="G20" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21">
+        <v>30</v>
+      </c>
+      <c r="D21">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>241</v>
+      </c>
+      <c r="F21" t="s">
+        <v>262</v>
+      </c>
+      <c r="G21" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>232</v>
+      </c>
+      <c r="C22">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>241</v>
+      </c>
+      <c r="F22" t="s">
+        <v>263</v>
+      </c>
+      <c r="G22" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>241</v>
+      </c>
+      <c r="F23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G23" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
+        <v>241</v>
+      </c>
+      <c r="F24" t="s">
+        <v>265</v>
+      </c>
+      <c r="G24" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>232</v>
+      </c>
+      <c r="C25">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F25" t="s">
+        <v>266</v>
+      </c>
+      <c r="G25" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C26">
+        <v>35</v>
+      </c>
+      <c r="D26">
+        <v>33</v>
+      </c>
+      <c r="E26" t="s">
+        <v>241</v>
+      </c>
+      <c r="F26" t="s">
+        <v>267</v>
+      </c>
+      <c r="G26" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C27">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>242</v>
+      </c>
+      <c r="F27" t="s">
+        <v>268</v>
+      </c>
+      <c r="G27" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C28">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>242</v>
+      </c>
+      <c r="F28" t="s">
+        <v>269</v>
+      </c>
+      <c r="G28" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>233</v>
+      </c>
+      <c r="C29">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>242</v>
+      </c>
+      <c r="F29" t="s">
+        <v>270</v>
+      </c>
+      <c r="G29" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>233</v>
+      </c>
+      <c r="C30">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
+        <v>242</v>
+      </c>
+      <c r="F30" t="s">
+        <v>271</v>
+      </c>
+      <c r="G30" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D31">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>242</v>
+      </c>
+      <c r="F31" t="s">
+        <v>272</v>
+      </c>
+      <c r="G31" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>242</v>
+      </c>
+      <c r="F32" t="s">
+        <v>273</v>
+      </c>
+      <c r="G32" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>233</v>
+      </c>
+      <c r="C33">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>242</v>
+      </c>
+      <c r="F33" t="s">
+        <v>274</v>
+      </c>
+      <c r="G33" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>242</v>
+      </c>
+      <c r="F34" t="s">
+        <v>275</v>
+      </c>
+      <c r="G34" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C35">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E35" t="s">
+        <v>242</v>
+      </c>
+      <c r="F35" t="s">
+        <v>276</v>
+      </c>
+      <c r="G35" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>233</v>
+      </c>
+      <c r="C36">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
+        <v>242</v>
+      </c>
+      <c r="F36" t="s">
+        <v>277</v>
+      </c>
+      <c r="G36" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>233</v>
+      </c>
+      <c r="C37">
+        <v>21</v>
+      </c>
+      <c r="E37" t="s">
+        <v>242</v>
+      </c>
+      <c r="F37" t="s">
+        <v>278</v>
+      </c>
+      <c r="G37" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C38">
+        <v>22</v>
+      </c>
+      <c r="E38" t="s">
+        <v>242</v>
+      </c>
+      <c r="F38" t="s">
+        <v>279</v>
+      </c>
+      <c r="G38" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
+        <v>233</v>
+      </c>
+      <c r="C39">
+        <v>23</v>
+      </c>
+      <c r="E39" t="s">
+        <v>242</v>
+      </c>
+      <c r="F39" t="s">
+        <v>280</v>
+      </c>
+      <c r="G39" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C40">
+        <v>24</v>
+      </c>
+      <c r="E40" t="s">
+        <v>242</v>
+      </c>
+      <c r="F40" t="s">
+        <v>281</v>
+      </c>
+      <c r="G40" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" t="s">
+        <v>233</v>
+      </c>
+      <c r="C41">
+        <v>25</v>
+      </c>
+      <c r="D41">
+        <v>23</v>
+      </c>
+      <c r="E41" t="s">
+        <v>242</v>
+      </c>
+      <c r="F41" t="s">
+        <v>282</v>
+      </c>
+      <c r="G41" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" t="s">
+        <v>233</v>
+      </c>
+      <c r="C42">
+        <v>26</v>
+      </c>
+      <c r="E42" t="s">
+        <v>242</v>
+      </c>
+      <c r="F42" t="s">
+        <v>283</v>
+      </c>
+      <c r="G42" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" t="s">
+        <v>233</v>
+      </c>
+      <c r="C43">
+        <v>27</v>
+      </c>
+      <c r="E43" t="s">
+        <v>242</v>
+      </c>
+      <c r="F43" t="s">
+        <v>284</v>
+      </c>
+      <c r="G43" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" t="s">
+        <v>233</v>
+      </c>
+      <c r="C44">
+        <v>28</v>
+      </c>
+      <c r="E44" t="s">
+        <v>242</v>
+      </c>
+      <c r="F44" t="s">
+        <v>285</v>
+      </c>
+      <c r="G44" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" t="s">
+        <v>233</v>
+      </c>
+      <c r="C45">
+        <v>29</v>
+      </c>
+      <c r="E45" t="s">
+        <v>242</v>
+      </c>
+      <c r="F45" t="s">
+        <v>286</v>
+      </c>
+      <c r="G45" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46">
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>28</v>
+      </c>
+      <c r="E46" t="s">
+        <v>242</v>
+      </c>
+      <c r="F46" t="s">
+        <v>287</v>
+      </c>
+      <c r="G46" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C47">
+        <v>31</v>
+      </c>
+      <c r="E47" t="s">
+        <v>242</v>
+      </c>
+      <c r="F47" t="s">
+        <v>288</v>
+      </c>
+      <c r="G47" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48">
+        <v>32</v>
+      </c>
+      <c r="E48" t="s">
+        <v>242</v>
+      </c>
+      <c r="F48" t="s">
+        <v>289</v>
+      </c>
+      <c r="G48" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49">
+        <v>33</v>
+      </c>
+      <c r="E49" t="s">
+        <v>242</v>
+      </c>
+      <c r="F49" t="s">
+        <v>290</v>
+      </c>
+      <c r="G49" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" t="s">
+        <v>233</v>
+      </c>
+      <c r="C50">
+        <v>34</v>
+      </c>
+      <c r="E50" t="s">
+        <v>242</v>
+      </c>
+      <c r="F50" t="s">
+        <v>291</v>
+      </c>
+      <c r="G50" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" t="s">
+        <v>233</v>
+      </c>
+      <c r="C51">
+        <v>35</v>
+      </c>
+      <c r="D51">
+        <v>33</v>
+      </c>
+      <c r="E51" t="s">
+        <v>242</v>
+      </c>
+      <c r="F51" t="s">
+        <v>292</v>
+      </c>
+      <c r="G51" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" t="s">
+        <v>234</v>
+      </c>
+      <c r="C52">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>242</v>
+      </c>
+      <c r="F52" t="s">
+        <v>293</v>
+      </c>
+      <c r="G52" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E53" t="s">
+        <v>242</v>
+      </c>
+      <c r="F53" t="s">
+        <v>294</v>
+      </c>
+      <c r="G53" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>242</v>
+      </c>
+      <c r="F54" t="s">
+        <v>295</v>
+      </c>
+      <c r="G54" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s">
+        <v>242</v>
+      </c>
+      <c r="F55" t="s">
+        <v>296</v>
+      </c>
+      <c r="G55" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" t="s">
+        <v>234</v>
+      </c>
+      <c r="C56">
+        <v>15</v>
+      </c>
+      <c r="D56">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>242</v>
+      </c>
+      <c r="F56" t="s">
+        <v>297</v>
+      </c>
+      <c r="G56" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" t="s">
+        <v>234</v>
+      </c>
+      <c r="C57">
         <v>16</v>
       </c>
-      <c r="E3">
+      <c r="E57" t="s">
+        <v>242</v>
+      </c>
+      <c r="F57" t="s">
+        <v>298</v>
+      </c>
+      <c r="G57" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" t="s">
+        <v>234</v>
+      </c>
+      <c r="C58">
+        <v>17</v>
+      </c>
+      <c r="E58" t="s">
+        <v>242</v>
+      </c>
+      <c r="F58" t="s">
+        <v>299</v>
+      </c>
+      <c r="G58" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" t="s">
+        <v>234</v>
+      </c>
+      <c r="C59">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>242</v>
+      </c>
+      <c r="F59" t="s">
+        <v>300</v>
+      </c>
+      <c r="G59" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" t="s">
+        <v>234</v>
+      </c>
+      <c r="C60">
+        <v>19</v>
+      </c>
+      <c r="E60" t="s">
+        <v>242</v>
+      </c>
+      <c r="F60" t="s">
+        <v>301</v>
+      </c>
+      <c r="G60" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61">
+        <v>20</v>
+      </c>
+      <c r="D61">
+        <v>18</v>
+      </c>
+      <c r="E61" t="s">
+        <v>242</v>
+      </c>
+      <c r="F61" t="s">
+        <v>302</v>
+      </c>
+      <c r="G61" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" t="s">
+        <v>234</v>
+      </c>
+      <c r="C62">
+        <v>21</v>
+      </c>
+      <c r="E62" t="s">
+        <v>242</v>
+      </c>
+      <c r="F62" t="s">
+        <v>303</v>
+      </c>
+      <c r="G62" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63" t="s">
+        <v>234</v>
+      </c>
+      <c r="C63">
+        <v>22</v>
+      </c>
+      <c r="E63" t="s">
+        <v>242</v>
+      </c>
+      <c r="F63" t="s">
+        <v>304</v>
+      </c>
+      <c r="G63" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" t="s">
+        <v>234</v>
+      </c>
+      <c r="C64">
+        <v>23</v>
+      </c>
+      <c r="E64" t="s">
+        <v>242</v>
+      </c>
+      <c r="F64" t="s">
+        <v>305</v>
+      </c>
+      <c r="G64" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65">
+        <v>24</v>
+      </c>
+      <c r="E65" t="s">
+        <v>242</v>
+      </c>
+      <c r="F65" t="s">
+        <v>306</v>
+      </c>
+      <c r="G65" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" t="s">
+        <v>234</v>
+      </c>
+      <c r="C66">
+        <v>25</v>
+      </c>
+      <c r="D66">
+        <v>23</v>
+      </c>
+      <c r="E66" t="s">
+        <v>242</v>
+      </c>
+      <c r="F66" t="s">
+        <v>307</v>
+      </c>
+      <c r="G66" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" t="s">
+        <v>234</v>
+      </c>
+      <c r="C67">
+        <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>242</v>
+      </c>
+      <c r="F67" t="s">
+        <v>308</v>
+      </c>
+      <c r="G67" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" t="s">
+        <v>234</v>
+      </c>
+      <c r="C68">
+        <v>27</v>
+      </c>
+      <c r="E68" t="s">
+        <v>242</v>
+      </c>
+      <c r="F68" t="s">
+        <v>309</v>
+      </c>
+      <c r="G68" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" t="s">
+        <v>234</v>
+      </c>
+      <c r="C69">
+        <v>28</v>
+      </c>
+      <c r="E69" t="s">
+        <v>242</v>
+      </c>
+      <c r="F69" t="s">
+        <v>310</v>
+      </c>
+      <c r="G69" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" t="s">
+        <v>234</v>
+      </c>
+      <c r="C70">
+        <v>29</v>
+      </c>
+      <c r="E70" t="s">
+        <v>242</v>
+      </c>
+      <c r="F70" t="s">
+        <v>311</v>
+      </c>
+      <c r="G70" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>76</v>
+      </c>
+      <c r="B71" t="s">
+        <v>234</v>
+      </c>
+      <c r="C71">
         <v>30</v>
       </c>
-      <c r="G3" t="s">
+      <c r="D71">
+        <v>28</v>
+      </c>
+      <c r="E71" t="s">
+        <v>242</v>
+      </c>
+      <c r="F71" t="s">
+        <v>312</v>
+      </c>
+      <c r="G71" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" t="s">
+        <v>234</v>
+      </c>
+      <c r="C72">
+        <v>31</v>
+      </c>
+      <c r="E72" t="s">
+        <v>242</v>
+      </c>
+      <c r="F72" t="s">
+        <v>313</v>
+      </c>
+      <c r="G72" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" t="s">
+        <v>234</v>
+      </c>
+      <c r="C73">
+        <v>32</v>
+      </c>
+      <c r="E73" t="s">
+        <v>242</v>
+      </c>
+      <c r="F73" t="s">
+        <v>314</v>
+      </c>
+      <c r="G73" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" t="s">
+        <v>234</v>
+      </c>
+      <c r="C74">
+        <v>33</v>
+      </c>
+      <c r="E74" t="s">
+        <v>242</v>
+      </c>
+      <c r="F74" t="s">
+        <v>315</v>
+      </c>
+      <c r="G74" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" t="s">
+        <v>234</v>
+      </c>
+      <c r="C75">
+        <v>34</v>
+      </c>
+      <c r="E75" t="s">
+        <v>242</v>
+      </c>
+      <c r="F75" t="s">
+        <v>316</v>
+      </c>
+      <c r="G75" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" t="s">
+        <v>234</v>
+      </c>
+      <c r="C76">
+        <v>35</v>
+      </c>
+      <c r="D76">
+        <v>33</v>
+      </c>
+      <c r="E76" t="s">
+        <v>242</v>
+      </c>
+      <c r="F76" t="s">
+        <v>317</v>
+      </c>
+      <c r="G76" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" t="s">
+        <v>235</v>
+      </c>
+      <c r="C77">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>241</v>
+      </c>
+      <c r="F77" t="s">
+        <v>318</v>
+      </c>
+      <c r="G77" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" t="s">
+        <v>235</v>
+      </c>
+      <c r="C78">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>241</v>
+      </c>
+      <c r="F78" t="s">
+        <v>319</v>
+      </c>
+      <c r="G78" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" t="s">
+        <v>235</v>
+      </c>
+      <c r="C79">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>241</v>
+      </c>
+      <c r="F79" t="s">
+        <v>320</v>
+      </c>
+      <c r="G79" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" t="s">
+        <v>235</v>
+      </c>
+      <c r="C80">
+        <v>14</v>
+      </c>
+      <c r="E80" t="s">
+        <v>241</v>
+      </c>
+      <c r="F80" t="s">
+        <v>321</v>
+      </c>
+      <c r="G80" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" t="s">
+        <v>235</v>
+      </c>
+      <c r="C81">
+        <v>15</v>
+      </c>
+      <c r="D81">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s">
+        <v>241</v>
+      </c>
+      <c r="F81" t="s">
+        <v>322</v>
+      </c>
+      <c r="G81" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" t="s">
+        <v>235</v>
+      </c>
+      <c r="C82">
+        <v>16</v>
+      </c>
+      <c r="E82" t="s">
+        <v>241</v>
+      </c>
+      <c r="F82" t="s">
+        <v>323</v>
+      </c>
+      <c r="G82" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" t="s">
+        <v>235</v>
+      </c>
+      <c r="C83">
+        <v>17</v>
+      </c>
+      <c r="E83" t="s">
+        <v>241</v>
+      </c>
+      <c r="F83" t="s">
+        <v>324</v>
+      </c>
+      <c r="G83" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" t="s">
+        <v>235</v>
+      </c>
+      <c r="C84">
+        <v>18</v>
+      </c>
+      <c r="E84" t="s">
+        <v>241</v>
+      </c>
+      <c r="F84" t="s">
+        <v>325</v>
+      </c>
+      <c r="G84" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" t="s">
+        <v>235</v>
+      </c>
+      <c r="C85">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="E85" t="s">
+        <v>241</v>
+      </c>
+      <c r="F85" t="s">
+        <v>326</v>
+      </c>
+      <c r="G85" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" t="s">
+        <v>235</v>
+      </c>
+      <c r="C86">
+        <v>20</v>
+      </c>
+      <c r="D86">
+        <v>18</v>
+      </c>
+      <c r="E86" t="s">
+        <v>241</v>
+      </c>
+      <c r="F86" t="s">
+        <v>327</v>
+      </c>
+      <c r="G86" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>92</v>
+      </c>
+      <c r="B87" t="s">
+        <v>235</v>
+      </c>
+      <c r="C87">
+        <v>21</v>
+      </c>
+      <c r="E87" t="s">
+        <v>241</v>
+      </c>
+      <c r="F87" t="s">
+        <v>328</v>
+      </c>
+      <c r="G87" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" t="s">
+        <v>235</v>
+      </c>
+      <c r="C88">
+        <v>22</v>
+      </c>
+      <c r="E88" t="s">
+        <v>241</v>
+      </c>
+      <c r="F88" t="s">
+        <v>329</v>
+      </c>
+      <c r="G88" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>94</v>
+      </c>
+      <c r="B89" t="s">
+        <v>235</v>
+      </c>
+      <c r="C89">
+        <v>23</v>
+      </c>
+      <c r="E89" t="s">
+        <v>241</v>
+      </c>
+      <c r="F89" t="s">
+        <v>330</v>
+      </c>
+      <c r="G89" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90">
+        <v>24</v>
+      </c>
+      <c r="E90" t="s">
+        <v>241</v>
+      </c>
+      <c r="F90" t="s">
+        <v>331</v>
+      </c>
+      <c r="G90" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" t="s">
+        <v>235</v>
+      </c>
+      <c r="C91">
+        <v>25</v>
+      </c>
+      <c r="D91">
+        <v>23</v>
+      </c>
+      <c r="E91" t="s">
+        <v>241</v>
+      </c>
+      <c r="F91" t="s">
+        <v>332</v>
+      </c>
+      <c r="G91" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" t="s">
+        <v>235</v>
+      </c>
+      <c r="C92">
+        <v>26</v>
+      </c>
+      <c r="E92" t="s">
+        <v>241</v>
+      </c>
+      <c r="F92" t="s">
+        <v>333</v>
+      </c>
+      <c r="G92" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" t="s">
+        <v>235</v>
+      </c>
+      <c r="C93">
+        <v>27</v>
+      </c>
+      <c r="E93" t="s">
+        <v>241</v>
+      </c>
+      <c r="F93" t="s">
+        <v>334</v>
+      </c>
+      <c r="G93" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" t="s">
+        <v>235</v>
+      </c>
+      <c r="C94">
+        <v>28</v>
+      </c>
+      <c r="E94" t="s">
+        <v>241</v>
+      </c>
+      <c r="F94" t="s">
+        <v>335</v>
+      </c>
+      <c r="G94" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" t="s">
+        <v>235</v>
+      </c>
+      <c r="C95">
+        <v>29</v>
+      </c>
+      <c r="E95" t="s">
+        <v>241</v>
+      </c>
+      <c r="F95" t="s">
+        <v>336</v>
+      </c>
+      <c r="G95" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>101</v>
+      </c>
+      <c r="B96" t="s">
+        <v>235</v>
+      </c>
+      <c r="C96">
+        <v>30</v>
+      </c>
+      <c r="D96">
+        <v>28</v>
+      </c>
+      <c r="E96" t="s">
+        <v>241</v>
+      </c>
+      <c r="F96" t="s">
+        <v>337</v>
+      </c>
+      <c r="G96" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" t="s">
+        <v>235</v>
+      </c>
+      <c r="C97">
+        <v>31</v>
+      </c>
+      <c r="E97" t="s">
+        <v>241</v>
+      </c>
+      <c r="F97" t="s">
+        <v>338</v>
+      </c>
+      <c r="G97" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>103</v>
+      </c>
+      <c r="B98" t="s">
+        <v>235</v>
+      </c>
+      <c r="C98">
+        <v>32</v>
+      </c>
+      <c r="E98" t="s">
+        <v>241</v>
+      </c>
+      <c r="F98" t="s">
+        <v>339</v>
+      </c>
+      <c r="G98" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" t="s">
+        <v>235</v>
+      </c>
+      <c r="C99">
+        <v>33</v>
+      </c>
+      <c r="E99" t="s">
+        <v>241</v>
+      </c>
+      <c r="F99" t="s">
+        <v>340</v>
+      </c>
+      <c r="G99" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" t="s">
+        <v>235</v>
+      </c>
+      <c r="C100">
+        <v>34</v>
+      </c>
+      <c r="E100" t="s">
+        <v>241</v>
+      </c>
+      <c r="F100" t="s">
+        <v>341</v>
+      </c>
+      <c r="G100" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>106</v>
+      </c>
+      <c r="B101" t="s">
+        <v>235</v>
+      </c>
+      <c r="C101">
+        <v>35</v>
+      </c>
+      <c r="D101">
+        <v>33</v>
+      </c>
+      <c r="E101" t="s">
+        <v>241</v>
+      </c>
+      <c r="F101" t="s">
+        <v>342</v>
+      </c>
+      <c r="G101" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" t="s">
+        <v>236</v>
+      </c>
+      <c r="C102">
+        <v>11</v>
+      </c>
+      <c r="E102" t="s">
+        <v>242</v>
+      </c>
+      <c r="F102" t="s">
+        <v>343</v>
+      </c>
+      <c r="G102" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" t="s">
+        <v>236</v>
+      </c>
+      <c r="C103">
+        <v>12</v>
+      </c>
+      <c r="E103" t="s">
+        <v>242</v>
+      </c>
+      <c r="F103" t="s">
+        <v>344</v>
+      </c>
+      <c r="G103" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" t="s">
+        <v>236</v>
+      </c>
+      <c r="C104">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E104" t="s">
+        <v>242</v>
+      </c>
+      <c r="F104" t="s">
+        <v>345</v>
+      </c>
+      <c r="G104" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" t="s">
+        <v>236</v>
+      </c>
+      <c r="C105">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s">
+        <v>242</v>
+      </c>
+      <c r="F105" t="s">
+        <v>346</v>
+      </c>
+      <c r="G105" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" t="s">
+        <v>236</v>
+      </c>
+      <c r="C106">
+        <v>15</v>
+      </c>
+      <c r="D106">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>242</v>
+      </c>
+      <c r="F106" t="s">
+        <v>347</v>
+      </c>
+      <c r="G106" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" t="s">
+        <v>236</v>
+      </c>
+      <c r="C107">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>242</v>
+      </c>
+      <c r="F107" t="s">
+        <v>348</v>
+      </c>
+      <c r="G107" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" t="s">
+        <v>236</v>
+      </c>
+      <c r="C108">
         <v>17</v>
       </c>
-      <c r="E4">
+      <c r="E108" t="s">
+        <v>242</v>
+      </c>
+      <c r="F108" t="s">
+        <v>349</v>
+      </c>
+      <c r="G108" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" t="s">
+        <v>236</v>
+      </c>
+      <c r="C109">
+        <v>18</v>
+      </c>
+      <c r="E109" t="s">
+        <v>242</v>
+      </c>
+      <c r="F109" t="s">
+        <v>350</v>
+      </c>
+      <c r="G109" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" t="s">
+        <v>236</v>
+      </c>
+      <c r="C110">
+        <v>19</v>
+      </c>
+      <c r="E110" t="s">
+        <v>242</v>
+      </c>
+      <c r="F110" t="s">
+        <v>351</v>
+      </c>
+      <c r="G110" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>116</v>
+      </c>
+      <c r="B111" t="s">
+        <v>236</v>
+      </c>
+      <c r="C111">
+        <v>20</v>
+      </c>
+      <c r="D111">
+        <v>18</v>
+      </c>
+      <c r="E111" t="s">
+        <v>242</v>
+      </c>
+      <c r="F111" t="s">
+        <v>352</v>
+      </c>
+      <c r="G111" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>117</v>
+      </c>
+      <c r="B112" t="s">
+        <v>236</v>
+      </c>
+      <c r="C112">
+        <v>21</v>
+      </c>
+      <c r="E112" t="s">
+        <v>242</v>
+      </c>
+      <c r="F112" t="s">
+        <v>353</v>
+      </c>
+      <c r="G112" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" t="s">
+        <v>236</v>
+      </c>
+      <c r="C113">
+        <v>22</v>
+      </c>
+      <c r="E113" t="s">
+        <v>242</v>
+      </c>
+      <c r="F113" t="s">
+        <v>354</v>
+      </c>
+      <c r="G113" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" t="s">
+        <v>236</v>
+      </c>
+      <c r="C114">
+        <v>23</v>
+      </c>
+      <c r="E114" t="s">
+        <v>242</v>
+      </c>
+      <c r="F114" t="s">
+        <v>355</v>
+      </c>
+      <c r="G114" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
         <v>120</v>
       </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="B115" t="s">
+        <v>236</v>
+      </c>
+      <c r="C115">
+        <v>24</v>
+      </c>
+      <c r="E115" t="s">
+        <v>242</v>
+      </c>
+      <c r="F115" t="s">
+        <v>356</v>
+      </c>
+      <c r="G115" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>121</v>
+      </c>
+      <c r="B116" t="s">
+        <v>236</v>
+      </c>
+      <c r="C116">
+        <v>25</v>
+      </c>
+      <c r="D116">
+        <v>23</v>
+      </c>
+      <c r="E116" t="s">
+        <v>242</v>
+      </c>
+      <c r="F116" t="s">
+        <v>357</v>
+      </c>
+      <c r="G116" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>122</v>
+      </c>
+      <c r="B117" t="s">
+        <v>236</v>
+      </c>
+      <c r="C117">
+        <v>26</v>
+      </c>
+      <c r="E117" t="s">
+        <v>242</v>
+      </c>
+      <c r="F117" t="s">
+        <v>358</v>
+      </c>
+      <c r="G117" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" t="s">
+        <v>236</v>
+      </c>
+      <c r="C118">
+        <v>27</v>
+      </c>
+      <c r="E118" t="s">
+        <v>242</v>
+      </c>
+      <c r="F118" t="s">
+        <v>359</v>
+      </c>
+      <c r="G118" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" t="s">
+        <v>236</v>
+      </c>
+      <c r="C119">
+        <v>28</v>
+      </c>
+      <c r="E119" t="s">
+        <v>242</v>
+      </c>
+      <c r="F119" t="s">
+        <v>360</v>
+      </c>
+      <c r="G119" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" t="s">
+        <v>236</v>
+      </c>
+      <c r="C120">
+        <v>29</v>
+      </c>
+      <c r="E120" t="s">
+        <v>242</v>
+      </c>
+      <c r="F120" t="s">
+        <v>361</v>
+      </c>
+      <c r="G120" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" t="s">
+        <v>236</v>
+      </c>
+      <c r="C121">
+        <v>30</v>
+      </c>
+      <c r="D121">
+        <v>28</v>
+      </c>
+      <c r="E121" t="s">
+        <v>242</v>
+      </c>
+      <c r="F121" t="s">
+        <v>362</v>
+      </c>
+      <c r="G121" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" t="s">
+        <v>236</v>
+      </c>
+      <c r="C122">
+        <v>31</v>
+      </c>
+      <c r="E122" t="s">
+        <v>242</v>
+      </c>
+      <c r="F122" t="s">
+        <v>363</v>
+      </c>
+      <c r="G122" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" t="s">
+        <v>236</v>
+      </c>
+      <c r="C123">
+        <v>32</v>
+      </c>
+      <c r="E123" t="s">
+        <v>242</v>
+      </c>
+      <c r="F123" t="s">
+        <v>364</v>
+      </c>
+      <c r="G123" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" t="s">
+        <v>236</v>
+      </c>
+      <c r="C124">
+        <v>33</v>
+      </c>
+      <c r="E124" t="s">
+        <v>242</v>
+      </c>
+      <c r="F124" t="s">
+        <v>365</v>
+      </c>
+      <c r="G124" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" t="s">
+        <v>236</v>
+      </c>
+      <c r="C125">
+        <v>34</v>
+      </c>
+      <c r="E125" t="s">
+        <v>242</v>
+      </c>
+      <c r="F125" t="s">
+        <v>366</v>
+      </c>
+      <c r="G125" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" t="s">
+        <v>236</v>
+      </c>
+      <c r="C126">
+        <v>35</v>
+      </c>
+      <c r="D126">
+        <v>33</v>
+      </c>
+      <c r="E126" t="s">
+        <v>242</v>
+      </c>
+      <c r="F126" t="s">
+        <v>367</v>
+      </c>
+      <c r="G126" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" t="s">
+        <v>237</v>
+      </c>
+      <c r="C127">
+        <v>11</v>
+      </c>
+      <c r="E127" t="s">
+        <v>242</v>
+      </c>
+      <c r="F127" t="s">
+        <v>368</v>
+      </c>
+      <c r="G127" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>133</v>
+      </c>
+      <c r="B128" t="s">
+        <v>237</v>
+      </c>
+      <c r="C128">
+        <v>12</v>
+      </c>
+      <c r="E128" t="s">
+        <v>242</v>
+      </c>
+      <c r="F128" t="s">
+        <v>369</v>
+      </c>
+      <c r="G128" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" t="s">
+        <v>237</v>
+      </c>
+      <c r="C129">
+        <v>13</v>
+      </c>
+      <c r="E129" t="s">
+        <v>242</v>
+      </c>
+      <c r="F129" t="s">
+        <v>370</v>
+      </c>
+      <c r="G129" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" t="s">
+        <v>237</v>
+      </c>
+      <c r="C130">
+        <v>14</v>
+      </c>
+      <c r="E130" t="s">
+        <v>242</v>
+      </c>
+      <c r="F130" t="s">
+        <v>371</v>
+      </c>
+      <c r="G130" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" t="s">
+        <v>237</v>
+      </c>
+      <c r="C131">
+        <v>15</v>
+      </c>
+      <c r="D131">
+        <v>13</v>
+      </c>
+      <c r="E131" t="s">
+        <v>242</v>
+      </c>
+      <c r="F131" t="s">
+        <v>372</v>
+      </c>
+      <c r="G131" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>137</v>
+      </c>
+      <c r="B132" t="s">
+        <v>237</v>
+      </c>
+      <c r="C132">
+        <v>16</v>
+      </c>
+      <c r="E132" t="s">
+        <v>242</v>
+      </c>
+      <c r="F132" t="s">
+        <v>373</v>
+      </c>
+      <c r="G132" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>138</v>
+      </c>
+      <c r="B133" t="s">
+        <v>237</v>
+      </c>
+      <c r="C133">
+        <v>17</v>
+      </c>
+      <c r="E133" t="s">
+        <v>242</v>
+      </c>
+      <c r="F133" t="s">
+        <v>374</v>
+      </c>
+      <c r="G133" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>139</v>
+      </c>
+      <c r="B134" t="s">
+        <v>237</v>
+      </c>
+      <c r="C134">
+        <v>18</v>
+      </c>
+      <c r="E134" t="s">
+        <v>242</v>
+      </c>
+      <c r="F134" t="s">
+        <v>375</v>
+      </c>
+      <c r="G134" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>140</v>
+      </c>
+      <c r="B135" t="s">
+        <v>237</v>
+      </c>
+      <c r="C135">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E135" t="s">
+        <v>242</v>
+      </c>
+      <c r="F135" t="s">
+        <v>376</v>
+      </c>
+      <c r="G135" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>141</v>
+      </c>
+      <c r="B136" t="s">
+        <v>237</v>
+      </c>
+      <c r="C136">
+        <v>20</v>
+      </c>
+      <c r="D136">
+        <v>18</v>
+      </c>
+      <c r="E136" t="s">
+        <v>242</v>
+      </c>
+      <c r="F136" t="s">
+        <v>377</v>
+      </c>
+      <c r="G136" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>142</v>
+      </c>
+      <c r="B137" t="s">
+        <v>237</v>
+      </c>
+      <c r="C137">
+        <v>21</v>
+      </c>
+      <c r="E137" t="s">
+        <v>242</v>
+      </c>
+      <c r="F137" t="s">
+        <v>378</v>
+      </c>
+      <c r="G137" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
+        <v>143</v>
+      </c>
+      <c r="B138" t="s">
+        <v>237</v>
+      </c>
+      <c r="C138">
+        <v>22</v>
+      </c>
+      <c r="E138" t="s">
+        <v>242</v>
+      </c>
+      <c r="F138" t="s">
+        <v>379</v>
+      </c>
+      <c r="G138" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" t="s">
+        <v>237</v>
+      </c>
+      <c r="C139">
+        <v>23</v>
+      </c>
+      <c r="E139" t="s">
+        <v>242</v>
+      </c>
+      <c r="F139" t="s">
+        <v>380</v>
+      </c>
+      <c r="G139" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>145</v>
+      </c>
+      <c r="B140" t="s">
+        <v>237</v>
+      </c>
+      <c r="C140">
+        <v>24</v>
+      </c>
+      <c r="E140" t="s">
+        <v>242</v>
+      </c>
+      <c r="F140" t="s">
+        <v>381</v>
+      </c>
+      <c r="G140" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>146</v>
+      </c>
+      <c r="B141" t="s">
+        <v>237</v>
+      </c>
+      <c r="C141">
+        <v>25</v>
+      </c>
+      <c r="D141">
+        <v>23</v>
+      </c>
+      <c r="E141" t="s">
+        <v>242</v>
+      </c>
+      <c r="F141" t="s">
+        <v>382</v>
+      </c>
+      <c r="G141" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>147</v>
+      </c>
+      <c r="B142" t="s">
+        <v>237</v>
+      </c>
+      <c r="C142">
+        <v>26</v>
+      </c>
+      <c r="E142" t="s">
+        <v>242</v>
+      </c>
+      <c r="F142" t="s">
+        <v>383</v>
+      </c>
+      <c r="G142" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>148</v>
+      </c>
+      <c r="B143" t="s">
+        <v>237</v>
+      </c>
+      <c r="C143">
+        <v>27</v>
+      </c>
+      <c r="E143" t="s">
+        <v>242</v>
+      </c>
+      <c r="F143" t="s">
+        <v>384</v>
+      </c>
+      <c r="G143" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" t="s">
+        <v>237</v>
+      </c>
+      <c r="C144">
+        <v>28</v>
+      </c>
+      <c r="E144" t="s">
+        <v>242</v>
+      </c>
+      <c r="F144" t="s">
+        <v>385</v>
+      </c>
+      <c r="G144" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>150</v>
+      </c>
+      <c r="B145" t="s">
+        <v>237</v>
+      </c>
+      <c r="C145">
+        <v>29</v>
+      </c>
+      <c r="E145" t="s">
+        <v>242</v>
+      </c>
+      <c r="F145" t="s">
+        <v>386</v>
+      </c>
+      <c r="G145" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>151</v>
+      </c>
+      <c r="B146" t="s">
+        <v>237</v>
+      </c>
+      <c r="C146">
+        <v>30</v>
+      </c>
+      <c r="D146">
+        <v>28</v>
+      </c>
+      <c r="E146" t="s">
+        <v>242</v>
+      </c>
+      <c r="F146" t="s">
+        <v>387</v>
+      </c>
+      <c r="G146" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>152</v>
+      </c>
+      <c r="B147" t="s">
+        <v>237</v>
+      </c>
+      <c r="C147">
+        <v>31</v>
+      </c>
+      <c r="E147" t="s">
+        <v>242</v>
+      </c>
+      <c r="F147" t="s">
+        <v>388</v>
+      </c>
+      <c r="G147" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>153</v>
+      </c>
+      <c r="B148" t="s">
+        <v>237</v>
+      </c>
+      <c r="C148">
+        <v>32</v>
+      </c>
+      <c r="E148" t="s">
+        <v>242</v>
+      </c>
+      <c r="F148" t="s">
+        <v>389</v>
+      </c>
+      <c r="G148" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>154</v>
+      </c>
+      <c r="B149" t="s">
+        <v>237</v>
+      </c>
+      <c r="C149">
+        <v>33</v>
+      </c>
+      <c r="E149" t="s">
+        <v>242</v>
+      </c>
+      <c r="F149" t="s">
+        <v>390</v>
+      </c>
+      <c r="G149" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>155</v>
+      </c>
+      <c r="B150" t="s">
+        <v>237</v>
+      </c>
+      <c r="C150">
+        <v>34</v>
+      </c>
+      <c r="E150" t="s">
+        <v>242</v>
+      </c>
+      <c r="F150" t="s">
+        <v>391</v>
+      </c>
+      <c r="G150" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>156</v>
+      </c>
+      <c r="B151" t="s">
+        <v>237</v>
+      </c>
+      <c r="C151">
+        <v>35</v>
+      </c>
+      <c r="D151">
+        <v>33</v>
+      </c>
+      <c r="E151" t="s">
+        <v>242</v>
+      </c>
+      <c r="F151" t="s">
+        <v>392</v>
+      </c>
+      <c r="G151" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>157</v>
+      </c>
+      <c r="B152" t="s">
+        <v>238</v>
+      </c>
+      <c r="C152">
+        <v>11</v>
+      </c>
+      <c r="E152" t="s">
+        <v>241</v>
+      </c>
+      <c r="F152" t="s">
+        <v>393</v>
+      </c>
+      <c r="G152" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>158</v>
+      </c>
+      <c r="B153" t="s">
+        <v>238</v>
+      </c>
+      <c r="C153">
+        <v>12</v>
+      </c>
+      <c r="E153" t="s">
+        <v>241</v>
+      </c>
+      <c r="F153" t="s">
+        <v>394</v>
+      </c>
+      <c r="G153" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>159</v>
+      </c>
+      <c r="B154" t="s">
+        <v>238</v>
+      </c>
+      <c r="C154">
+        <v>13</v>
+      </c>
+      <c r="E154" t="s">
+        <v>241</v>
+      </c>
+      <c r="F154" t="s">
+        <v>395</v>
+      </c>
+      <c r="G154" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>160</v>
+      </c>
+      <c r="B155" t="s">
+        <v>238</v>
+      </c>
+      <c r="C155">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E155" t="s">
+        <v>241</v>
+      </c>
+      <c r="F155" t="s">
+        <v>396</v>
+      </c>
+      <c r="G155" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B156" t="s">
+        <v>238</v>
+      </c>
+      <c r="C156">
+        <v>15</v>
+      </c>
+      <c r="D156">
+        <v>13</v>
+      </c>
+      <c r="E156" t="s">
+        <v>241</v>
+      </c>
+      <c r="F156" t="s">
+        <v>397</v>
+      </c>
+      <c r="G156" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>162</v>
+      </c>
+      <c r="B157" t="s">
+        <v>238</v>
+      </c>
+      <c r="C157">
+        <v>16</v>
+      </c>
+      <c r="E157" t="s">
+        <v>241</v>
+      </c>
+      <c r="F157" t="s">
+        <v>398</v>
+      </c>
+      <c r="G157" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>163</v>
+      </c>
+      <c r="B158" t="s">
+        <v>238</v>
+      </c>
+      <c r="C158">
+        <v>17</v>
+      </c>
+      <c r="E158" t="s">
+        <v>241</v>
+      </c>
+      <c r="F158" t="s">
+        <v>399</v>
+      </c>
+      <c r="G158" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>164</v>
+      </c>
+      <c r="B159" t="s">
+        <v>238</v>
+      </c>
+      <c r="C159">
         <v>18</v>
       </c>
-      <c r="E5">
+      <c r="E159" t="s">
+        <v>241</v>
+      </c>
+      <c r="F159" t="s">
+        <v>400</v>
+      </c>
+      <c r="G159" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>165</v>
+      </c>
+      <c r="B160" t="s">
+        <v>238</v>
+      </c>
+      <c r="C160">
+        <v>19</v>
+      </c>
+      <c r="E160" t="s">
+        <v>241</v>
+      </c>
+      <c r="F160" t="s">
+        <v>401</v>
+      </c>
+      <c r="G160" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>166</v>
+      </c>
+      <c r="B161" t="s">
+        <v>238</v>
+      </c>
+      <c r="C161">
+        <v>20</v>
+      </c>
+      <c r="D161">
+        <v>18</v>
+      </c>
+      <c r="E161" t="s">
+        <v>241</v>
+      </c>
+      <c r="F161" t="s">
+        <v>402</v>
+      </c>
+      <c r="G161" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>167</v>
+      </c>
+      <c r="B162" t="s">
+        <v>238</v>
+      </c>
+      <c r="C162">
+        <v>21</v>
+      </c>
+      <c r="E162" t="s">
+        <v>241</v>
+      </c>
+      <c r="F162" t="s">
+        <v>403</v>
+      </c>
+      <c r="G162" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>168</v>
+      </c>
+      <c r="B163" t="s">
+        <v>238</v>
+      </c>
+      <c r="C163">
+        <v>22</v>
+      </c>
+      <c r="E163" t="s">
+        <v>241</v>
+      </c>
+      <c r="F163" t="s">
+        <v>404</v>
+      </c>
+      <c r="G163" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>169</v>
+      </c>
+      <c r="B164" t="s">
+        <v>238</v>
+      </c>
+      <c r="C164">
+        <v>23</v>
+      </c>
+      <c r="E164" t="s">
+        <v>241</v>
+      </c>
+      <c r="F164" t="s">
+        <v>405</v>
+      </c>
+      <c r="G164" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>170</v>
+      </c>
+      <c r="B165" t="s">
+        <v>238</v>
+      </c>
+      <c r="C165">
+        <v>24</v>
+      </c>
+      <c r="E165" t="s">
+        <v>241</v>
+      </c>
+      <c r="F165" t="s">
+        <v>406</v>
+      </c>
+      <c r="G165" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>171</v>
+      </c>
+      <c r="B166" t="s">
+        <v>238</v>
+      </c>
+      <c r="C166">
         <v>25</v>
       </c>
-      <c r="G5" t="s">
+      <c r="D166">
+        <v>23</v>
+      </c>
+      <c r="E166" t="s">
+        <v>241</v>
+      </c>
+      <c r="F166" t="s">
+        <v>407</v>
+      </c>
+      <c r="G166" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>172</v>
+      </c>
+      <c r="B167" t="s">
+        <v>238</v>
+      </c>
+      <c r="C167">
+        <v>26</v>
+      </c>
+      <c r="E167" t="s">
+        <v>241</v>
+      </c>
+      <c r="F167" t="s">
+        <v>408</v>
+      </c>
+      <c r="G167" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>173</v>
+      </c>
+      <c r="B168" t="s">
+        <v>238</v>
+      </c>
+      <c r="C168">
+        <v>27</v>
+      </c>
+      <c r="E168" t="s">
+        <v>241</v>
+      </c>
+      <c r="F168" t="s">
+        <v>409</v>
+      </c>
+      <c r="G168" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>174</v>
+      </c>
+      <c r="B169" t="s">
+        <v>238</v>
+      </c>
+      <c r="C169">
+        <v>28</v>
+      </c>
+      <c r="E169" t="s">
+        <v>241</v>
+      </c>
+      <c r="F169" t="s">
+        <v>410</v>
+      </c>
+      <c r="G169" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>175</v>
+      </c>
+      <c r="B170" t="s">
+        <v>238</v>
+      </c>
+      <c r="C170">
+        <v>29</v>
+      </c>
+      <c r="E170" t="s">
+        <v>241</v>
+      </c>
+      <c r="F170" t="s">
+        <v>411</v>
+      </c>
+      <c r="G170" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>176</v>
+      </c>
+      <c r="B171" t="s">
+        <v>238</v>
+      </c>
+      <c r="C171">
+        <v>30</v>
+      </c>
+      <c r="D171">
+        <v>28</v>
+      </c>
+      <c r="E171" t="s">
+        <v>241</v>
+      </c>
+      <c r="F171" t="s">
+        <v>412</v>
+      </c>
+      <c r="G171" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>177</v>
+      </c>
+      <c r="B172" t="s">
+        <v>238</v>
+      </c>
+      <c r="C172">
+        <v>31</v>
+      </c>
+      <c r="E172" t="s">
+        <v>241</v>
+      </c>
+      <c r="F172" t="s">
+        <v>413</v>
+      </c>
+      <c r="G172" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>178</v>
+      </c>
+      <c r="B173" t="s">
+        <v>238</v>
+      </c>
+      <c r="C173">
+        <v>32</v>
+      </c>
+      <c r="E173" t="s">
+        <v>241</v>
+      </c>
+      <c r="F173" t="s">
+        <v>414</v>
+      </c>
+      <c r="G173" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>179</v>
+      </c>
+      <c r="B174" t="s">
+        <v>238</v>
+      </c>
+      <c r="C174">
+        <v>33</v>
+      </c>
+      <c r="E174" t="s">
+        <v>241</v>
+      </c>
+      <c r="F174" t="s">
+        <v>415</v>
+      </c>
+      <c r="G174" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>180</v>
+      </c>
+      <c r="B175" t="s">
+        <v>238</v>
+      </c>
+      <c r="C175">
+        <v>34</v>
+      </c>
+      <c r="E175" t="s">
+        <v>241</v>
+      </c>
+      <c r="F175" t="s">
+        <v>416</v>
+      </c>
+      <c r="G175" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>181</v>
+      </c>
+      <c r="B176" t="s">
+        <v>238</v>
+      </c>
+      <c r="C176">
+        <v>35</v>
+      </c>
+      <c r="D176">
+        <v>33</v>
+      </c>
+      <c r="E176" t="s">
+        <v>241</v>
+      </c>
+      <c r="F176" t="s">
+        <v>417</v>
+      </c>
+      <c r="G176" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>182</v>
+      </c>
+      <c r="B177" t="s">
+        <v>239</v>
+      </c>
+      <c r="C177">
+        <v>11</v>
+      </c>
+      <c r="E177" t="s">
+        <v>242</v>
+      </c>
+      <c r="F177" t="s">
+        <v>418</v>
+      </c>
+      <c r="G177" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>183</v>
+      </c>
+      <c r="B178" t="s">
+        <v>239</v>
+      </c>
+      <c r="C178">
+        <v>12</v>
+      </c>
+      <c r="E178" t="s">
+        <v>242</v>
+      </c>
+      <c r="F178" t="s">
+        <v>419</v>
+      </c>
+      <c r="G178" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>184</v>
+      </c>
+      <c r="B179" t="s">
+        <v>239</v>
+      </c>
+      <c r="C179">
+        <v>13</v>
+      </c>
+      <c r="E179" t="s">
+        <v>242</v>
+      </c>
+      <c r="F179" t="s">
+        <v>420</v>
+      </c>
+      <c r="G179" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>185</v>
+      </c>
+      <c r="B180" t="s">
+        <v>239</v>
+      </c>
+      <c r="C180">
+        <v>14</v>
+      </c>
+      <c r="E180" t="s">
+        <v>242</v>
+      </c>
+      <c r="F180" t="s">
+        <v>421</v>
+      </c>
+      <c r="G180" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>186</v>
+      </c>
+      <c r="B181" t="s">
+        <v>239</v>
+      </c>
+      <c r="C181">
+        <v>15</v>
+      </c>
+      <c r="D181">
+        <v>13</v>
+      </c>
+      <c r="E181" t="s">
+        <v>242</v>
+      </c>
+      <c r="F181" t="s">
+        <v>422</v>
+      </c>
+      <c r="G181" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>187</v>
+      </c>
+      <c r="B182" t="s">
+        <v>239</v>
+      </c>
+      <c r="C182">
+        <v>16</v>
+      </c>
+      <c r="E182" t="s">
+        <v>242</v>
+      </c>
+      <c r="F182" t="s">
+        <v>423</v>
+      </c>
+      <c r="G182" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>188</v>
+      </c>
+      <c r="B183" t="s">
+        <v>239</v>
+      </c>
+      <c r="C183">
+        <v>17</v>
+      </c>
+      <c r="E183" t="s">
+        <v>242</v>
+      </c>
+      <c r="F183" t="s">
+        <v>424</v>
+      </c>
+      <c r="G183" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" t="s">
+        <v>189</v>
+      </c>
+      <c r="B184" t="s">
+        <v>239</v>
+      </c>
+      <c r="C184">
+        <v>18</v>
+      </c>
+      <c r="E184" t="s">
+        <v>242</v>
+      </c>
+      <c r="F184" t="s">
+        <v>425</v>
+      </c>
+      <c r="G184" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>190</v>
+      </c>
+      <c r="B185" t="s">
+        <v>239</v>
+      </c>
+      <c r="C185">
+        <v>19</v>
+      </c>
+      <c r="E185" t="s">
+        <v>242</v>
+      </c>
+      <c r="F185" t="s">
+        <v>426</v>
+      </c>
+      <c r="G185" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" t="s">
+        <v>191</v>
+      </c>
+      <c r="B186" t="s">
+        <v>239</v>
+      </c>
+      <c r="C186">
         <v>20</v>
+      </c>
+      <c r="D186">
+        <v>18</v>
+      </c>
+      <c r="E186" t="s">
+        <v>242</v>
+      </c>
+      <c r="F186" t="s">
+        <v>427</v>
+      </c>
+      <c r="G186" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>192</v>
+      </c>
+      <c r="B187" t="s">
+        <v>239</v>
+      </c>
+      <c r="C187">
+        <v>21</v>
+      </c>
+      <c r="E187" t="s">
+        <v>242</v>
+      </c>
+      <c r="F187" t="s">
+        <v>428</v>
+      </c>
+      <c r="G187" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" t="s">
+        <v>193</v>
+      </c>
+      <c r="B188" t="s">
+        <v>239</v>
+      </c>
+      <c r="C188">
+        <v>22</v>
+      </c>
+      <c r="E188" t="s">
+        <v>242</v>
+      </c>
+      <c r="F188" t="s">
+        <v>429</v>
+      </c>
+      <c r="G188" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" t="s">
+        <v>194</v>
+      </c>
+      <c r="B189" t="s">
+        <v>239</v>
+      </c>
+      <c r="C189">
+        <v>23</v>
+      </c>
+      <c r="E189" t="s">
+        <v>242</v>
+      </c>
+      <c r="F189" t="s">
+        <v>430</v>
+      </c>
+      <c r="G189" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
+        <v>195</v>
+      </c>
+      <c r="B190" t="s">
+        <v>239</v>
+      </c>
+      <c r="C190">
+        <v>24</v>
+      </c>
+      <c r="E190" t="s">
+        <v>242</v>
+      </c>
+      <c r="F190" t="s">
+        <v>431</v>
+      </c>
+      <c r="G190" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" t="s">
+        <v>196</v>
+      </c>
+      <c r="B191" t="s">
+        <v>239</v>
+      </c>
+      <c r="C191">
+        <v>25</v>
+      </c>
+      <c r="D191">
+        <v>23</v>
+      </c>
+      <c r="E191" t="s">
+        <v>242</v>
+      </c>
+      <c r="F191" t="s">
+        <v>432</v>
+      </c>
+      <c r="G191" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B192" t="s">
+        <v>239</v>
+      </c>
+      <c r="C192">
+        <v>26</v>
+      </c>
+      <c r="E192" t="s">
+        <v>242</v>
+      </c>
+      <c r="F192" t="s">
+        <v>433</v>
+      </c>
+      <c r="G192" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
+        <v>198</v>
+      </c>
+      <c r="B193" t="s">
+        <v>239</v>
+      </c>
+      <c r="C193">
+        <v>27</v>
+      </c>
+      <c r="E193" t="s">
+        <v>242</v>
+      </c>
+      <c r="F193" t="s">
+        <v>434</v>
+      </c>
+      <c r="G193" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" t="s">
+        <v>199</v>
+      </c>
+      <c r="B194" t="s">
+        <v>239</v>
+      </c>
+      <c r="C194">
+        <v>28</v>
+      </c>
+      <c r="E194" t="s">
+        <v>242</v>
+      </c>
+      <c r="F194" t="s">
+        <v>435</v>
+      </c>
+      <c r="G194" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" t="s">
+        <v>200</v>
+      </c>
+      <c r="B195" t="s">
+        <v>239</v>
+      </c>
+      <c r="C195">
+        <v>29</v>
+      </c>
+      <c r="E195" t="s">
+        <v>242</v>
+      </c>
+      <c r="F195" t="s">
+        <v>436</v>
+      </c>
+      <c r="G195" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" t="s">
+        <v>201</v>
+      </c>
+      <c r="B196" t="s">
+        <v>239</v>
+      </c>
+      <c r="C196">
+        <v>30</v>
+      </c>
+      <c r="D196">
+        <v>28</v>
+      </c>
+      <c r="E196" t="s">
+        <v>242</v>
+      </c>
+      <c r="F196" t="s">
+        <v>437</v>
+      </c>
+      <c r="G196" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" t="s">
+        <v>202</v>
+      </c>
+      <c r="B197" t="s">
+        <v>239</v>
+      </c>
+      <c r="C197">
+        <v>31</v>
+      </c>
+      <c r="E197" t="s">
+        <v>242</v>
+      </c>
+      <c r="F197" t="s">
+        <v>438</v>
+      </c>
+      <c r="G197" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>203</v>
+      </c>
+      <c r="B198" t="s">
+        <v>239</v>
+      </c>
+      <c r="C198">
+        <v>32</v>
+      </c>
+      <c r="E198" t="s">
+        <v>242</v>
+      </c>
+      <c r="F198" t="s">
+        <v>439</v>
+      </c>
+      <c r="G198" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" t="s">
+        <v>204</v>
+      </c>
+      <c r="B199" t="s">
+        <v>239</v>
+      </c>
+      <c r="C199">
+        <v>33</v>
+      </c>
+      <c r="E199" t="s">
+        <v>242</v>
+      </c>
+      <c r="F199" t="s">
+        <v>440</v>
+      </c>
+      <c r="G199" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>205</v>
+      </c>
+      <c r="B200" t="s">
+        <v>239</v>
+      </c>
+      <c r="C200">
+        <v>34</v>
+      </c>
+      <c r="E200" t="s">
+        <v>242</v>
+      </c>
+      <c r="F200" t="s">
+        <v>441</v>
+      </c>
+      <c r="G200" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" t="s">
+        <v>206</v>
+      </c>
+      <c r="B201" t="s">
+        <v>239</v>
+      </c>
+      <c r="C201">
+        <v>35</v>
+      </c>
+      <c r="D201">
+        <v>33</v>
+      </c>
+      <c r="E201" t="s">
+        <v>242</v>
+      </c>
+      <c r="F201" t="s">
+        <v>442</v>
+      </c>
+      <c r="G201" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>207</v>
+      </c>
+      <c r="B202" t="s">
+        <v>240</v>
+      </c>
+      <c r="C202">
+        <v>11</v>
+      </c>
+      <c r="E202" t="s">
+        <v>242</v>
+      </c>
+      <c r="F202" t="s">
+        <v>443</v>
+      </c>
+      <c r="G202" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" t="s">
+        <v>208</v>
+      </c>
+      <c r="B203" t="s">
+        <v>240</v>
+      </c>
+      <c r="C203">
+        <v>12</v>
+      </c>
+      <c r="E203" t="s">
+        <v>242</v>
+      </c>
+      <c r="F203" t="s">
+        <v>444</v>
+      </c>
+      <c r="G203" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" t="s">
+        <v>209</v>
+      </c>
+      <c r="B204" t="s">
+        <v>240</v>
+      </c>
+      <c r="C204">
+        <v>13</v>
+      </c>
+      <c r="E204" t="s">
+        <v>242</v>
+      </c>
+      <c r="F204" t="s">
+        <v>445</v>
+      </c>
+      <c r="G204" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" t="s">
+        <v>210</v>
+      </c>
+      <c r="B205" t="s">
+        <v>240</v>
+      </c>
+      <c r="C205">
+        <v>14</v>
+      </c>
+      <c r="E205" t="s">
+        <v>242</v>
+      </c>
+      <c r="F205" t="s">
+        <v>446</v>
+      </c>
+      <c r="G205" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" t="s">
+        <v>211</v>
+      </c>
+      <c r="B206" t="s">
+        <v>240</v>
+      </c>
+      <c r="C206">
+        <v>15</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>242</v>
+      </c>
+      <c r="F206" t="s">
+        <v>447</v>
+      </c>
+      <c r="G206" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" t="s">
+        <v>212</v>
+      </c>
+      <c r="B207" t="s">
+        <v>240</v>
+      </c>
+      <c r="C207">
+        <v>16</v>
+      </c>
+      <c r="E207" t="s">
+        <v>242</v>
+      </c>
+      <c r="F207" t="s">
+        <v>448</v>
+      </c>
+      <c r="G207" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" t="s">
+        <v>213</v>
+      </c>
+      <c r="B208" t="s">
+        <v>240</v>
+      </c>
+      <c r="C208">
+        <v>17</v>
+      </c>
+      <c r="E208" t="s">
+        <v>242</v>
+      </c>
+      <c r="F208" t="s">
+        <v>449</v>
+      </c>
+      <c r="G208" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" t="s">
+        <v>214</v>
+      </c>
+      <c r="B209" t="s">
+        <v>240</v>
+      </c>
+      <c r="C209">
+        <v>18</v>
+      </c>
+      <c r="E209" t="s">
+        <v>242</v>
+      </c>
+      <c r="F209" t="s">
+        <v>450</v>
+      </c>
+      <c r="G209" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" t="s">
+        <v>215</v>
+      </c>
+      <c r="B210" t="s">
+        <v>240</v>
+      </c>
+      <c r="C210">
+        <v>19</v>
+      </c>
+      <c r="E210" t="s">
+        <v>242</v>
+      </c>
+      <c r="F210" t="s">
+        <v>451</v>
+      </c>
+      <c r="G210" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" t="s">
+        <v>216</v>
+      </c>
+      <c r="B211" t="s">
+        <v>240</v>
+      </c>
+      <c r="C211">
+        <v>20</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>242</v>
+      </c>
+      <c r="F211" t="s">
+        <v>452</v>
+      </c>
+      <c r="G211" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" t="s">
+        <v>217</v>
+      </c>
+      <c r="B212" t="s">
+        <v>240</v>
+      </c>
+      <c r="C212">
+        <v>21</v>
+      </c>
+      <c r="E212" t="s">
+        <v>242</v>
+      </c>
+      <c r="F212" t="s">
+        <v>453</v>
+      </c>
+      <c r="G212" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" t="s">
+        <v>218</v>
+      </c>
+      <c r="B213" t="s">
+        <v>240</v>
+      </c>
+      <c r="C213">
+        <v>22</v>
+      </c>
+      <c r="E213" t="s">
+        <v>242</v>
+      </c>
+      <c r="F213" t="s">
+        <v>454</v>
+      </c>
+      <c r="G213" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" t="s">
+        <v>219</v>
+      </c>
+      <c r="B214" t="s">
+        <v>240</v>
+      </c>
+      <c r="C214">
+        <v>23</v>
+      </c>
+      <c r="E214" t="s">
+        <v>242</v>
+      </c>
+      <c r="F214" t="s">
+        <v>455</v>
+      </c>
+      <c r="G214" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" t="s">
+        <v>220</v>
+      </c>
+      <c r="B215" t="s">
+        <v>240</v>
+      </c>
+      <c r="C215">
+        <v>24</v>
+      </c>
+      <c r="E215" t="s">
+        <v>242</v>
+      </c>
+      <c r="F215" t="s">
+        <v>456</v>
+      </c>
+      <c r="G215" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" t="s">
+        <v>221</v>
+      </c>
+      <c r="B216" t="s">
+        <v>240</v>
+      </c>
+      <c r="C216">
+        <v>25</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>242</v>
+      </c>
+      <c r="F216" t="s">
+        <v>457</v>
+      </c>
+      <c r="G216" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" t="s">
+        <v>222</v>
+      </c>
+      <c r="B217" t="s">
+        <v>240</v>
+      </c>
+      <c r="C217">
+        <v>26</v>
+      </c>
+      <c r="E217" t="s">
+        <v>242</v>
+      </c>
+      <c r="F217" t="s">
+        <v>458</v>
+      </c>
+      <c r="G217" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" t="s">
+        <v>223</v>
+      </c>
+      <c r="B218" t="s">
+        <v>240</v>
+      </c>
+      <c r="C218">
+        <v>27</v>
+      </c>
+      <c r="E218" t="s">
+        <v>242</v>
+      </c>
+      <c r="F218" t="s">
+        <v>459</v>
+      </c>
+      <c r="G218" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" t="s">
+        <v>224</v>
+      </c>
+      <c r="B219" t="s">
+        <v>240</v>
+      </c>
+      <c r="C219">
+        <v>28</v>
+      </c>
+      <c r="E219" t="s">
+        <v>242</v>
+      </c>
+      <c r="F219" t="s">
+        <v>460</v>
+      </c>
+      <c r="G219" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" t="s">
+        <v>225</v>
+      </c>
+      <c r="B220" t="s">
+        <v>240</v>
+      </c>
+      <c r="C220">
+        <v>29</v>
+      </c>
+      <c r="E220" t="s">
+        <v>242</v>
+      </c>
+      <c r="F220" t="s">
+        <v>461</v>
+      </c>
+      <c r="G220" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" t="s">
+        <v>226</v>
+      </c>
+      <c r="B221" t="s">
+        <v>240</v>
+      </c>
+      <c r="C221">
+        <v>30</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>242</v>
+      </c>
+      <c r="F221" t="s">
+        <v>462</v>
+      </c>
+      <c r="G221" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" t="s">
+        <v>227</v>
+      </c>
+      <c r="B222" t="s">
+        <v>240</v>
+      </c>
+      <c r="C222">
+        <v>31</v>
+      </c>
+      <c r="E222" t="s">
+        <v>242</v>
+      </c>
+      <c r="F222" t="s">
+        <v>463</v>
+      </c>
+      <c r="G222" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" t="s">
+        <v>228</v>
+      </c>
+      <c r="B223" t="s">
+        <v>240</v>
+      </c>
+      <c r="C223">
+        <v>32</v>
+      </c>
+      <c r="E223" t="s">
+        <v>242</v>
+      </c>
+      <c r="F223" t="s">
+        <v>464</v>
+      </c>
+      <c r="G223" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" t="s">
+        <v>229</v>
+      </c>
+      <c r="B224" t="s">
+        <v>240</v>
+      </c>
+      <c r="C224">
+        <v>33</v>
+      </c>
+      <c r="E224" t="s">
+        <v>242</v>
+      </c>
+      <c r="F224" t="s">
+        <v>465</v>
+      </c>
+      <c r="G224" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" t="s">
+        <v>230</v>
+      </c>
+      <c r="B225" t="s">
+        <v>240</v>
+      </c>
+      <c r="C225">
+        <v>34</v>
+      </c>
+      <c r="E225" t="s">
+        <v>242</v>
+      </c>
+      <c r="F225" t="s">
+        <v>466</v>
+      </c>
+      <c r="G225" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" t="s">
+        <v>231</v>
+      </c>
+      <c r="B226" t="s">
+        <v>240</v>
+      </c>
+      <c r="C226">
+        <v>35</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>242</v>
+      </c>
+      <c r="F226" t="s">
+        <v>467</v>
+      </c>
+      <c r="G226" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="245">
   <si>
     <t>الاسم</t>
   </si>
@@ -745,685 +745,10 @@
     <t>قطعة</t>
   </si>
   <si>
-    <t>images/الفواكه والخضار_prod_1.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_2.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_3.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_4.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_5.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_6.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_7.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_8.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_9.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_10.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_11.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_12.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_13.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_14.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_15.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_16.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_17.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_18.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_19.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_20.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_21.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_22.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_23.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_24.png</t>
-  </si>
-  <si>
-    <t>images/الفواكه والخضار_prod_25.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_1.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_2.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_3.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_4.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_5.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_6.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_7.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_8.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_9.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_10.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_11.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_12.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_13.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_14.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_15.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_16.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_17.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_18.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_19.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_20.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_21.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_22.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_23.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_24.png</t>
-  </si>
-  <si>
-    <t>images/التسالي والمكسرات_prod_25.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_1.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_2.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_3.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_4.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_5.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_6.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_7.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_8.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_9.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_10.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_11.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_12.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_13.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_14.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_15.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_16.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_17.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_18.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_19.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_20.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_21.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_22.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_23.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_24.png</t>
-  </si>
-  <si>
-    <t>images/المشروبات_prod_25.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_1.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_2.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_3.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_4.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_5.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_6.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_7.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_8.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_9.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_10.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_11.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_12.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_13.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_14.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_15.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_16.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_17.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_18.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_19.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_20.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_21.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_22.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_23.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_24.png</t>
-  </si>
-  <si>
-    <t>images/البقالة_prod_25.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_1.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_2.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_3.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_4.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_5.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_6.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_7.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_8.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_9.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_10.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_11.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_12.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_13.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_14.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_15.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_16.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_17.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_18.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_19.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_20.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_21.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_22.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_23.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_24.png</t>
-  </si>
-  <si>
-    <t>images/الألبان_prod_25.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_1.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_2.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_3.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_4.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_5.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_6.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_7.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_8.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_9.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_10.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_11.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_12.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_13.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_14.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_15.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_16.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_17.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_18.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_19.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_20.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_21.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_22.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_23.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_24.png</t>
-  </si>
-  <si>
-    <t>images/المخبوزات_prod_25.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_1.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_2.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_3.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_4.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_5.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_6.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_7.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_8.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_9.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_10.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_11.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_12.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_13.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_14.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_15.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_16.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_17.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_18.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_19.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_20.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_21.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_22.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_23.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_24.png</t>
-  </si>
-  <si>
-    <t>images/التوابل والبهارات_prod_25.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_1.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_2.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_3.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_4.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_5.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_6.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_7.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_8.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_9.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_10.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_11.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_12.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_13.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_14.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_15.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_16.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_17.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_18.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_19.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_20.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_21.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_22.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_23.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_24.png</t>
-  </si>
-  <si>
-    <t>images/الحلويات والكاندي_prod_25.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_1.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_2.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_3.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_4.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_5.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_6.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_7.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_8.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_9.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_10.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_11.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_12.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_13.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_14.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_15.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_16.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_17.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_18.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_19.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_20.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_21.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_22.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_23.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_24.png</t>
-  </si>
-  <si>
-    <t>images/المنظفات_prod_25.png</t>
+    <t>images/placeholder.png</t>
   </si>
   <si>
     <t>نعم</t>
-  </si>
-  <si>
-    <t>لا</t>
   </si>
 </sst>
 </file>
@@ -1824,7 +1149,7 @@
         <v>243</v>
       </c>
       <c r="G2" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1841,10 +1166,10 @@
         <v>241</v>
       </c>
       <c r="F3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G3" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1861,10 +1186,10 @@
         <v>241</v>
       </c>
       <c r="F4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G4" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1881,10 +1206,10 @@
         <v>241</v>
       </c>
       <c r="F5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G5" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1904,10 +1229,10 @@
         <v>241</v>
       </c>
       <c r="F6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G6" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1924,10 +1249,10 @@
         <v>241</v>
       </c>
       <c r="F7" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G7" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1944,10 +1269,10 @@
         <v>241</v>
       </c>
       <c r="F8" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G8" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1964,10 +1289,10 @@
         <v>241</v>
       </c>
       <c r="F9" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G9" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1984,10 +1309,10 @@
         <v>241</v>
       </c>
       <c r="F10" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G10" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2007,10 +1332,10 @@
         <v>241</v>
       </c>
       <c r="F11" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="G11" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2027,10 +1352,10 @@
         <v>241</v>
       </c>
       <c r="F12" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="G12" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2047,10 +1372,10 @@
         <v>241</v>
       </c>
       <c r="F13" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G13" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2067,10 +1392,10 @@
         <v>241</v>
       </c>
       <c r="F14" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="G14" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2087,10 +1412,10 @@
         <v>241</v>
       </c>
       <c r="F15" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G15" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2110,10 +1435,10 @@
         <v>241</v>
       </c>
       <c r="F16" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="G16" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2130,10 +1455,10 @@
         <v>241</v>
       </c>
       <c r="F17" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="G17" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2150,10 +1475,10 @@
         <v>241</v>
       </c>
       <c r="F18" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="G18" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2170,10 +1495,10 @@
         <v>241</v>
       </c>
       <c r="F19" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="G19" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2190,10 +1515,10 @@
         <v>241</v>
       </c>
       <c r="F20" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="G20" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2213,10 +1538,10 @@
         <v>241</v>
       </c>
       <c r="F21" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="G21" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2233,10 +1558,10 @@
         <v>241</v>
       </c>
       <c r="F22" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="G22" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2253,10 +1578,10 @@
         <v>241</v>
       </c>
       <c r="F23" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="G23" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2273,10 +1598,10 @@
         <v>241</v>
       </c>
       <c r="F24" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="G24" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2293,10 +1618,10 @@
         <v>241</v>
       </c>
       <c r="F25" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="G25" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2316,10 +1641,10 @@
         <v>241</v>
       </c>
       <c r="F26" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="G26" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2336,10 +1661,10 @@
         <v>242</v>
       </c>
       <c r="F27" t="s">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="G27" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2356,10 +1681,10 @@
         <v>242</v>
       </c>
       <c r="F28" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="G28" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2376,10 +1701,10 @@
         <v>242</v>
       </c>
       <c r="F29" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="G29" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2396,10 +1721,10 @@
         <v>242</v>
       </c>
       <c r="F30" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="G30" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2419,10 +1744,10 @@
         <v>242</v>
       </c>
       <c r="F31" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="G31" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2439,10 +1764,10 @@
         <v>242</v>
       </c>
       <c r="F32" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="G32" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2459,10 +1784,10 @@
         <v>242</v>
       </c>
       <c r="F33" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="G33" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2479,10 +1804,10 @@
         <v>242</v>
       </c>
       <c r="F34" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="G34" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2499,10 +1824,10 @@
         <v>242</v>
       </c>
       <c r="F35" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="G35" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2522,10 +1847,10 @@
         <v>242</v>
       </c>
       <c r="F36" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="G36" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2542,10 +1867,10 @@
         <v>242</v>
       </c>
       <c r="F37" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="G37" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2562,10 +1887,10 @@
         <v>242</v>
       </c>
       <c r="F38" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="G38" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2582,10 +1907,10 @@
         <v>242</v>
       </c>
       <c r="F39" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="G39" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2602,10 +1927,10 @@
         <v>242</v>
       </c>
       <c r="F40" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="G40" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2625,10 +1950,10 @@
         <v>242</v>
       </c>
       <c r="F41" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="G41" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2645,10 +1970,10 @@
         <v>242</v>
       </c>
       <c r="F42" t="s">
-        <v>283</v>
+        <v>243</v>
       </c>
       <c r="G42" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2665,10 +1990,10 @@
         <v>242</v>
       </c>
       <c r="F43" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="G43" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2685,10 +2010,10 @@
         <v>242</v>
       </c>
       <c r="F44" t="s">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="G44" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2705,10 +2030,10 @@
         <v>242</v>
       </c>
       <c r="F45" t="s">
-        <v>286</v>
+        <v>243</v>
       </c>
       <c r="G45" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2728,10 +2053,10 @@
         <v>242</v>
       </c>
       <c r="F46" t="s">
-        <v>287</v>
+        <v>243</v>
       </c>
       <c r="G46" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2748,10 +2073,10 @@
         <v>242</v>
       </c>
       <c r="F47" t="s">
-        <v>288</v>
+        <v>243</v>
       </c>
       <c r="G47" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2768,10 +2093,10 @@
         <v>242</v>
       </c>
       <c r="F48" t="s">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="G48" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2788,10 +2113,10 @@
         <v>242</v>
       </c>
       <c r="F49" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
       <c r="G49" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2808,10 +2133,10 @@
         <v>242</v>
       </c>
       <c r="F50" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="G50" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2831,10 +2156,10 @@
         <v>242</v>
       </c>
       <c r="F51" t="s">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="G51" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2851,10 +2176,10 @@
         <v>242</v>
       </c>
       <c r="F52" t="s">
-        <v>293</v>
+        <v>243</v>
       </c>
       <c r="G52" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2871,10 +2196,10 @@
         <v>242</v>
       </c>
       <c r="F53" t="s">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="G53" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2891,10 +2216,10 @@
         <v>242</v>
       </c>
       <c r="F54" t="s">
-        <v>295</v>
+        <v>243</v>
       </c>
       <c r="G54" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2911,10 +2236,10 @@
         <v>242</v>
       </c>
       <c r="F55" t="s">
-        <v>296</v>
+        <v>243</v>
       </c>
       <c r="G55" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2934,10 +2259,10 @@
         <v>242</v>
       </c>
       <c r="F56" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="G56" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2954,10 +2279,10 @@
         <v>242</v>
       </c>
       <c r="F57" t="s">
-        <v>298</v>
+        <v>243</v>
       </c>
       <c r="G57" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2974,10 +2299,10 @@
         <v>242</v>
       </c>
       <c r="F58" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="G58" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2994,10 +2319,10 @@
         <v>242</v>
       </c>
       <c r="F59" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="G59" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3014,10 +2339,10 @@
         <v>242</v>
       </c>
       <c r="F60" t="s">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="G60" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3037,10 +2362,10 @@
         <v>242</v>
       </c>
       <c r="F61" t="s">
-        <v>302</v>
+        <v>243</v>
       </c>
       <c r="G61" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3057,10 +2382,10 @@
         <v>242</v>
       </c>
       <c r="F62" t="s">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="G62" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3077,10 +2402,10 @@
         <v>242</v>
       </c>
       <c r="F63" t="s">
-        <v>304</v>
+        <v>243</v>
       </c>
       <c r="G63" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3097,10 +2422,10 @@
         <v>242</v>
       </c>
       <c r="F64" t="s">
-        <v>305</v>
+        <v>243</v>
       </c>
       <c r="G64" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3117,10 +2442,10 @@
         <v>242</v>
       </c>
       <c r="F65" t="s">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="G65" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3140,10 +2465,10 @@
         <v>242</v>
       </c>
       <c r="F66" t="s">
-        <v>307</v>
+        <v>243</v>
       </c>
       <c r="G66" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3160,10 +2485,10 @@
         <v>242</v>
       </c>
       <c r="F67" t="s">
-        <v>308</v>
+        <v>243</v>
       </c>
       <c r="G67" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3180,10 +2505,10 @@
         <v>242</v>
       </c>
       <c r="F68" t="s">
-        <v>309</v>
+        <v>243</v>
       </c>
       <c r="G68" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3200,10 +2525,10 @@
         <v>242</v>
       </c>
       <c r="F69" t="s">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="G69" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3220,10 +2545,10 @@
         <v>242</v>
       </c>
       <c r="F70" t="s">
-        <v>311</v>
+        <v>243</v>
       </c>
       <c r="G70" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3243,10 +2568,10 @@
         <v>242</v>
       </c>
       <c r="F71" t="s">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="G71" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3263,10 +2588,10 @@
         <v>242</v>
       </c>
       <c r="F72" t="s">
-        <v>313</v>
+        <v>243</v>
       </c>
       <c r="G72" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3283,10 +2608,10 @@
         <v>242</v>
       </c>
       <c r="F73" t="s">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="G73" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3303,10 +2628,10 @@
         <v>242</v>
       </c>
       <c r="F74" t="s">
-        <v>315</v>
+        <v>243</v>
       </c>
       <c r="G74" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3323,10 +2648,10 @@
         <v>242</v>
       </c>
       <c r="F75" t="s">
-        <v>316</v>
+        <v>243</v>
       </c>
       <c r="G75" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3346,10 +2671,10 @@
         <v>242</v>
       </c>
       <c r="F76" t="s">
-        <v>317</v>
+        <v>243</v>
       </c>
       <c r="G76" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3366,10 +2691,10 @@
         <v>241</v>
       </c>
       <c r="F77" t="s">
-        <v>318</v>
+        <v>243</v>
       </c>
       <c r="G77" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3386,10 +2711,10 @@
         <v>241</v>
       </c>
       <c r="F78" t="s">
-        <v>319</v>
+        <v>243</v>
       </c>
       <c r="G78" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3406,10 +2731,10 @@
         <v>241</v>
       </c>
       <c r="F79" t="s">
-        <v>320</v>
+        <v>243</v>
       </c>
       <c r="G79" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3426,10 +2751,10 @@
         <v>241</v>
       </c>
       <c r="F80" t="s">
-        <v>321</v>
+        <v>243</v>
       </c>
       <c r="G80" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3449,10 +2774,10 @@
         <v>241</v>
       </c>
       <c r="F81" t="s">
-        <v>322</v>
+        <v>243</v>
       </c>
       <c r="G81" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3469,10 +2794,10 @@
         <v>241</v>
       </c>
       <c r="F82" t="s">
-        <v>323</v>
+        <v>243</v>
       </c>
       <c r="G82" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3489,10 +2814,10 @@
         <v>241</v>
       </c>
       <c r="F83" t="s">
-        <v>324</v>
+        <v>243</v>
       </c>
       <c r="G83" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3509,10 +2834,10 @@
         <v>241</v>
       </c>
       <c r="F84" t="s">
-        <v>325</v>
+        <v>243</v>
       </c>
       <c r="G84" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3529,10 +2854,10 @@
         <v>241</v>
       </c>
       <c r="F85" t="s">
-        <v>326</v>
+        <v>243</v>
       </c>
       <c r="G85" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3552,10 +2877,10 @@
         <v>241</v>
       </c>
       <c r="F86" t="s">
-        <v>327</v>
+        <v>243</v>
       </c>
       <c r="G86" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3572,10 +2897,10 @@
         <v>241</v>
       </c>
       <c r="F87" t="s">
-        <v>328</v>
+        <v>243</v>
       </c>
       <c r="G87" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3592,10 +2917,10 @@
         <v>241</v>
       </c>
       <c r="F88" t="s">
-        <v>329</v>
+        <v>243</v>
       </c>
       <c r="G88" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3612,10 +2937,10 @@
         <v>241</v>
       </c>
       <c r="F89" t="s">
-        <v>330</v>
+        <v>243</v>
       </c>
       <c r="G89" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3632,10 +2957,10 @@
         <v>241</v>
       </c>
       <c r="F90" t="s">
-        <v>331</v>
+        <v>243</v>
       </c>
       <c r="G90" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3655,10 +2980,10 @@
         <v>241</v>
       </c>
       <c r="F91" t="s">
-        <v>332</v>
+        <v>243</v>
       </c>
       <c r="G91" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3675,10 +3000,10 @@
         <v>241</v>
       </c>
       <c r="F92" t="s">
-        <v>333</v>
+        <v>243</v>
       </c>
       <c r="G92" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3695,10 +3020,10 @@
         <v>241</v>
       </c>
       <c r="F93" t="s">
-        <v>334</v>
+        <v>243</v>
       </c>
       <c r="G93" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3715,10 +3040,10 @@
         <v>241</v>
       </c>
       <c r="F94" t="s">
-        <v>335</v>
+        <v>243</v>
       </c>
       <c r="G94" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3735,10 +3060,10 @@
         <v>241</v>
       </c>
       <c r="F95" t="s">
-        <v>336</v>
+        <v>243</v>
       </c>
       <c r="G95" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3758,10 +3083,10 @@
         <v>241</v>
       </c>
       <c r="F96" t="s">
-        <v>337</v>
+        <v>243</v>
       </c>
       <c r="G96" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3778,10 +3103,10 @@
         <v>241</v>
       </c>
       <c r="F97" t="s">
-        <v>338</v>
+        <v>243</v>
       </c>
       <c r="G97" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3798,10 +3123,10 @@
         <v>241</v>
       </c>
       <c r="F98" t="s">
-        <v>339</v>
+        <v>243</v>
       </c>
       <c r="G98" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3818,10 +3143,10 @@
         <v>241</v>
       </c>
       <c r="F99" t="s">
-        <v>340</v>
+        <v>243</v>
       </c>
       <c r="G99" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3838,10 +3163,10 @@
         <v>241</v>
       </c>
       <c r="F100" t="s">
-        <v>341</v>
+        <v>243</v>
       </c>
       <c r="G100" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3861,10 +3186,10 @@
         <v>241</v>
       </c>
       <c r="F101" t="s">
-        <v>342</v>
+        <v>243</v>
       </c>
       <c r="G101" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3881,10 +3206,10 @@
         <v>242</v>
       </c>
       <c r="F102" t="s">
-        <v>343</v>
+        <v>243</v>
       </c>
       <c r="G102" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3901,10 +3226,10 @@
         <v>242</v>
       </c>
       <c r="F103" t="s">
-        <v>344</v>
+        <v>243</v>
       </c>
       <c r="G103" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3921,10 +3246,10 @@
         <v>242</v>
       </c>
       <c r="F104" t="s">
-        <v>345</v>
+        <v>243</v>
       </c>
       <c r="G104" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3941,10 +3266,10 @@
         <v>242</v>
       </c>
       <c r="F105" t="s">
-        <v>346</v>
+        <v>243</v>
       </c>
       <c r="G105" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3964,10 +3289,10 @@
         <v>242</v>
       </c>
       <c r="F106" t="s">
-        <v>347</v>
+        <v>243</v>
       </c>
       <c r="G106" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3984,10 +3309,10 @@
         <v>242</v>
       </c>
       <c r="F107" t="s">
-        <v>348</v>
+        <v>243</v>
       </c>
       <c r="G107" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4004,10 +3329,10 @@
         <v>242</v>
       </c>
       <c r="F108" t="s">
-        <v>349</v>
+        <v>243</v>
       </c>
       <c r="G108" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4024,10 +3349,10 @@
         <v>242</v>
       </c>
       <c r="F109" t="s">
-        <v>350</v>
+        <v>243</v>
       </c>
       <c r="G109" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4044,10 +3369,10 @@
         <v>242</v>
       </c>
       <c r="F110" t="s">
-        <v>351</v>
+        <v>243</v>
       </c>
       <c r="G110" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4067,10 +3392,10 @@
         <v>242</v>
       </c>
       <c r="F111" t="s">
-        <v>352</v>
+        <v>243</v>
       </c>
       <c r="G111" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4087,10 +3412,10 @@
         <v>242</v>
       </c>
       <c r="F112" t="s">
-        <v>353</v>
+        <v>243</v>
       </c>
       <c r="G112" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4107,10 +3432,10 @@
         <v>242</v>
       </c>
       <c r="F113" t="s">
-        <v>354</v>
+        <v>243</v>
       </c>
       <c r="G113" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4127,10 +3452,10 @@
         <v>242</v>
       </c>
       <c r="F114" t="s">
-        <v>355</v>
+        <v>243</v>
       </c>
       <c r="G114" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4147,10 +3472,10 @@
         <v>242</v>
       </c>
       <c r="F115" t="s">
-        <v>356</v>
+        <v>243</v>
       </c>
       <c r="G115" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4170,10 +3495,10 @@
         <v>242</v>
       </c>
       <c r="F116" t="s">
-        <v>357</v>
+        <v>243</v>
       </c>
       <c r="G116" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4190,10 +3515,10 @@
         <v>242</v>
       </c>
       <c r="F117" t="s">
-        <v>358</v>
+        <v>243</v>
       </c>
       <c r="G117" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4210,10 +3535,10 @@
         <v>242</v>
       </c>
       <c r="F118" t="s">
-        <v>359</v>
+        <v>243</v>
       </c>
       <c r="G118" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4230,10 +3555,10 @@
         <v>242</v>
       </c>
       <c r="F119" t="s">
-        <v>360</v>
+        <v>243</v>
       </c>
       <c r="G119" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4250,10 +3575,10 @@
         <v>242</v>
       </c>
       <c r="F120" t="s">
-        <v>361</v>
+        <v>243</v>
       </c>
       <c r="G120" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4273,10 +3598,10 @@
         <v>242</v>
       </c>
       <c r="F121" t="s">
-        <v>362</v>
+        <v>243</v>
       </c>
       <c r="G121" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4293,10 +3618,10 @@
         <v>242</v>
       </c>
       <c r="F122" t="s">
-        <v>363</v>
+        <v>243</v>
       </c>
       <c r="G122" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4313,10 +3638,10 @@
         <v>242</v>
       </c>
       <c r="F123" t="s">
-        <v>364</v>
+        <v>243</v>
       </c>
       <c r="G123" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4333,10 +3658,10 @@
         <v>242</v>
       </c>
       <c r="F124" t="s">
-        <v>365</v>
+        <v>243</v>
       </c>
       <c r="G124" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4353,10 +3678,10 @@
         <v>242</v>
       </c>
       <c r="F125" t="s">
-        <v>366</v>
+        <v>243</v>
       </c>
       <c r="G125" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4376,10 +3701,10 @@
         <v>242</v>
       </c>
       <c r="F126" t="s">
-        <v>367</v>
+        <v>243</v>
       </c>
       <c r="G126" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4396,10 +3721,10 @@
         <v>242</v>
       </c>
       <c r="F127" t="s">
-        <v>368</v>
+        <v>243</v>
       </c>
       <c r="G127" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4416,10 +3741,10 @@
         <v>242</v>
       </c>
       <c r="F128" t="s">
-        <v>369</v>
+        <v>243</v>
       </c>
       <c r="G128" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4436,10 +3761,10 @@
         <v>242</v>
       </c>
       <c r="F129" t="s">
-        <v>370</v>
+        <v>243</v>
       </c>
       <c r="G129" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4456,10 +3781,10 @@
         <v>242</v>
       </c>
       <c r="F130" t="s">
-        <v>371</v>
+        <v>243</v>
       </c>
       <c r="G130" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4479,10 +3804,10 @@
         <v>242</v>
       </c>
       <c r="F131" t="s">
-        <v>372</v>
+        <v>243</v>
       </c>
       <c r="G131" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4499,10 +3824,10 @@
         <v>242</v>
       </c>
       <c r="F132" t="s">
-        <v>373</v>
+        <v>243</v>
       </c>
       <c r="G132" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4519,10 +3844,10 @@
         <v>242</v>
       </c>
       <c r="F133" t="s">
-        <v>374</v>
+        <v>243</v>
       </c>
       <c r="G133" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4539,10 +3864,10 @@
         <v>242</v>
       </c>
       <c r="F134" t="s">
-        <v>375</v>
+        <v>243</v>
       </c>
       <c r="G134" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4559,10 +3884,10 @@
         <v>242</v>
       </c>
       <c r="F135" t="s">
-        <v>376</v>
+        <v>243</v>
       </c>
       <c r="G135" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4582,10 +3907,10 @@
         <v>242</v>
       </c>
       <c r="F136" t="s">
-        <v>377</v>
+        <v>243</v>
       </c>
       <c r="G136" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4602,10 +3927,10 @@
         <v>242</v>
       </c>
       <c r="F137" t="s">
-        <v>378</v>
+        <v>243</v>
       </c>
       <c r="G137" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4622,10 +3947,10 @@
         <v>242</v>
       </c>
       <c r="F138" t="s">
-        <v>379</v>
+        <v>243</v>
       </c>
       <c r="G138" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4642,10 +3967,10 @@
         <v>242</v>
       </c>
       <c r="F139" t="s">
-        <v>380</v>
+        <v>243</v>
       </c>
       <c r="G139" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4662,10 +3987,10 @@
         <v>242</v>
       </c>
       <c r="F140" t="s">
-        <v>381</v>
+        <v>243</v>
       </c>
       <c r="G140" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4685,10 +4010,10 @@
         <v>242</v>
       </c>
       <c r="F141" t="s">
-        <v>382</v>
+        <v>243</v>
       </c>
       <c r="G141" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4705,10 +4030,10 @@
         <v>242</v>
       </c>
       <c r="F142" t="s">
-        <v>383</v>
+        <v>243</v>
       </c>
       <c r="G142" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4725,10 +4050,10 @@
         <v>242</v>
       </c>
       <c r="F143" t="s">
-        <v>384</v>
+        <v>243</v>
       </c>
       <c r="G143" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4745,10 +4070,10 @@
         <v>242</v>
       </c>
       <c r="F144" t="s">
-        <v>385</v>
+        <v>243</v>
       </c>
       <c r="G144" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4765,10 +4090,10 @@
         <v>242</v>
       </c>
       <c r="F145" t="s">
-        <v>386</v>
+        <v>243</v>
       </c>
       <c r="G145" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4788,10 +4113,10 @@
         <v>242</v>
       </c>
       <c r="F146" t="s">
-        <v>387</v>
+        <v>243</v>
       </c>
       <c r="G146" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4808,10 +4133,10 @@
         <v>242</v>
       </c>
       <c r="F147" t="s">
-        <v>388</v>
+        <v>243</v>
       </c>
       <c r="G147" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4828,10 +4153,10 @@
         <v>242</v>
       </c>
       <c r="F148" t="s">
-        <v>389</v>
+        <v>243</v>
       </c>
       <c r="G148" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4848,10 +4173,10 @@
         <v>242</v>
       </c>
       <c r="F149" t="s">
-        <v>390</v>
+        <v>243</v>
       </c>
       <c r="G149" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4868,10 +4193,10 @@
         <v>242</v>
       </c>
       <c r="F150" t="s">
-        <v>391</v>
+        <v>243</v>
       </c>
       <c r="G150" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4891,10 +4216,10 @@
         <v>242</v>
       </c>
       <c r="F151" t="s">
-        <v>392</v>
+        <v>243</v>
       </c>
       <c r="G151" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4911,10 +4236,10 @@
         <v>241</v>
       </c>
       <c r="F152" t="s">
-        <v>393</v>
+        <v>243</v>
       </c>
       <c r="G152" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4931,10 +4256,10 @@
         <v>241</v>
       </c>
       <c r="F153" t="s">
-        <v>394</v>
+        <v>243</v>
       </c>
       <c r="G153" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4951,10 +4276,10 @@
         <v>241</v>
       </c>
       <c r="F154" t="s">
-        <v>395</v>
+        <v>243</v>
       </c>
       <c r="G154" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4971,10 +4296,10 @@
         <v>241</v>
       </c>
       <c r="F155" t="s">
-        <v>396</v>
+        <v>243</v>
       </c>
       <c r="G155" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4994,10 +4319,10 @@
         <v>241</v>
       </c>
       <c r="F156" t="s">
-        <v>397</v>
+        <v>243</v>
       </c>
       <c r="G156" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5014,10 +4339,10 @@
         <v>241</v>
       </c>
       <c r="F157" t="s">
-        <v>398</v>
+        <v>243</v>
       </c>
       <c r="G157" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5034,10 +4359,10 @@
         <v>241</v>
       </c>
       <c r="F158" t="s">
-        <v>399</v>
+        <v>243</v>
       </c>
       <c r="G158" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5054,10 +4379,10 @@
         <v>241</v>
       </c>
       <c r="F159" t="s">
-        <v>400</v>
+        <v>243</v>
       </c>
       <c r="G159" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5074,10 +4399,10 @@
         <v>241</v>
       </c>
       <c r="F160" t="s">
-        <v>401</v>
+        <v>243</v>
       </c>
       <c r="G160" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5097,10 +4422,10 @@
         <v>241</v>
       </c>
       <c r="F161" t="s">
-        <v>402</v>
+        <v>243</v>
       </c>
       <c r="G161" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5117,10 +4442,10 @@
         <v>241</v>
       </c>
       <c r="F162" t="s">
-        <v>403</v>
+        <v>243</v>
       </c>
       <c r="G162" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5137,10 +4462,10 @@
         <v>241</v>
       </c>
       <c r="F163" t="s">
-        <v>404</v>
+        <v>243</v>
       </c>
       <c r="G163" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5157,10 +4482,10 @@
         <v>241</v>
       </c>
       <c r="F164" t="s">
-        <v>405</v>
+        <v>243</v>
       </c>
       <c r="G164" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5177,10 +4502,10 @@
         <v>241</v>
       </c>
       <c r="F165" t="s">
-        <v>406</v>
+        <v>243</v>
       </c>
       <c r="G165" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5200,10 +4525,10 @@
         <v>241</v>
       </c>
       <c r="F166" t="s">
-        <v>407</v>
+        <v>243</v>
       </c>
       <c r="G166" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5220,10 +4545,10 @@
         <v>241</v>
       </c>
       <c r="F167" t="s">
-        <v>408</v>
+        <v>243</v>
       </c>
       <c r="G167" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5240,10 +4565,10 @@
         <v>241</v>
       </c>
       <c r="F168" t="s">
-        <v>409</v>
+        <v>243</v>
       </c>
       <c r="G168" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5260,10 +4585,10 @@
         <v>241</v>
       </c>
       <c r="F169" t="s">
-        <v>410</v>
+        <v>243</v>
       </c>
       <c r="G169" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5280,10 +4605,10 @@
         <v>241</v>
       </c>
       <c r="F170" t="s">
-        <v>411</v>
+        <v>243</v>
       </c>
       <c r="G170" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5303,10 +4628,10 @@
         <v>241</v>
       </c>
       <c r="F171" t="s">
-        <v>412</v>
+        <v>243</v>
       </c>
       <c r="G171" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5323,10 +4648,10 @@
         <v>241</v>
       </c>
       <c r="F172" t="s">
-        <v>413</v>
+        <v>243</v>
       </c>
       <c r="G172" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5343,10 +4668,10 @@
         <v>241</v>
       </c>
       <c r="F173" t="s">
-        <v>414</v>
+        <v>243</v>
       </c>
       <c r="G173" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5363,10 +4688,10 @@
         <v>241</v>
       </c>
       <c r="F174" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
       <c r="G174" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5383,10 +4708,10 @@
         <v>241</v>
       </c>
       <c r="F175" t="s">
-        <v>416</v>
+        <v>243</v>
       </c>
       <c r="G175" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5406,10 +4731,10 @@
         <v>241</v>
       </c>
       <c r="F176" t="s">
-        <v>417</v>
+        <v>243</v>
       </c>
       <c r="G176" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5426,10 +4751,10 @@
         <v>242</v>
       </c>
       <c r="F177" t="s">
-        <v>418</v>
+        <v>243</v>
       </c>
       <c r="G177" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5446,10 +4771,10 @@
         <v>242</v>
       </c>
       <c r="F178" t="s">
-        <v>419</v>
+        <v>243</v>
       </c>
       <c r="G178" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5466,10 +4791,10 @@
         <v>242</v>
       </c>
       <c r="F179" t="s">
-        <v>420</v>
+        <v>243</v>
       </c>
       <c r="G179" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5486,10 +4811,10 @@
         <v>242</v>
       </c>
       <c r="F180" t="s">
-        <v>421</v>
+        <v>243</v>
       </c>
       <c r="G180" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5509,10 +4834,10 @@
         <v>242</v>
       </c>
       <c r="F181" t="s">
-        <v>422</v>
+        <v>243</v>
       </c>
       <c r="G181" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5529,10 +4854,10 @@
         <v>242</v>
       </c>
       <c r="F182" t="s">
-        <v>423</v>
+        <v>243</v>
       </c>
       <c r="G182" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5549,10 +4874,10 @@
         <v>242</v>
       </c>
       <c r="F183" t="s">
-        <v>424</v>
+        <v>243</v>
       </c>
       <c r="G183" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5569,10 +4894,10 @@
         <v>242</v>
       </c>
       <c r="F184" t="s">
-        <v>425</v>
+        <v>243</v>
       </c>
       <c r="G184" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5589,10 +4914,10 @@
         <v>242</v>
       </c>
       <c r="F185" t="s">
-        <v>426</v>
+        <v>243</v>
       </c>
       <c r="G185" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5612,10 +4937,10 @@
         <v>242</v>
       </c>
       <c r="F186" t="s">
-        <v>427</v>
+        <v>243</v>
       </c>
       <c r="G186" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5632,10 +4957,10 @@
         <v>242</v>
       </c>
       <c r="F187" t="s">
-        <v>428</v>
+        <v>243</v>
       </c>
       <c r="G187" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5652,10 +4977,10 @@
         <v>242</v>
       </c>
       <c r="F188" t="s">
-        <v>429</v>
+        <v>243</v>
       </c>
       <c r="G188" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5672,10 +4997,10 @@
         <v>242</v>
       </c>
       <c r="F189" t="s">
-        <v>430</v>
+        <v>243</v>
       </c>
       <c r="G189" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5692,10 +5017,10 @@
         <v>242</v>
       </c>
       <c r="F190" t="s">
-        <v>431</v>
+        <v>243</v>
       </c>
       <c r="G190" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5715,10 +5040,10 @@
         <v>242</v>
       </c>
       <c r="F191" t="s">
-        <v>432</v>
+        <v>243</v>
       </c>
       <c r="G191" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5735,10 +5060,10 @@
         <v>242</v>
       </c>
       <c r="F192" t="s">
-        <v>433</v>
+        <v>243</v>
       </c>
       <c r="G192" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5755,10 +5080,10 @@
         <v>242</v>
       </c>
       <c r="F193" t="s">
-        <v>434</v>
+        <v>243</v>
       </c>
       <c r="G193" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5775,10 +5100,10 @@
         <v>242</v>
       </c>
       <c r="F194" t="s">
-        <v>435</v>
+        <v>243</v>
       </c>
       <c r="G194" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5795,10 +5120,10 @@
         <v>242</v>
       </c>
       <c r="F195" t="s">
-        <v>436</v>
+        <v>243</v>
       </c>
       <c r="G195" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5818,10 +5143,10 @@
         <v>242</v>
       </c>
       <c r="F196" t="s">
-        <v>437</v>
+        <v>243</v>
       </c>
       <c r="G196" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5838,10 +5163,10 @@
         <v>242</v>
       </c>
       <c r="F197" t="s">
-        <v>438</v>
+        <v>243</v>
       </c>
       <c r="G197" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5858,10 +5183,10 @@
         <v>242</v>
       </c>
       <c r="F198" t="s">
-        <v>439</v>
+        <v>243</v>
       </c>
       <c r="G198" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5878,10 +5203,10 @@
         <v>242</v>
       </c>
       <c r="F199" t="s">
-        <v>440</v>
+        <v>243</v>
       </c>
       <c r="G199" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5898,10 +5223,10 @@
         <v>242</v>
       </c>
       <c r="F200" t="s">
-        <v>441</v>
+        <v>243</v>
       </c>
       <c r="G200" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5921,10 +5246,10 @@
         <v>242</v>
       </c>
       <c r="F201" t="s">
-        <v>442</v>
+        <v>243</v>
       </c>
       <c r="G201" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5941,10 +5266,10 @@
         <v>242</v>
       </c>
       <c r="F202" t="s">
-        <v>443</v>
+        <v>243</v>
       </c>
       <c r="G202" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5961,10 +5286,10 @@
         <v>242</v>
       </c>
       <c r="F203" t="s">
-        <v>444</v>
+        <v>243</v>
       </c>
       <c r="G203" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5981,10 +5306,10 @@
         <v>242</v>
       </c>
       <c r="F204" t="s">
-        <v>445</v>
+        <v>243</v>
       </c>
       <c r="G204" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6001,10 +5326,10 @@
         <v>242</v>
       </c>
       <c r="F205" t="s">
-        <v>446</v>
+        <v>243</v>
       </c>
       <c r="G205" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6024,10 +5349,10 @@
         <v>242</v>
       </c>
       <c r="F206" t="s">
-        <v>447</v>
+        <v>243</v>
       </c>
       <c r="G206" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6044,10 +5369,10 @@
         <v>242</v>
       </c>
       <c r="F207" t="s">
-        <v>448</v>
+        <v>243</v>
       </c>
       <c r="G207" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6064,10 +5389,10 @@
         <v>242</v>
       </c>
       <c r="F208" t="s">
-        <v>449</v>
+        <v>243</v>
       </c>
       <c r="G208" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6084,10 +5409,10 @@
         <v>242</v>
       </c>
       <c r="F209" t="s">
-        <v>450</v>
+        <v>243</v>
       </c>
       <c r="G209" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6104,10 +5429,10 @@
         <v>242</v>
       </c>
       <c r="F210" t="s">
-        <v>451</v>
+        <v>243</v>
       </c>
       <c r="G210" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6127,10 +5452,10 @@
         <v>242</v>
       </c>
       <c r="F211" t="s">
-        <v>452</v>
+        <v>243</v>
       </c>
       <c r="G211" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6147,10 +5472,10 @@
         <v>242</v>
       </c>
       <c r="F212" t="s">
-        <v>453</v>
+        <v>243</v>
       </c>
       <c r="G212" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6167,10 +5492,10 @@
         <v>242</v>
       </c>
       <c r="F213" t="s">
-        <v>454</v>
+        <v>243</v>
       </c>
       <c r="G213" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6187,10 +5512,10 @@
         <v>242</v>
       </c>
       <c r="F214" t="s">
-        <v>455</v>
+        <v>243</v>
       </c>
       <c r="G214" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6207,10 +5532,10 @@
         <v>242</v>
       </c>
       <c r="F215" t="s">
-        <v>456</v>
+        <v>243</v>
       </c>
       <c r="G215" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6230,10 +5555,10 @@
         <v>242</v>
       </c>
       <c r="F216" t="s">
-        <v>457</v>
+        <v>243</v>
       </c>
       <c r="G216" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6250,10 +5575,10 @@
         <v>242</v>
       </c>
       <c r="F217" t="s">
-        <v>458</v>
+        <v>243</v>
       </c>
       <c r="G217" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6270,10 +5595,10 @@
         <v>242</v>
       </c>
       <c r="F218" t="s">
-        <v>459</v>
+        <v>243</v>
       </c>
       <c r="G218" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6290,10 +5615,10 @@
         <v>242</v>
       </c>
       <c r="F219" t="s">
-        <v>460</v>
+        <v>243</v>
       </c>
       <c r="G219" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6310,10 +5635,10 @@
         <v>242</v>
       </c>
       <c r="F220" t="s">
-        <v>461</v>
+        <v>243</v>
       </c>
       <c r="G220" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6333,10 +5658,10 @@
         <v>242</v>
       </c>
       <c r="F221" t="s">
-        <v>462</v>
+        <v>243</v>
       </c>
       <c r="G221" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6353,10 +5678,10 @@
         <v>242</v>
       </c>
       <c r="F222" t="s">
-        <v>463</v>
+        <v>243</v>
       </c>
       <c r="G222" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6373,10 +5698,10 @@
         <v>242</v>
       </c>
       <c r="F223" t="s">
-        <v>464</v>
+        <v>243</v>
       </c>
       <c r="G223" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6393,10 +5718,10 @@
         <v>242</v>
       </c>
       <c r="F224" t="s">
-        <v>465</v>
+        <v>243</v>
       </c>
       <c r="G224" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6413,10 +5738,10 @@
         <v>242</v>
       </c>
       <c r="F225" t="s">
-        <v>466</v>
+        <v>243</v>
       </c>
       <c r="G225" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6436,10 +5761,10 @@
         <v>242</v>
       </c>
       <c r="F226" t="s">
-        <v>467</v>
+        <v>243</v>
       </c>
       <c r="G226" t="s">
-        <v>469</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -437,7 +437,7 @@
         <v>20.0</v>
       </c>
       <c r="D2" s="5">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>9</v>
@@ -521,7 +521,7 @@
         <v>35.0</v>
       </c>
       <c r="D4" s="5">
-        <v>30.0</v>
+        <v>41.0</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>16</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="26">
   <si>
     <t>الاسم</t>
   </si>
@@ -43,25 +43,31 @@
     <t>كيلو</t>
   </si>
   <si>
+    <t>images/طماطم.png</t>
+  </si>
+  <si>
+    <t>نعم</t>
+  </si>
+  <si>
+    <t>مانجا</t>
+  </si>
+  <si>
+    <t>images/خيار.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مناديل سحب </t>
+  </si>
+  <si>
+    <t>قطعة</t>
+  </si>
+  <si>
+    <t>images/كوسة.png</t>
+  </si>
+  <si>
+    <t>شاي250 جرام</t>
+  </si>
+  <si>
     <t>images/placeholder.png</t>
-  </si>
-  <si>
-    <t>لا</t>
-  </si>
-  <si>
-    <t>مانجا</t>
-  </si>
-  <si>
-    <t>نعم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مناديل سحب </t>
-  </si>
-  <si>
-    <t>قطعة</t>
-  </si>
-  <si>
-    <t>شاي250 جرام</t>
   </si>
   <si>
     <t>فلل اسود 100جرام</t>
@@ -414,12 +420,12 @@
         <v>20.0</v>
       </c>
       <c r="D2" s="4">
-        <v>16.0</v>
+        <v>777777.0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -437,16 +443,16 @@
         <v>70.0</v>
       </c>
       <c r="D3" s="4">
-        <v>6666.0</v>
+        <v>60.0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -460,21 +466,21 @@
         <v>35.0</v>
       </c>
       <c r="D4" s="4">
-        <v>666.0</v>
+        <v>30.0</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>10</v>
+      <c r="F4" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>8</v>
@@ -489,15 +495,15 @@
         <v>15</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>8</v>
@@ -506,21 +512,21 @@
         <v>40.0</v>
       </c>
       <c r="D6" s="4">
-        <v>77898.0</v>
+        <v>30.0</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
@@ -535,15 +541,15 @@
         <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
@@ -552,21 +558,21 @@
         <v>33.0</v>
       </c>
       <c r="D8" s="4">
-        <v>34.0</v>
+        <v>777777.0</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>8</v>
@@ -581,15 +587,15 @@
         <v>15</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
@@ -604,15 +610,15 @@
         <v>9</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>8</v>
@@ -627,15 +633,15 @@
         <v>9</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>8</v>
@@ -650,15 +656,15 @@
         <v>9</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>8</v>
@@ -673,10 +679,10 @@
         <v>9</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -43,7 +43,7 @@
     <t>كيلو</t>
   </si>
   <si>
-    <t>images/طماطم.png</t>
+    <t>images/1.png</t>
   </si>
   <si>
     <t>نعم</t>
@@ -52,7 +52,7 @@
     <t>مانجا</t>
   </si>
   <si>
-    <t>images/خيار.png</t>
+    <t>images/2.png</t>
   </si>
   <si>
     <t xml:space="preserve">مناديل سحب </t>
@@ -61,7 +61,7 @@
     <t>قطعة</t>
   </si>
   <si>
-    <t>images/كوسة.png</t>
+    <t>images/3.png</t>
   </si>
   <si>
     <t>شاي250 جرام</t>
@@ -420,7 +420,7 @@
         <v>20.0</v>
       </c>
       <c r="D2" s="4">
-        <v>777777.0</v>
+        <v>9.99999999E8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
@@ -443,7 +443,7 @@
         <v>70.0</v>
       </c>
       <c r="D3" s="4">
-        <v>60.0</v>
+        <v>6666666.0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="245">
   <si>
     <t>الاسم</t>
   </si>
@@ -712,36 +712,6 @@
     <t>معطر تفصيل</t>
   </si>
   <si>
-    <t>عرض حصري 1</t>
-  </si>
-  <si>
-    <t>عرض حصري 2</t>
-  </si>
-  <si>
-    <t>عرض حصري 3</t>
-  </si>
-  <si>
-    <t>عرض حصري 4</t>
-  </si>
-  <si>
-    <t>عرض حصري 5</t>
-  </si>
-  <si>
-    <t>عرض حصري 6</t>
-  </si>
-  <si>
-    <t>عرض حصري 7</t>
-  </si>
-  <si>
-    <t>عرض حصري 8</t>
-  </si>
-  <si>
-    <t>عرض حصري 9</t>
-  </si>
-  <si>
-    <t>عرض حصري 10</t>
-  </si>
-  <si>
     <t>الفواكه والخضار</t>
   </si>
   <si>
@@ -767,9 +737,6 @@
   </si>
   <si>
     <t>المنظفات</t>
-  </si>
-  <si>
-    <t>عروض اليوم</t>
   </si>
   <si>
     <t>كيلو</t>
@@ -1139,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G236"/>
+  <dimension ref="A1:G226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1170,7 +1137,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C2">
         <v>22</v>
@@ -1179,13 +1146,13 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G2" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1193,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C3">
         <v>24</v>
@@ -1202,13 +1169,13 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F3" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G3" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1216,7 +1183,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C4">
         <v>26</v>
@@ -1225,13 +1192,13 @@
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F4" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G4" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1239,19 +1206,19 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C5">
         <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F5" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G5" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1259,19 +1226,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C6">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F6" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G6" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1279,19 +1246,19 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F7" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G7" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1299,19 +1266,19 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C8">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F8" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G8" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1319,19 +1286,19 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C9">
         <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F9" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G9" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1339,19 +1306,19 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C10">
         <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F10" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G10" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1359,19 +1326,19 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C11">
         <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F11" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G11" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1379,19 +1346,19 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C12">
         <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F12" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G12" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1399,19 +1366,19 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C13">
         <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F13" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G13" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1419,19 +1386,19 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C14">
         <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F14" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G14" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1439,19 +1406,19 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C15">
         <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F15" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G15" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1459,19 +1426,19 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C16">
         <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F16" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G16" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1479,19 +1446,19 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C17">
         <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F17" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G17" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1499,19 +1466,19 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C18">
         <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F18" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G18" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1519,19 +1486,19 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C19">
         <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F19" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G19" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1539,19 +1506,19 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C20">
         <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F20" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G20" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1559,19 +1526,19 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C21">
         <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F21" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G21" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1579,19 +1546,19 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C22">
         <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F22" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G22" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1599,19 +1566,19 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C23">
         <v>64</v>
       </c>
       <c r="E23" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F23" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G23" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1619,19 +1586,19 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C24">
         <v>66</v>
       </c>
       <c r="E24" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F24" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G24" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1639,19 +1606,19 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C25">
         <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F25" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G25" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1659,19 +1626,19 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C26">
         <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F26" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G26" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1679,7 +1646,7 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C27">
         <v>22</v>
@@ -1688,13 +1655,13 @@
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F27" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G27" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1702,7 +1669,7 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C28">
         <v>24</v>
@@ -1711,13 +1678,13 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F28" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G28" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1725,7 +1692,7 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C29">
         <v>26</v>
@@ -1734,13 +1701,13 @@
         <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F29" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G29" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1748,19 +1715,19 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C30">
         <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F30" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G30" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1768,19 +1735,19 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F31" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G31" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1788,19 +1755,19 @@
         <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C32">
         <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F32" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G32" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1808,19 +1775,19 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C33">
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F33" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G33" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1828,19 +1795,19 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C34">
         <v>36</v>
       </c>
       <c r="E34" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F34" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G34" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1848,19 +1815,19 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C35">
         <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F35" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G35" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1868,19 +1835,19 @@
         <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C36">
         <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F36" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G36" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1888,19 +1855,19 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C37">
         <v>42</v>
       </c>
       <c r="E37" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F37" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G37" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1908,19 +1875,19 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C38">
         <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F38" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G38" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1928,19 +1895,19 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C39">
         <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F39" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G39" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1948,19 +1915,19 @@
         <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C40">
         <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F40" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G40" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1968,19 +1935,19 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C41">
         <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F41" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G41" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1988,19 +1955,19 @@
         <v>47</v>
       </c>
       <c r="B42" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C42">
         <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F42" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G42" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2008,19 +1975,19 @@
         <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C43">
         <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F43" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G43" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2028,19 +1995,19 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C44">
         <v>56</v>
       </c>
       <c r="E44" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F44" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G44" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2048,19 +2015,19 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C45">
         <v>58</v>
       </c>
       <c r="E45" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F45" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G45" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2068,19 +2035,19 @@
         <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C46">
         <v>60</v>
       </c>
       <c r="E46" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F46" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G46" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2088,19 +2055,19 @@
         <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C47">
         <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F47" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G47" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2108,19 +2075,19 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C48">
         <v>64</v>
       </c>
       <c r="E48" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F48" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G48" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2128,19 +2095,19 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C49">
         <v>66</v>
       </c>
       <c r="E49" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F49" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G49" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2148,19 +2115,19 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C50">
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F50" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G50" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2168,19 +2135,19 @@
         <v>56</v>
       </c>
       <c r="B51" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C51">
         <v>70</v>
       </c>
       <c r="E51" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F51" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G51" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2188,7 +2155,7 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C52">
         <v>22</v>
@@ -2197,13 +2164,13 @@
         <v>17</v>
       </c>
       <c r="E52" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F52" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G52" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2211,7 +2178,7 @@
         <v>58</v>
       </c>
       <c r="B53" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C53">
         <v>24</v>
@@ -2220,13 +2187,13 @@
         <v>19</v>
       </c>
       <c r="E53" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F53" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G53" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2234,7 +2201,7 @@
         <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C54">
         <v>26</v>
@@ -2243,13 +2210,13 @@
         <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F54" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G54" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2257,19 +2224,19 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C55">
         <v>28</v>
       </c>
       <c r="E55" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F55" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G55" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2277,19 +2244,19 @@
         <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C56">
         <v>30</v>
       </c>
       <c r="E56" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F56" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G56" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2297,19 +2264,19 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C57">
         <v>32</v>
       </c>
       <c r="E57" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F57" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G57" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2317,19 +2284,19 @@
         <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C58">
         <v>34</v>
       </c>
       <c r="E58" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F58" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G58" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2337,19 +2304,19 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C59">
         <v>36</v>
       </c>
       <c r="E59" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F59" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G59" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2357,19 +2324,19 @@
         <v>65</v>
       </c>
       <c r="B60" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C60">
         <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F60" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G60" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2377,19 +2344,19 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C61">
         <v>40</v>
       </c>
       <c r="E61" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F61" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G61" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2397,19 +2364,19 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C62">
         <v>42</v>
       </c>
       <c r="E62" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F62" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G62" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2417,19 +2384,19 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C63">
         <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F63" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G63" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2437,19 +2404,19 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C64">
         <v>46</v>
       </c>
       <c r="E64" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F64" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G64" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2457,19 +2424,19 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C65">
         <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F65" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G65" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2477,19 +2444,19 @@
         <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C66">
         <v>50</v>
       </c>
       <c r="E66" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F66" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G66" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2497,19 +2464,19 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C67">
         <v>52</v>
       </c>
       <c r="E67" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F67" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G67" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2517,19 +2484,19 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C68">
         <v>54</v>
       </c>
       <c r="E68" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F68" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G68" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2537,19 +2504,19 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C69">
         <v>56</v>
       </c>
       <c r="E69" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F69" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G69" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2557,19 +2524,19 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C70">
         <v>58</v>
       </c>
       <c r="E70" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F70" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G70" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2577,19 +2544,19 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C71">
         <v>60</v>
       </c>
       <c r="E71" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F71" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G71" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2597,19 +2564,19 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C72">
         <v>62</v>
       </c>
       <c r="E72" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F72" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G72" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2617,19 +2584,19 @@
         <v>78</v>
       </c>
       <c r="B73" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C73">
         <v>64</v>
       </c>
       <c r="E73" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F73" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G73" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2637,19 +2604,19 @@
         <v>79</v>
       </c>
       <c r="B74" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C74">
         <v>66</v>
       </c>
       <c r="E74" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F74" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G74" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2657,19 +2624,19 @@
         <v>80</v>
       </c>
       <c r="B75" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C75">
         <v>68</v>
       </c>
       <c r="E75" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F75" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G75" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2677,19 +2644,19 @@
         <v>81</v>
       </c>
       <c r="B76" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C76">
         <v>70</v>
       </c>
       <c r="E76" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F76" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G76" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2697,7 +2664,7 @@
         <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C77">
         <v>22</v>
@@ -2706,13 +2673,13 @@
         <v>17</v>
       </c>
       <c r="E77" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F77" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G77" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2720,7 +2687,7 @@
         <v>83</v>
       </c>
       <c r="B78" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C78">
         <v>24</v>
@@ -2729,13 +2696,13 @@
         <v>19</v>
       </c>
       <c r="E78" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F78" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G78" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2743,7 +2710,7 @@
         <v>84</v>
       </c>
       <c r="B79" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C79">
         <v>26</v>
@@ -2752,13 +2719,13 @@
         <v>21</v>
       </c>
       <c r="E79" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F79" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G79" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2766,19 +2733,19 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C80">
         <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F80" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G80" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2786,19 +2753,19 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C81">
         <v>30</v>
       </c>
       <c r="E81" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F81" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G81" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2806,19 +2773,19 @@
         <v>87</v>
       </c>
       <c r="B82" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C82">
         <v>32</v>
       </c>
       <c r="E82" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F82" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G82" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2826,19 +2793,19 @@
         <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C83">
         <v>34</v>
       </c>
       <c r="E83" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F83" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G83" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2846,19 +2813,19 @@
         <v>89</v>
       </c>
       <c r="B84" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C84">
         <v>36</v>
       </c>
       <c r="E84" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F84" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G84" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2866,19 +2833,19 @@
         <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C85">
         <v>38</v>
       </c>
       <c r="E85" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F85" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G85" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2886,19 +2853,19 @@
         <v>91</v>
       </c>
       <c r="B86" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C86">
         <v>40</v>
       </c>
       <c r="E86" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F86" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G86" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2906,19 +2873,19 @@
         <v>92</v>
       </c>
       <c r="B87" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C87">
         <v>42</v>
       </c>
       <c r="E87" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F87" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G87" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2926,19 +2893,19 @@
         <v>93</v>
       </c>
       <c r="B88" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C88">
         <v>44</v>
       </c>
       <c r="E88" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F88" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G88" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2946,19 +2913,19 @@
         <v>94</v>
       </c>
       <c r="B89" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C89">
         <v>46</v>
       </c>
       <c r="E89" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F89" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G89" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2966,19 +2933,19 @@
         <v>95</v>
       </c>
       <c r="B90" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C90">
         <v>48</v>
       </c>
       <c r="E90" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F90" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G90" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2986,19 +2953,19 @@
         <v>96</v>
       </c>
       <c r="B91" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C91">
         <v>50</v>
       </c>
       <c r="E91" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F91" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G91" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3006,19 +2973,19 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C92">
         <v>52</v>
       </c>
       <c r="E92" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F92" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G92" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3026,19 +2993,19 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C93">
         <v>54</v>
       </c>
       <c r="E93" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F93" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G93" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3046,19 +3013,19 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C94">
         <v>56</v>
       </c>
       <c r="E94" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F94" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G94" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3066,19 +3033,19 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C95">
         <v>58</v>
       </c>
       <c r="E95" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F95" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G95" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3086,19 +3053,19 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C96">
         <v>60</v>
       </c>
       <c r="E96" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F96" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G96" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3106,19 +3073,19 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C97">
         <v>62</v>
       </c>
       <c r="E97" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F97" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G97" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3126,19 +3093,19 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C98">
         <v>64</v>
       </c>
       <c r="E98" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F98" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G98" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3146,19 +3113,19 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C99">
         <v>66</v>
       </c>
       <c r="E99" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F99" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G99" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3166,19 +3133,19 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C100">
         <v>68</v>
       </c>
       <c r="E100" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F100" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G100" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3186,19 +3153,19 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C101">
         <v>70</v>
       </c>
       <c r="E101" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F101" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G101" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3206,7 +3173,7 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C102">
         <v>22</v>
@@ -3215,13 +3182,13 @@
         <v>17</v>
       </c>
       <c r="E102" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F102" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G102" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3229,7 +3196,7 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C103">
         <v>24</v>
@@ -3238,13 +3205,13 @@
         <v>19</v>
       </c>
       <c r="E103" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F103" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G103" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3252,7 +3219,7 @@
         <v>109</v>
       </c>
       <c r="B104" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C104">
         <v>26</v>
@@ -3261,13 +3228,13 @@
         <v>21</v>
       </c>
       <c r="E104" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F104" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G104" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3275,19 +3242,19 @@
         <v>110</v>
       </c>
       <c r="B105" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C105">
         <v>28</v>
       </c>
       <c r="E105" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F105" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G105" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3295,19 +3262,19 @@
         <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C106">
         <v>30</v>
       </c>
       <c r="E106" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F106" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G106" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3315,19 +3282,19 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C107">
         <v>32</v>
       </c>
       <c r="E107" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F107" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G107" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3335,19 +3302,19 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C108">
         <v>34</v>
       </c>
       <c r="E108" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F108" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G108" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3355,19 +3322,19 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C109">
         <v>36</v>
       </c>
       <c r="E109" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F109" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G109" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3375,19 +3342,19 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C110">
         <v>38</v>
       </c>
       <c r="E110" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F110" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G110" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3395,19 +3362,19 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C111">
         <v>40</v>
       </c>
       <c r="E111" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F111" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G111" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3415,19 +3382,19 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C112">
         <v>42</v>
       </c>
       <c r="E112" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F112" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G112" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3435,19 +3402,19 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C113">
         <v>44</v>
       </c>
       <c r="E113" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F113" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G113" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3455,19 +3422,19 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C114">
         <v>46</v>
       </c>
       <c r="E114" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F114" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G114" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3475,19 +3442,19 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C115">
         <v>48</v>
       </c>
       <c r="E115" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F115" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G115" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3495,19 +3462,19 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C116">
         <v>50</v>
       </c>
       <c r="E116" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F116" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G116" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3515,19 +3482,19 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C117">
         <v>52</v>
       </c>
       <c r="E117" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F117" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G117" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3535,19 +3502,19 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C118">
         <v>54</v>
       </c>
       <c r="E118" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F118" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G118" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3555,19 +3522,19 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C119">
         <v>56</v>
       </c>
       <c r="E119" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F119" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G119" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3575,19 +3542,19 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C120">
         <v>58</v>
       </c>
       <c r="E120" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F120" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G120" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3595,19 +3562,19 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C121">
         <v>60</v>
       </c>
       <c r="E121" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F121" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G121" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3615,19 +3582,19 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C122">
         <v>62</v>
       </c>
       <c r="E122" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F122" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G122" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3635,19 +3602,19 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C123">
         <v>64</v>
       </c>
       <c r="E123" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F123" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G123" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3655,19 +3622,19 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C124">
         <v>66</v>
       </c>
       <c r="E124" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F124" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G124" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3675,19 +3642,19 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C125">
         <v>68</v>
       </c>
       <c r="E125" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F125" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G125" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3695,19 +3662,19 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C126">
         <v>70</v>
       </c>
       <c r="E126" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F126" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G126" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -3715,7 +3682,7 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C127">
         <v>22</v>
@@ -3724,13 +3691,13 @@
         <v>17</v>
       </c>
       <c r="E127" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F127" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G127" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -3738,7 +3705,7 @@
         <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C128">
         <v>24</v>
@@ -3747,13 +3714,13 @@
         <v>19</v>
       </c>
       <c r="E128" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F128" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G128" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -3761,7 +3728,7 @@
         <v>134</v>
       </c>
       <c r="B129" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C129">
         <v>26</v>
@@ -3770,13 +3737,13 @@
         <v>21</v>
       </c>
       <c r="E129" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F129" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G129" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3784,19 +3751,19 @@
         <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C130">
         <v>28</v>
       </c>
       <c r="E130" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F130" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G130" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -3804,19 +3771,19 @@
         <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C131">
         <v>30</v>
       </c>
       <c r="E131" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F131" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G131" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -3824,19 +3791,19 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C132">
         <v>32</v>
       </c>
       <c r="E132" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F132" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G132" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3844,19 +3811,19 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C133">
         <v>34</v>
       </c>
       <c r="E133" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F133" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G133" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -3864,19 +3831,19 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C134">
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F134" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G134" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -3884,19 +3851,19 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C135">
         <v>38</v>
       </c>
       <c r="E135" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F135" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G135" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -3904,19 +3871,19 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C136">
         <v>40</v>
       </c>
       <c r="E136" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F136" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G136" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -3924,19 +3891,19 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C137">
         <v>42</v>
       </c>
       <c r="E137" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F137" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G137" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -3944,19 +3911,19 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C138">
         <v>44</v>
       </c>
       <c r="E138" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F138" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G138" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -3964,19 +3931,19 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C139">
         <v>46</v>
       </c>
       <c r="E139" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F139" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G139" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -3984,19 +3951,19 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C140">
         <v>48</v>
       </c>
       <c r="E140" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F140" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G140" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4004,19 +3971,19 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C141">
         <v>50</v>
       </c>
       <c r="E141" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F141" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G141" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4024,19 +3991,19 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C142">
         <v>52</v>
       </c>
       <c r="E142" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F142" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G142" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4044,19 +4011,19 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C143">
         <v>54</v>
       </c>
       <c r="E143" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F143" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G143" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4064,19 +4031,19 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C144">
         <v>56</v>
       </c>
       <c r="E144" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F144" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G144" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4084,19 +4051,19 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C145">
         <v>58</v>
       </c>
       <c r="E145" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F145" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G145" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4104,19 +4071,19 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C146">
         <v>60</v>
       </c>
       <c r="E146" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F146" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G146" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4124,19 +4091,19 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C147">
         <v>62</v>
       </c>
       <c r="E147" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F147" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G147" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4144,19 +4111,19 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C148">
         <v>64</v>
       </c>
       <c r="E148" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F148" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G148" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4164,19 +4131,19 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C149">
         <v>66</v>
       </c>
       <c r="E149" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F149" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G149" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4184,19 +4151,19 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C150">
         <v>68</v>
       </c>
       <c r="E150" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F150" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G150" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4204,19 +4171,19 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C151">
         <v>70</v>
       </c>
       <c r="E151" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F151" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G151" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4224,7 +4191,7 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C152">
         <v>22</v>
@@ -4233,13 +4200,13 @@
         <v>17</v>
       </c>
       <c r="E152" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F152" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G152" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4247,7 +4214,7 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C153">
         <v>24</v>
@@ -4256,13 +4223,13 @@
         <v>19</v>
       </c>
       <c r="E153" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F153" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G153" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4270,7 +4237,7 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C154">
         <v>26</v>
@@ -4279,13 +4246,13 @@
         <v>21</v>
       </c>
       <c r="E154" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F154" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G154" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4293,19 +4260,19 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C155">
         <v>28</v>
       </c>
       <c r="E155" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F155" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G155" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4313,19 +4280,19 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C156">
         <v>30</v>
       </c>
       <c r="E156" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F156" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G156" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4333,19 +4300,19 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C157">
         <v>32</v>
       </c>
       <c r="E157" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F157" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G157" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4353,19 +4320,19 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C158">
         <v>34</v>
       </c>
       <c r="E158" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F158" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G158" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4373,19 +4340,19 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C159">
         <v>36</v>
       </c>
       <c r="E159" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F159" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G159" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4393,19 +4360,19 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C160">
         <v>38</v>
       </c>
       <c r="E160" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F160" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G160" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4413,19 +4380,19 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C161">
         <v>40</v>
       </c>
       <c r="E161" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F161" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G161" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4433,19 +4400,19 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C162">
         <v>42</v>
       </c>
       <c r="E162" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F162" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G162" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4453,19 +4420,19 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C163">
         <v>44</v>
       </c>
       <c r="E163" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F163" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G163" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4473,19 +4440,19 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C164">
         <v>46</v>
       </c>
       <c r="E164" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F164" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G164" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4493,19 +4460,19 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C165">
         <v>48</v>
       </c>
       <c r="E165" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F165" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G165" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4513,19 +4480,19 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C166">
         <v>50</v>
       </c>
       <c r="E166" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F166" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G166" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4533,19 +4500,19 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C167">
         <v>52</v>
       </c>
       <c r="E167" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F167" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G167" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4553,19 +4520,19 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C168">
         <v>54</v>
       </c>
       <c r="E168" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F168" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G168" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4573,19 +4540,19 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C169">
         <v>56</v>
       </c>
       <c r="E169" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F169" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G169" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4593,19 +4560,19 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C170">
         <v>58</v>
       </c>
       <c r="E170" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F170" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G170" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4613,19 +4580,19 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C171">
         <v>60</v>
       </c>
       <c r="E171" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F171" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G171" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4633,19 +4600,19 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C172">
         <v>62</v>
       </c>
       <c r="E172" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F172" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G172" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4653,19 +4620,19 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C173">
         <v>64</v>
       </c>
       <c r="E173" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F173" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G173" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4673,19 +4640,19 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C174">
         <v>66</v>
       </c>
       <c r="E174" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F174" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G174" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4693,19 +4660,19 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C175">
         <v>68</v>
       </c>
       <c r="E175" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F175" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G175" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4713,19 +4680,19 @@
         <v>181</v>
       </c>
       <c r="B176" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C176">
         <v>70</v>
       </c>
       <c r="E176" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="F176" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G176" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -4733,7 +4700,7 @@
         <v>182</v>
       </c>
       <c r="B177" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C177">
         <v>22</v>
@@ -4742,13 +4709,13 @@
         <v>17</v>
       </c>
       <c r="E177" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F177" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G177" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -4756,7 +4723,7 @@
         <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C178">
         <v>24</v>
@@ -4765,13 +4732,13 @@
         <v>19</v>
       </c>
       <c r="E178" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F178" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G178" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -4779,7 +4746,7 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C179">
         <v>26</v>
@@ -4788,13 +4755,13 @@
         <v>21</v>
       </c>
       <c r="E179" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F179" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G179" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -4802,19 +4769,19 @@
         <v>185</v>
       </c>
       <c r="B180" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C180">
         <v>28</v>
       </c>
       <c r="E180" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F180" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G180" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -4822,19 +4789,19 @@
         <v>186</v>
       </c>
       <c r="B181" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C181">
         <v>30</v>
       </c>
       <c r="E181" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F181" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G181" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -4842,19 +4809,19 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C182">
         <v>32</v>
       </c>
       <c r="E182" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F182" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G182" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -4862,19 +4829,19 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C183">
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F183" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G183" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -4882,19 +4849,19 @@
         <v>189</v>
       </c>
       <c r="B184" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C184">
         <v>36</v>
       </c>
       <c r="E184" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F184" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G184" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -4902,19 +4869,19 @@
         <v>190</v>
       </c>
       <c r="B185" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C185">
         <v>38</v>
       </c>
       <c r="E185" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F185" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G185" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -4922,19 +4889,19 @@
         <v>191</v>
       </c>
       <c r="B186" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C186">
         <v>40</v>
       </c>
       <c r="E186" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F186" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G186" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -4942,19 +4909,19 @@
         <v>192</v>
       </c>
       <c r="B187" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C187">
         <v>42</v>
       </c>
       <c r="E187" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F187" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G187" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -4962,19 +4929,19 @@
         <v>193</v>
       </c>
       <c r="B188" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C188">
         <v>44</v>
       </c>
       <c r="E188" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F188" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G188" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -4982,19 +4949,19 @@
         <v>194</v>
       </c>
       <c r="B189" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C189">
         <v>46</v>
       </c>
       <c r="E189" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F189" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G189" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5002,19 +4969,19 @@
         <v>195</v>
       </c>
       <c r="B190" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C190">
         <v>48</v>
       </c>
       <c r="E190" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F190" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G190" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5022,19 +4989,19 @@
         <v>196</v>
       </c>
       <c r="B191" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C191">
         <v>50</v>
       </c>
       <c r="E191" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F191" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G191" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5042,19 +5009,19 @@
         <v>197</v>
       </c>
       <c r="B192" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C192">
         <v>52</v>
       </c>
       <c r="E192" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F192" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G192" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5062,19 +5029,19 @@
         <v>198</v>
       </c>
       <c r="B193" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C193">
         <v>54</v>
       </c>
       <c r="E193" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F193" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G193" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5082,19 +5049,19 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C194">
         <v>56</v>
       </c>
       <c r="E194" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F194" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G194" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5102,19 +5069,19 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C195">
         <v>58</v>
       </c>
       <c r="E195" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F195" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G195" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5122,19 +5089,19 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C196">
         <v>60</v>
       </c>
       <c r="E196" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F196" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G196" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5142,19 +5109,19 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C197">
         <v>62</v>
       </c>
       <c r="E197" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F197" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G197" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5162,19 +5129,19 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C198">
         <v>64</v>
       </c>
       <c r="E198" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F198" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G198" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5182,19 +5149,19 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C199">
         <v>66</v>
       </c>
       <c r="E199" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F199" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G199" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5202,19 +5169,19 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C200">
         <v>68</v>
       </c>
       <c r="E200" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F200" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G200" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5222,19 +5189,19 @@
         <v>206</v>
       </c>
       <c r="B201" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C201">
         <v>70</v>
       </c>
       <c r="E201" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F201" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G201" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5242,7 +5209,7 @@
         <v>207</v>
       </c>
       <c r="B202" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C202">
         <v>22</v>
@@ -5251,13 +5218,13 @@
         <v>17</v>
       </c>
       <c r="E202" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F202" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G202" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5265,7 +5232,7 @@
         <v>208</v>
       </c>
       <c r="B203" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C203">
         <v>24</v>
@@ -5274,13 +5241,13 @@
         <v>19</v>
       </c>
       <c r="E203" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F203" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G203" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5288,7 +5255,7 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C204">
         <v>26</v>
@@ -5297,13 +5264,13 @@
         <v>21</v>
       </c>
       <c r="E204" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F204" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G204" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5311,19 +5278,19 @@
         <v>210</v>
       </c>
       <c r="B205" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C205">
         <v>28</v>
       </c>
       <c r="E205" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F205" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G205" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5331,19 +5298,19 @@
         <v>211</v>
       </c>
       <c r="B206" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C206">
         <v>30</v>
       </c>
       <c r="E206" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F206" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G206" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5351,19 +5318,19 @@
         <v>212</v>
       </c>
       <c r="B207" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C207">
         <v>32</v>
       </c>
       <c r="E207" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F207" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G207" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5371,19 +5338,19 @@
         <v>213</v>
       </c>
       <c r="B208" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C208">
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F208" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G208" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5391,19 +5358,19 @@
         <v>214</v>
       </c>
       <c r="B209" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C209">
         <v>36</v>
       </c>
       <c r="E209" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F209" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G209" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5411,19 +5378,19 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C210">
         <v>38</v>
       </c>
       <c r="E210" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F210" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G210" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5431,19 +5398,19 @@
         <v>216</v>
       </c>
       <c r="B211" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C211">
         <v>40</v>
       </c>
       <c r="E211" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F211" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G211" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5451,19 +5418,19 @@
         <v>217</v>
       </c>
       <c r="B212" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C212">
         <v>42</v>
       </c>
       <c r="E212" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F212" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G212" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5471,19 +5438,19 @@
         <v>218</v>
       </c>
       <c r="B213" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C213">
         <v>44</v>
       </c>
       <c r="E213" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F213" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G213" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5491,19 +5458,19 @@
         <v>219</v>
       </c>
       <c r="B214" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C214">
         <v>46</v>
       </c>
       <c r="E214" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F214" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G214" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5511,19 +5478,19 @@
         <v>220</v>
       </c>
       <c r="B215" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C215">
         <v>48</v>
       </c>
       <c r="E215" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F215" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G215" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5531,19 +5498,19 @@
         <v>221</v>
       </c>
       <c r="B216" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C216">
         <v>50</v>
       </c>
       <c r="E216" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F216" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G216" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5551,19 +5518,19 @@
         <v>222</v>
       </c>
       <c r="B217" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C217">
         <v>52</v>
       </c>
       <c r="E217" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F217" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G217" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5571,19 +5538,19 @@
         <v>223</v>
       </c>
       <c r="B218" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>54</v>
       </c>
       <c r="E218" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F218" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G218" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5591,19 +5558,19 @@
         <v>224</v>
       </c>
       <c r="B219" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C219">
         <v>56</v>
       </c>
       <c r="E219" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F219" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G219" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5611,19 +5578,19 @@
         <v>225</v>
       </c>
       <c r="B220" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C220">
         <v>58</v>
       </c>
       <c r="E220" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F220" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G220" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -5631,19 +5598,19 @@
         <v>226</v>
       </c>
       <c r="B221" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C221">
         <v>60</v>
       </c>
       <c r="E221" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F221" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G221" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -5651,19 +5618,19 @@
         <v>227</v>
       </c>
       <c r="B222" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C222">
         <v>62</v>
       </c>
       <c r="E222" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F222" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G222" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -5671,19 +5638,19 @@
         <v>228</v>
       </c>
       <c r="B223" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C223">
         <v>64</v>
       </c>
       <c r="E223" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F223" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G223" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -5691,19 +5658,19 @@
         <v>229</v>
       </c>
       <c r="B224" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C224">
         <v>66</v>
       </c>
       <c r="E224" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F224" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G224" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5711,19 +5678,19 @@
         <v>230</v>
       </c>
       <c r="B225" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C225">
         <v>68</v>
       </c>
       <c r="E225" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F225" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G225" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5731,249 +5698,19 @@
         <v>231</v>
       </c>
       <c r="B226" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C226">
         <v>70</v>
       </c>
       <c r="E226" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F226" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G226" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7">
-      <c r="A227" t="s">
-        <v>232</v>
-      </c>
-      <c r="B227" t="s">
-        <v>251</v>
-      </c>
-      <c r="C227">
-        <v>105</v>
-      </c>
-      <c r="D227">
-        <v>85</v>
-      </c>
-      <c r="E227" t="s">
-        <v>253</v>
-      </c>
-      <c r="F227" t="s">
-        <v>254</v>
-      </c>
-      <c r="G227" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7">
-      <c r="A228" t="s">
-        <v>233</v>
-      </c>
-      <c r="B228" t="s">
-        <v>251</v>
-      </c>
-      <c r="C228">
-        <v>110</v>
-      </c>
-      <c r="D228">
-        <v>90</v>
-      </c>
-      <c r="E228" t="s">
-        <v>253</v>
-      </c>
-      <c r="F228" t="s">
-        <v>254</v>
-      </c>
-      <c r="G228" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7">
-      <c r="A229" t="s">
-        <v>234</v>
-      </c>
-      <c r="B229" t="s">
-        <v>251</v>
-      </c>
-      <c r="C229">
-        <v>115</v>
-      </c>
-      <c r="D229">
-        <v>95</v>
-      </c>
-      <c r="E229" t="s">
-        <v>253</v>
-      </c>
-      <c r="F229" t="s">
-        <v>254</v>
-      </c>
-      <c r="G229" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7">
-      <c r="A230" t="s">
-        <v>235</v>
-      </c>
-      <c r="B230" t="s">
-        <v>251</v>
-      </c>
-      <c r="C230">
-        <v>120</v>
-      </c>
-      <c r="D230">
-        <v>100</v>
-      </c>
-      <c r="E230" t="s">
-        <v>253</v>
-      </c>
-      <c r="F230" t="s">
-        <v>254</v>
-      </c>
-      <c r="G230" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7">
-      <c r="A231" t="s">
-        <v>236</v>
-      </c>
-      <c r="B231" t="s">
-        <v>251</v>
-      </c>
-      <c r="C231">
-        <v>125</v>
-      </c>
-      <c r="D231">
-        <v>105</v>
-      </c>
-      <c r="E231" t="s">
-        <v>253</v>
-      </c>
-      <c r="F231" t="s">
-        <v>254</v>
-      </c>
-      <c r="G231" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7">
-      <c r="A232" t="s">
-        <v>237</v>
-      </c>
-      <c r="B232" t="s">
-        <v>251</v>
-      </c>
-      <c r="C232">
-        <v>130</v>
-      </c>
-      <c r="D232">
-        <v>110</v>
-      </c>
-      <c r="E232" t="s">
-        <v>253</v>
-      </c>
-      <c r="F232" t="s">
-        <v>254</v>
-      </c>
-      <c r="G232" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7">
-      <c r="A233" t="s">
-        <v>238</v>
-      </c>
-      <c r="B233" t="s">
-        <v>251</v>
-      </c>
-      <c r="C233">
-        <v>135</v>
-      </c>
-      <c r="D233">
-        <v>115</v>
-      </c>
-      <c r="E233" t="s">
-        <v>253</v>
-      </c>
-      <c r="F233" t="s">
-        <v>254</v>
-      </c>
-      <c r="G233" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7">
-      <c r="A234" t="s">
-        <v>239</v>
-      </c>
-      <c r="B234" t="s">
-        <v>251</v>
-      </c>
-      <c r="C234">
-        <v>140</v>
-      </c>
-      <c r="D234">
-        <v>120</v>
-      </c>
-      <c r="E234" t="s">
-        <v>253</v>
-      </c>
-      <c r="F234" t="s">
-        <v>254</v>
-      </c>
-      <c r="G234" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7">
-      <c r="A235" t="s">
-        <v>240</v>
-      </c>
-      <c r="B235" t="s">
-        <v>251</v>
-      </c>
-      <c r="C235">
-        <v>145</v>
-      </c>
-      <c r="D235">
-        <v>125</v>
-      </c>
-      <c r="E235" t="s">
-        <v>253</v>
-      </c>
-      <c r="F235" t="s">
-        <v>254</v>
-      </c>
-      <c r="G235" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
-      <c r="A236" t="s">
-        <v>241</v>
-      </c>
-      <c r="B236" t="s">
-        <v>251</v>
-      </c>
-      <c r="C236">
-        <v>150</v>
-      </c>
-      <c r="D236">
-        <v>130</v>
-      </c>
-      <c r="E236" t="s">
-        <v>253</v>
-      </c>
-      <c r="F236" t="s">
-        <v>254</v>
-      </c>
-      <c r="G236" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="244">
   <si>
     <t>الاسم</t>
   </si>
@@ -37,679 +37,679 @@
     <t>متوفر</t>
   </si>
   <si>
-    <t>طماطم بلدي</t>
-  </si>
-  <si>
-    <t>خيار طازج</t>
-  </si>
-  <si>
-    <t>بطاطس تقلية</t>
-  </si>
-  <si>
-    <t>بصل أحمر</t>
-  </si>
-  <si>
-    <t>جزر طازج</t>
-  </si>
-  <si>
-    <t>فلفل رومي</t>
-  </si>
-  <si>
-    <t>باذنجان رومي</t>
-  </si>
-  <si>
-    <t>ليمون أصفر</t>
-  </si>
-  <si>
-    <t>تفاح أمريكي</t>
-  </si>
-  <si>
-    <t>موز مستورد</t>
-  </si>
-  <si>
-    <t>برتقال أبو صير</t>
-  </si>
-  <si>
-    <t>فراولة طازجة</t>
-  </si>
-  <si>
-    <t>مانجو زبدية</t>
-  </si>
-  <si>
-    <t>خوخ بلدي</t>
-  </si>
-  <si>
-    <t>عنب مرسلي</t>
-  </si>
-  <si>
-    <t>بطيخ أحمر</t>
-  </si>
-  <si>
-    <t>كنتالوب</t>
-  </si>
-  <si>
-    <t>أنناس</t>
-  </si>
-  <si>
-    <t>كيوي</t>
-  </si>
-  <si>
-    <t>بلح زغلول</t>
-  </si>
-  <si>
-    <t>كرنب أحمر</t>
-  </si>
-  <si>
-    <t>خس كابوتشا</t>
-  </si>
-  <si>
-    <t>بقدونس</t>
-  </si>
-  <si>
-    <t>كزبرة</t>
-  </si>
-  <si>
-    <t>شبت</t>
-  </si>
-  <si>
-    <t>لب محمص</t>
-  </si>
-  <si>
-    <t>لب سوبر</t>
-  </si>
-  <si>
-    <t>لب أبيض</t>
-  </si>
-  <si>
-    <t>سوداني مقشر</t>
-  </si>
-  <si>
-    <t>مكسرات مشكلة</t>
-  </si>
-  <si>
-    <t>فستق محمص</t>
-  </si>
-  <si>
-    <t>بندق محمص</t>
-  </si>
-  <si>
-    <t>كاجو محمص</t>
-  </si>
-  <si>
-    <t>لوز محمص</t>
-  </si>
-  <si>
-    <t>عين جمل</t>
-  </si>
-  <si>
-    <t>مقرمشات جبنة</t>
-  </si>
-  <si>
-    <t>مقرمشات حار</t>
-  </si>
-  <si>
-    <t>ذرة تبشير</t>
-  </si>
-  <si>
-    <t>فسدوق</t>
-  </si>
-  <si>
-    <t>مقرمشات مكسيكية</t>
-  </si>
-  <si>
-    <t>فول سوداني بالشوكولاتة</t>
-  </si>
-  <si>
-    <t>زبيب جولد</t>
-  </si>
-  <si>
-    <t>قراصيا مجففة</t>
-  </si>
-  <si>
-    <t>مشمشية</t>
-  </si>
-  <si>
-    <t>تين مجفف</t>
-  </si>
-  <si>
-    <t>تمر هندي</t>
-  </si>
-  <si>
-    <t>مقرمشات بالملح</t>
-  </si>
-  <si>
-    <t>لب سوري</t>
-  </si>
-  <si>
-    <t>لب تركي</t>
-  </si>
-  <si>
-    <t>مكسرات صيني</t>
-  </si>
-  <si>
-    <t>شاي العروسة</t>
-  </si>
-  <si>
-    <t>شاي ليبتون</t>
-  </si>
-  <si>
-    <t>نسكافيه كلاسيك</t>
-  </si>
-  <si>
-    <t>قهوة تركي مظبوط</t>
-  </si>
-  <si>
-    <t>عصير مانجو جهينة</t>
-  </si>
-  <si>
-    <t>عصير جوافة جهينة</t>
-  </si>
-  <si>
-    <t>مياه معدنية نستله</t>
-  </si>
-  <si>
-    <t>مياه بريل</t>
-  </si>
-  <si>
-    <t>بيبسي كانز</t>
-  </si>
-  <si>
-    <t>كوكا كولا كانز</t>
-  </si>
-  <si>
-    <t>سفن أب</t>
-  </si>
-  <si>
-    <t>ميرندا تفاح</t>
-  </si>
-  <si>
-    <t>شاي سبز</t>
-  </si>
-  <si>
-    <t>ينسون كابتن</t>
-  </si>
-  <si>
-    <t>نعناع هاني</t>
-  </si>
-  <si>
-    <t>كركديه أسواني</t>
-  </si>
-  <si>
-    <t>حلبة حصى</t>
-  </si>
-  <si>
-    <t>قهوة إسبرسو</t>
-  </si>
-  <si>
-    <t>مشروب طاقة ريد بول</t>
-  </si>
-  <si>
-    <t>عصير برتقال طبيعي</t>
-  </si>
-  <si>
-    <t>شاي مثلج</t>
-  </si>
-  <si>
-    <t>قهوة بالبندق</t>
-  </si>
-  <si>
-    <t>شاي أخضر بالياسمين</t>
-  </si>
-  <si>
-    <t>سحلب تركي</t>
-  </si>
-  <si>
-    <t>مشروب شوكولاتة ساخنة</t>
-  </si>
-  <si>
-    <t>أرز المصري</t>
-  </si>
-  <si>
-    <t>مكرونة الملكة</t>
-  </si>
-  <si>
-    <t>مكرونة الضحكة</t>
-  </si>
-  <si>
-    <t>زيت عافية ذرة</t>
-  </si>
-  <si>
-    <t>زيت سلايت عباد</t>
-  </si>
-  <si>
-    <t>سمنة روابي</t>
-  </si>
-  <si>
-    <t>عدس أصفر</t>
-  </si>
-  <si>
-    <t>عدس بجبة</t>
-  </si>
-  <si>
-    <t>فول تدميس</t>
-  </si>
-  <si>
-    <t>لوبيا خشک</t>
-  </si>
-  <si>
-    <t>فاصوليا وائت</t>
-  </si>
-  <si>
-    <t>ملح طعام</t>
-  </si>
-  <si>
-    <t>صلصة طماطم</t>
-  </si>
-  <si>
-    <t>تونة إيطالي</t>
-  </si>
-  <si>
-    <t>مرقة دجاج ماجي</t>
-  </si>
-  <si>
-    <t>خل عود</t>
-  </si>
-  <si>
-    <t>دقيق فاخر</t>
-  </si>
-  <si>
-    <t>نشا ذرة</t>
-  </si>
-  <si>
-    <t>برغل دقيق</t>
-  </si>
-  <si>
-    <t>فريك دقيق</t>
-  </si>
-  <si>
-    <t>حمص شام</t>
-  </si>
-  <si>
-    <t>ترمس حلو</t>
-  </si>
-  <si>
-    <t>مياه غازية</t>
-  </si>
-  <si>
-    <t>شعرية المطبخ</t>
-  </si>
-  <si>
-    <t>لسان عصفور</t>
-  </si>
-  <si>
-    <t>لبن جهينة طبيعي</t>
-  </si>
-  <si>
-    <t>لبن المراعي</t>
-  </si>
-  <si>
-    <t>جبنة فيتا طرية</t>
-  </si>
-  <si>
-    <t>جبنة رومي أقدم</t>
-  </si>
-  <si>
-    <t>جبنة شيدر مستورد</t>
-  </si>
-  <si>
-    <t>قشطة بلدي</t>
-  </si>
-  <si>
-    <t>زبادي المراعي</t>
-  </si>
-  <si>
-    <t>زبادي دانيت</t>
-  </si>
-  <si>
-    <t>زبدة نيوزلندي</t>
-  </si>
-  <si>
-    <t>موتزاريلا مبشورة</t>
-  </si>
-  <si>
-    <t>جبنة إسطنبولي</t>
-  </si>
-  <si>
-    <t>جبنة براميلي</t>
-  </si>
-  <si>
-    <t>جبنة مثلثات</t>
-  </si>
-  <si>
-    <t>لبن رايب</t>
-  </si>
-  <si>
-    <t>كريمة طهي</t>
-  </si>
-  <si>
-    <t>كريمة خفق</t>
-  </si>
-  <si>
-    <t>جبنة قريش</t>
-  </si>
-  <si>
-    <t>حليب مكثف محلى</t>
-  </si>
-  <si>
-    <t>زبادي فواكه</t>
-  </si>
-  <si>
-    <t>لبن جوز الهند</t>
-  </si>
-  <si>
-    <t>جبنة بلاستيك</t>
-  </si>
-  <si>
-    <t>شيدر مدخن</t>
-  </si>
-  <si>
-    <t>جبنة حلوم</t>
-  </si>
-  <si>
-    <t>حليب بودرة</t>
-  </si>
-  <si>
-    <t>لبن ماعز</t>
-  </si>
-  <si>
-    <t>عيش بلدي طازج</t>
-  </si>
-  <si>
-    <t>عيش فينو</t>
-  </si>
-  <si>
-    <t>قرص بالصكوك</t>
-  </si>
-  <si>
-    <t>قرص عجوة</t>
-  </si>
-  <si>
-    <t>باتيه جبنة</t>
-  </si>
-  <si>
-    <t>باتيه شوكولاتة</t>
-  </si>
-  <si>
-    <t>كرواسون زبدة</t>
-  </si>
-  <si>
-    <t>كرواسون شوكولاتة</t>
-  </si>
-  <si>
-    <t>توست بر</t>
-  </si>
-  <si>
-    <t>توست أبيض</t>
-  </si>
-  <si>
-    <t>شابورة دايت</t>
-  </si>
-  <si>
-    <t>بقسماط بالسمسم</t>
-  </si>
-  <si>
-    <t>كيك شوكولاتة</t>
-  </si>
-  <si>
-    <t>كب كيك</t>
-  </si>
-  <si>
-    <t>تارت فراولة</t>
-  </si>
-  <si>
-    <t>بسكويت سادة</t>
-  </si>
-  <si>
-    <t>بسكويت بالشوكولاتة</t>
-  </si>
-  <si>
-    <t>فطير مشلتت</t>
-  </si>
-  <si>
-    <t>عيش سوري</t>
-  </si>
-  <si>
-    <t>عيش شامي</t>
-  </si>
-  <si>
-    <t>بسكويت دايجستف</t>
-  </si>
-  <si>
-    <t>قرص سادة</t>
-  </si>
-  <si>
-    <t>كوكيز بالشوكولاتة</t>
-  </si>
-  <si>
-    <t>خبز برجر</t>
-  </si>
-  <si>
-    <t>خبز توست أسمر</t>
-  </si>
-  <si>
-    <t>فلفل أسود مطحون</t>
-  </si>
-  <si>
-    <t>كمون بلدي</t>
-  </si>
-  <si>
-    <t>كزبرة خشکة</t>
-  </si>
-  <si>
-    <t>بهارات مشكلة</t>
-  </si>
-  <si>
-    <t>قرفة مطحونة</t>
-  </si>
-  <si>
-    <t>هيل (حبهان)</t>
-  </si>
-  <si>
-    <t>قرنفل صحيح</t>
-  </si>
-  <si>
-    <t>كركم آصلي</t>
-  </si>
-  <si>
-    <t>كاري هندي</t>
-  </si>
-  <si>
-    <t>بابريكا سموكي</t>
-  </si>
-  <si>
-    <t>زعتر بري</t>
-  </si>
-  <si>
-    <t>روزماري</t>
-  </si>
-  <si>
-    <t>ورق لورا</t>
-  </si>
-  <si>
-    <t>ملح ليمون</t>
-  </si>
-  <si>
-    <t>ثوم بودرة</t>
-  </si>
-  <si>
-    <t>بصل بودرة</t>
-  </si>
-  <si>
-    <t>شطّة حارة</t>
-  </si>
-  <si>
-    <t>جنزبيل مطحون</t>
-  </si>
-  <si>
-    <t>سماق تركي</t>
-  </si>
-  <si>
-    <t>جوزة الطيب</t>
-  </si>
-  <si>
-    <t>بهارات لحمة</t>
-  </si>
-  <si>
-    <t>بهارات فراخ</t>
-  </si>
-  <si>
-    <t>زعفران</t>
-  </si>
-  <si>
-    <t>كمون حاص</t>
-  </si>
-  <si>
-    <t>فلفل أبيض</t>
-  </si>
-  <si>
-    <t>شوكولاتة جالاكسي</t>
-  </si>
-  <si>
-    <t>شوكولاتة كادبوري</t>
-  </si>
-  <si>
-    <t>شوكولاتة بيك اب</t>
-  </si>
-  <si>
-    <t>بسكويت أوريو</t>
-  </si>
-  <si>
-    <t>شوكولاتة مارس</t>
-  </si>
-  <si>
-    <t>شوكولاتة سنيكرز</t>
-  </si>
-  <si>
-    <t>جيلي فواكه</t>
-  </si>
-  <si>
-    <t>مصاصة كاندي</t>
-  </si>
-  <si>
-    <t>مللبس لوز</t>
-  </si>
-  <si>
-    <t>حلاوة طحينية</t>
-  </si>
-  <si>
-    <t>شوكولاتة كيت كات</t>
-  </si>
-  <si>
-    <t>بونبوني نعناع</t>
-  </si>
-  <si>
-    <t>علوة مستكة</t>
-  </si>
-  <si>
-    <t>شوكولاتة فريرو روشيه</t>
-  </si>
-  <si>
-    <t>حلوى جيلي كولا</t>
-  </si>
-  <si>
-    <t>شوكولاتة باونتي</t>
-  </si>
-  <si>
-    <t>توفي بقر</t>
-  </si>
-  <si>
-    <t>كراميل</t>
-  </si>
-  <si>
-    <t>شوكولاتة بالبندق</t>
-  </si>
-  <si>
-    <t>بسكويت لوتا</t>
-  </si>
-  <si>
-    <t>شوكولاتة ديربي</t>
-  </si>
-  <si>
-    <t>شوكولاتة بيمبو</t>
-  </si>
-  <si>
-    <t>بسكويت تومي</t>
-  </si>
-  <si>
-    <t>حلوى غزل البنات</t>
-  </si>
-  <si>
-    <t>شوكولاتة داكنة</t>
-  </si>
-  <si>
-    <t>مسحوق أريال أوتوماتيك</t>
-  </si>
-  <si>
-    <t>برسيل جل</t>
-  </si>
-  <si>
-    <t>دواني منعم ملابس</t>
-  </si>
-  <si>
-    <t>سائل غسيل أطباق فيري</t>
-  </si>
-  <si>
-    <t>كلوركس ابيض</t>
-  </si>
-  <si>
-    <t>كلوركس ألوان</t>
-  </si>
-  <si>
-    <t>ديتول مطهر</t>
-  </si>
-  <si>
-    <t>صابون بانيو</t>
-  </si>
-  <si>
-    <t>معطر جو فبريز</t>
-  </si>
-  <si>
-    <t>مناديل فاين</t>
-  </si>
-  <si>
-    <t>بكر تواليت سانيتا</t>
-  </si>
-  <si>
-    <t>اسفنج مواعين</t>
-  </si>
-  <si>
-    <t>فلاش تنظيف الحمامات</t>
-  </si>
-  <si>
-    <t>مسحوق تايد</t>
-  </si>
-  <si>
-    <t>جل استحمام شاور</t>
-  </si>
-  <si>
-    <t>شامبو صانسيلك</t>
-  </si>
-  <si>
-    <t>معجون اسنان كولجيت</t>
-  </si>
-  <si>
-    <t>فرشاة اسنان</t>
-  </si>
-  <si>
-    <t>مبيد حشرات ريد</t>
-  </si>
-  <si>
-    <t>أكياس قمامة</t>
-  </si>
-  <si>
-    <t>مسحوق برسيل اليدوي</t>
-  </si>
-  <si>
-    <t>صابون سائل لليدين</t>
-  </si>
-  <si>
-    <t>منظف زجاج</t>
-  </si>
-  <si>
-    <t>كلور فلاش</t>
-  </si>
-  <si>
-    <t>معطر تفصيل</t>
+    <t>منتج من الفواكه والخضار 1</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 2</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 3</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 4</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 5</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 6</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 7</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 8</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 9</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 10</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 11</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 12</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 13</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 14</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 15</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 16</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 17</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 18</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 19</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 20</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 21</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 22</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 23</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 24</t>
+  </si>
+  <si>
+    <t>منتج من الفواكه والخضار 25</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 1</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 2</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 3</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 4</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 5</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 6</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 7</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 8</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 9</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 10</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 11</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 12</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 13</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 14</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 15</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 16</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 17</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 18</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 19</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 20</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 21</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 22</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 23</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 24</t>
+  </si>
+  <si>
+    <t>منتج من التسالي والمكسرات 25</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 1</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 2</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 3</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 4</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 5</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 6</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 7</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 8</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 9</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 10</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 11</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 12</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 13</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 14</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 15</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 16</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 17</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 18</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 19</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 20</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 21</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 22</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 23</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 24</t>
+  </si>
+  <si>
+    <t>منتج من المشروبات 25</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 1</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 2</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 3</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 4</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 5</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 6</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 7</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 8</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 9</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 10</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 11</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 12</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 13</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 14</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 15</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 16</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 17</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 18</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 19</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 20</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 21</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 22</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 23</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 24</t>
+  </si>
+  <si>
+    <t>منتج من البقالة 25</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 1</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 2</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 3</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 4</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 5</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 6</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 7</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 8</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 9</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 10</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 11</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 12</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 13</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 14</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 15</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 16</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 17</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 18</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 19</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 20</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 21</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 22</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 23</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 24</t>
+  </si>
+  <si>
+    <t>منتج من الألبان 25</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 1</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 2</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 3</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 4</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 5</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 6</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 7</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 8</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 9</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 10</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 11</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 12</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 13</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 14</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 15</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 16</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 17</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 18</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 19</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 20</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 21</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 22</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 23</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 24</t>
+  </si>
+  <si>
+    <t>منتج من المخبوزات 25</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 1</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 2</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 3</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 4</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 5</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 6</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 7</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 8</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 9</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 10</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 11</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 12</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 13</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 14</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 15</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 16</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 17</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 18</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 19</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 20</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 21</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 22</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 23</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 24</t>
+  </si>
+  <si>
+    <t>منتج من التوابل والبهارات 25</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 1</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 2</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 3</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 4</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 5</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 6</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 7</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 8</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 9</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 10</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 11</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 12</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 13</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 14</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 15</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 16</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 17</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 18</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 19</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 20</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 21</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 22</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 23</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 24</t>
+  </si>
+  <si>
+    <t>منتج من الحلويات والكاندي 25</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 1</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 2</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 3</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 4</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 5</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 6</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 7</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 8</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 9</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 10</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 11</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 12</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 13</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 14</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 15</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 16</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 17</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 18</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 19</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 20</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 21</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 22</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 23</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 24</t>
+  </si>
+  <si>
+    <t>منتج من المنظفات 25</t>
   </si>
   <si>
     <t>الفواكه والخضار</t>
@@ -737,9 +737,6 @@
   </si>
   <si>
     <t>المنظفات</t>
-  </si>
-  <si>
-    <t>كيلو</t>
   </si>
   <si>
     <t>قطعة</t>
@@ -1149,10 +1146,10 @@
         <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1172,10 +1169,10 @@
         <v>241</v>
       </c>
       <c r="F3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1195,10 +1192,10 @@
         <v>241</v>
       </c>
       <c r="F4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1215,10 +1212,10 @@
         <v>241</v>
       </c>
       <c r="F5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1235,10 +1232,10 @@
         <v>241</v>
       </c>
       <c r="F6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1255,10 +1252,10 @@
         <v>241</v>
       </c>
       <c r="F7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1275,10 +1272,10 @@
         <v>241</v>
       </c>
       <c r="F8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1295,10 +1292,10 @@
         <v>241</v>
       </c>
       <c r="F9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1315,10 +1312,10 @@
         <v>241</v>
       </c>
       <c r="F10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1335,10 +1332,10 @@
         <v>241</v>
       </c>
       <c r="F11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1355,10 +1352,10 @@
         <v>241</v>
       </c>
       <c r="F12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1375,10 +1372,10 @@
         <v>241</v>
       </c>
       <c r="F13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1395,10 +1392,10 @@
         <v>241</v>
       </c>
       <c r="F14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1415,10 +1412,10 @@
         <v>241</v>
       </c>
       <c r="F15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1435,10 +1432,10 @@
         <v>241</v>
       </c>
       <c r="F16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1455,10 +1452,10 @@
         <v>241</v>
       </c>
       <c r="F17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1475,10 +1472,10 @@
         <v>241</v>
       </c>
       <c r="F18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1495,10 +1492,10 @@
         <v>241</v>
       </c>
       <c r="F19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1515,10 +1512,10 @@
         <v>241</v>
       </c>
       <c r="F20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1535,10 +1532,10 @@
         <v>241</v>
       </c>
       <c r="F21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1555,10 +1552,10 @@
         <v>241</v>
       </c>
       <c r="F22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1575,10 +1572,10 @@
         <v>241</v>
       </c>
       <c r="F23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1595,10 +1592,10 @@
         <v>241</v>
       </c>
       <c r="F24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1615,10 +1612,10 @@
         <v>241</v>
       </c>
       <c r="F25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1635,10 +1632,10 @@
         <v>241</v>
       </c>
       <c r="F26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1655,13 +1652,13 @@
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1678,13 +1675,13 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1701,13 +1698,13 @@
         <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G29" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1721,13 +1718,13 @@
         <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F30" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G30" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1741,13 +1738,13 @@
         <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F31" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G31" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1761,13 +1758,13 @@
         <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1781,13 +1778,13 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F33" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1801,13 +1798,13 @@
         <v>36</v>
       </c>
       <c r="E34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F34" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G34" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1821,13 +1818,13 @@
         <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F35" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G35" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1841,13 +1838,13 @@
         <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F36" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G36" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1861,13 +1858,13 @@
         <v>42</v>
       </c>
       <c r="E37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G37" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1881,13 +1878,13 @@
         <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G38" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1901,13 +1898,13 @@
         <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F39" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G39" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1921,13 +1918,13 @@
         <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G40" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1941,13 +1938,13 @@
         <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1961,13 +1958,13 @@
         <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F42" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1981,13 +1978,13 @@
         <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2001,13 +1998,13 @@
         <v>56</v>
       </c>
       <c r="E44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F44" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2021,13 +2018,13 @@
         <v>58</v>
       </c>
       <c r="E45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F45" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2041,13 +2038,13 @@
         <v>60</v>
       </c>
       <c r="E46" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F46" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G46" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2061,13 +2058,13 @@
         <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F47" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2081,13 +2078,13 @@
         <v>64</v>
       </c>
       <c r="E48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G48" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2101,13 +2098,13 @@
         <v>66</v>
       </c>
       <c r="E49" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F49" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G49" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2121,13 +2118,13 @@
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F50" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G50" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2141,13 +2138,13 @@
         <v>70</v>
       </c>
       <c r="E51" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G51" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2164,13 +2161,13 @@
         <v>17</v>
       </c>
       <c r="E52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F52" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G52" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2187,13 +2184,13 @@
         <v>19</v>
       </c>
       <c r="E53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F53" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G53" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2210,13 +2207,13 @@
         <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F54" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G54" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2230,13 +2227,13 @@
         <v>28</v>
       </c>
       <c r="E55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F55" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G55" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2250,13 +2247,13 @@
         <v>30</v>
       </c>
       <c r="E56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2270,13 +2267,13 @@
         <v>32</v>
       </c>
       <c r="E57" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F57" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G57" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2290,13 +2287,13 @@
         <v>34</v>
       </c>
       <c r="E58" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F58" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G58" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2310,13 +2307,13 @@
         <v>36</v>
       </c>
       <c r="E59" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F59" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G59" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2330,13 +2327,13 @@
         <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F60" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G60" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2350,13 +2347,13 @@
         <v>40</v>
       </c>
       <c r="E61" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F61" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G61" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2370,13 +2367,13 @@
         <v>42</v>
       </c>
       <c r="E62" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F62" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G62" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2390,13 +2387,13 @@
         <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F63" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G63" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2410,13 +2407,13 @@
         <v>46</v>
       </c>
       <c r="E64" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G64" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2430,13 +2427,13 @@
         <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G65" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2450,13 +2447,13 @@
         <v>50</v>
       </c>
       <c r="E66" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F66" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G66" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2470,13 +2467,13 @@
         <v>52</v>
       </c>
       <c r="E67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G67" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2490,13 +2487,13 @@
         <v>54</v>
       </c>
       <c r="E68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F68" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G68" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2510,13 +2507,13 @@
         <v>56</v>
       </c>
       <c r="E69" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F69" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G69" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2530,13 +2527,13 @@
         <v>58</v>
       </c>
       <c r="E70" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2550,13 +2547,13 @@
         <v>60</v>
       </c>
       <c r="E71" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F71" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2570,13 +2567,13 @@
         <v>62</v>
       </c>
       <c r="E72" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F72" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G72" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2590,13 +2587,13 @@
         <v>64</v>
       </c>
       <c r="E73" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F73" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G73" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2610,13 +2607,13 @@
         <v>66</v>
       </c>
       <c r="E74" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2630,13 +2627,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F75" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G75" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2650,13 +2647,13 @@
         <v>70</v>
       </c>
       <c r="E76" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F76" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G76" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2676,10 +2673,10 @@
         <v>241</v>
       </c>
       <c r="F77" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2699,10 +2696,10 @@
         <v>241</v>
       </c>
       <c r="F78" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G78" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2722,10 +2719,10 @@
         <v>241</v>
       </c>
       <c r="F79" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G79" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2742,10 +2739,10 @@
         <v>241</v>
       </c>
       <c r="F80" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G80" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2762,10 +2759,10 @@
         <v>241</v>
       </c>
       <c r="F81" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G81" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2782,10 +2779,10 @@
         <v>241</v>
       </c>
       <c r="F82" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G82" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2802,10 +2799,10 @@
         <v>241</v>
       </c>
       <c r="F83" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G83" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2822,10 +2819,10 @@
         <v>241</v>
       </c>
       <c r="F84" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G84" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2842,10 +2839,10 @@
         <v>241</v>
       </c>
       <c r="F85" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G85" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2862,10 +2859,10 @@
         <v>241</v>
       </c>
       <c r="F86" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G86" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2882,10 +2879,10 @@
         <v>241</v>
       </c>
       <c r="F87" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G87" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2902,10 +2899,10 @@
         <v>241</v>
       </c>
       <c r="F88" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G88" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2922,10 +2919,10 @@
         <v>241</v>
       </c>
       <c r="F89" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G89" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2942,10 +2939,10 @@
         <v>241</v>
       </c>
       <c r="F90" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G90" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2962,10 +2959,10 @@
         <v>241</v>
       </c>
       <c r="F91" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G91" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2982,10 +2979,10 @@
         <v>241</v>
       </c>
       <c r="F92" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G92" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3002,10 +2999,10 @@
         <v>241</v>
       </c>
       <c r="F93" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G93" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3022,10 +3019,10 @@
         <v>241</v>
       </c>
       <c r="F94" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G94" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3042,10 +3039,10 @@
         <v>241</v>
       </c>
       <c r="F95" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G95" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3062,10 +3059,10 @@
         <v>241</v>
       </c>
       <c r="F96" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G96" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3082,10 +3079,10 @@
         <v>241</v>
       </c>
       <c r="F97" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G97" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3102,10 +3099,10 @@
         <v>241</v>
       </c>
       <c r="F98" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G98" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3122,10 +3119,10 @@
         <v>241</v>
       </c>
       <c r="F99" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G99" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3142,10 +3139,10 @@
         <v>241</v>
       </c>
       <c r="F100" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G100" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3162,10 +3159,10 @@
         <v>241</v>
       </c>
       <c r="F101" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G101" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3185,10 +3182,10 @@
         <v>241</v>
       </c>
       <c r="F102" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G102" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3208,10 +3205,10 @@
         <v>241</v>
       </c>
       <c r="F103" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G103" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3231,10 +3228,10 @@
         <v>241</v>
       </c>
       <c r="F104" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G104" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3251,10 +3248,10 @@
         <v>241</v>
       </c>
       <c r="F105" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G105" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3271,10 +3268,10 @@
         <v>241</v>
       </c>
       <c r="F106" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G106" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3291,10 +3288,10 @@
         <v>241</v>
       </c>
       <c r="F107" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G107" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3311,10 +3308,10 @@
         <v>241</v>
       </c>
       <c r="F108" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G108" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3331,10 +3328,10 @@
         <v>241</v>
       </c>
       <c r="F109" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G109" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3351,10 +3348,10 @@
         <v>241</v>
       </c>
       <c r="F110" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G110" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3371,10 +3368,10 @@
         <v>241</v>
       </c>
       <c r="F111" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G111" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3391,10 +3388,10 @@
         <v>241</v>
       </c>
       <c r="F112" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G112" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3411,10 +3408,10 @@
         <v>241</v>
       </c>
       <c r="F113" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G113" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3431,10 +3428,10 @@
         <v>241</v>
       </c>
       <c r="F114" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G114" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3451,10 +3448,10 @@
         <v>241</v>
       </c>
       <c r="F115" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G115" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3471,10 +3468,10 @@
         <v>241</v>
       </c>
       <c r="F116" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G116" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3491,10 +3488,10 @@
         <v>241</v>
       </c>
       <c r="F117" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G117" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3511,10 +3508,10 @@
         <v>241</v>
       </c>
       <c r="F118" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G118" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3531,10 +3528,10 @@
         <v>241</v>
       </c>
       <c r="F119" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G119" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3551,10 +3548,10 @@
         <v>241</v>
       </c>
       <c r="F120" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G120" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3571,10 +3568,10 @@
         <v>241</v>
       </c>
       <c r="F121" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G121" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3591,10 +3588,10 @@
         <v>241</v>
       </c>
       <c r="F122" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G122" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3611,10 +3608,10 @@
         <v>241</v>
       </c>
       <c r="F123" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G123" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3631,10 +3628,10 @@
         <v>241</v>
       </c>
       <c r="F124" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G124" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3651,10 +3648,10 @@
         <v>241</v>
       </c>
       <c r="F125" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G125" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3671,10 +3668,10 @@
         <v>241</v>
       </c>
       <c r="F126" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G126" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -3691,13 +3688,13 @@
         <v>17</v>
       </c>
       <c r="E127" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F127" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G127" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -3714,13 +3711,13 @@
         <v>19</v>
       </c>
       <c r="E128" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F128" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G128" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -3737,13 +3734,13 @@
         <v>21</v>
       </c>
       <c r="E129" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F129" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G129" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3757,13 +3754,13 @@
         <v>28</v>
       </c>
       <c r="E130" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F130" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G130" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -3777,13 +3774,13 @@
         <v>30</v>
       </c>
       <c r="E131" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F131" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G131" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -3797,13 +3794,13 @@
         <v>32</v>
       </c>
       <c r="E132" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F132" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G132" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3817,13 +3814,13 @@
         <v>34</v>
       </c>
       <c r="E133" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F133" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G133" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -3837,13 +3834,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F134" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G134" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -3857,13 +3854,13 @@
         <v>38</v>
       </c>
       <c r="E135" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F135" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G135" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -3877,13 +3874,13 @@
         <v>40</v>
       </c>
       <c r="E136" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F136" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G136" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -3897,13 +3894,13 @@
         <v>42</v>
       </c>
       <c r="E137" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F137" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G137" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -3917,13 +3914,13 @@
         <v>44</v>
       </c>
       <c r="E138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F138" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G138" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -3937,13 +3934,13 @@
         <v>46</v>
       </c>
       <c r="E139" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F139" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G139" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -3957,13 +3954,13 @@
         <v>48</v>
       </c>
       <c r="E140" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F140" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G140" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -3977,13 +3974,13 @@
         <v>50</v>
       </c>
       <c r="E141" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F141" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G141" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -3997,13 +3994,13 @@
         <v>52</v>
       </c>
       <c r="E142" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G142" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4017,13 +4014,13 @@
         <v>54</v>
       </c>
       <c r="E143" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F143" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G143" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4037,13 +4034,13 @@
         <v>56</v>
       </c>
       <c r="E144" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F144" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G144" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4057,13 +4054,13 @@
         <v>58</v>
       </c>
       <c r="E145" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F145" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G145" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4077,13 +4074,13 @@
         <v>60</v>
       </c>
       <c r="E146" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F146" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G146" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4097,13 +4094,13 @@
         <v>62</v>
       </c>
       <c r="E147" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F147" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G147" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4117,13 +4114,13 @@
         <v>64</v>
       </c>
       <c r="E148" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F148" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G148" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4137,13 +4134,13 @@
         <v>66</v>
       </c>
       <c r="E149" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F149" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G149" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4157,13 +4154,13 @@
         <v>68</v>
       </c>
       <c r="E150" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F150" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G150" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4177,13 +4174,13 @@
         <v>70</v>
       </c>
       <c r="E151" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F151" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G151" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4203,10 +4200,10 @@
         <v>241</v>
       </c>
       <c r="F152" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G152" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4226,10 +4223,10 @@
         <v>241</v>
       </c>
       <c r="F153" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G153" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4249,10 +4246,10 @@
         <v>241</v>
       </c>
       <c r="F154" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G154" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4269,10 +4266,10 @@
         <v>241</v>
       </c>
       <c r="F155" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G155" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4289,10 +4286,10 @@
         <v>241</v>
       </c>
       <c r="F156" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G156" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4309,10 +4306,10 @@
         <v>241</v>
       </c>
       <c r="F157" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G157" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4329,10 +4326,10 @@
         <v>241</v>
       </c>
       <c r="F158" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G158" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4349,10 +4346,10 @@
         <v>241</v>
       </c>
       <c r="F159" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G159" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4369,10 +4366,10 @@
         <v>241</v>
       </c>
       <c r="F160" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G160" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4389,10 +4386,10 @@
         <v>241</v>
       </c>
       <c r="F161" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G161" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4409,10 +4406,10 @@
         <v>241</v>
       </c>
       <c r="F162" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G162" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4429,10 +4426,10 @@
         <v>241</v>
       </c>
       <c r="F163" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G163" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4449,10 +4446,10 @@
         <v>241</v>
       </c>
       <c r="F164" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G164" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4469,10 +4466,10 @@
         <v>241</v>
       </c>
       <c r="F165" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G165" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4489,10 +4486,10 @@
         <v>241</v>
       </c>
       <c r="F166" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G166" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4509,10 +4506,10 @@
         <v>241</v>
       </c>
       <c r="F167" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G167" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4529,10 +4526,10 @@
         <v>241</v>
       </c>
       <c r="F168" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G168" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4549,10 +4546,10 @@
         <v>241</v>
       </c>
       <c r="F169" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G169" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4569,10 +4566,10 @@
         <v>241</v>
       </c>
       <c r="F170" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G170" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4589,10 +4586,10 @@
         <v>241</v>
       </c>
       <c r="F171" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G171" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4609,10 +4606,10 @@
         <v>241</v>
       </c>
       <c r="F172" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G172" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4629,10 +4626,10 @@
         <v>241</v>
       </c>
       <c r="F173" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G173" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4649,10 +4646,10 @@
         <v>241</v>
       </c>
       <c r="F174" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G174" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4669,10 +4666,10 @@
         <v>241</v>
       </c>
       <c r="F175" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G175" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4689,10 +4686,10 @@
         <v>241</v>
       </c>
       <c r="F176" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G176" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -4709,13 +4706,13 @@
         <v>17</v>
       </c>
       <c r="E177" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F177" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G177" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -4732,13 +4729,13 @@
         <v>19</v>
       </c>
       <c r="E178" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F178" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G178" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -4755,13 +4752,13 @@
         <v>21</v>
       </c>
       <c r="E179" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F179" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G179" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -4775,13 +4772,13 @@
         <v>28</v>
       </c>
       <c r="E180" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F180" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G180" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -4795,13 +4792,13 @@
         <v>30</v>
       </c>
       <c r="E181" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F181" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G181" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -4815,13 +4812,13 @@
         <v>32</v>
       </c>
       <c r="E182" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F182" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G182" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -4835,13 +4832,13 @@
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F183" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G183" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -4855,13 +4852,13 @@
         <v>36</v>
       </c>
       <c r="E184" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F184" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G184" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -4875,13 +4872,13 @@
         <v>38</v>
       </c>
       <c r="E185" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F185" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G185" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -4895,13 +4892,13 @@
         <v>40</v>
       </c>
       <c r="E186" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F186" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G186" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -4915,13 +4912,13 @@
         <v>42</v>
       </c>
       <c r="E187" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F187" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G187" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -4935,13 +4932,13 @@
         <v>44</v>
       </c>
       <c r="E188" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F188" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G188" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -4955,13 +4952,13 @@
         <v>46</v>
       </c>
       <c r="E189" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F189" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -4975,13 +4972,13 @@
         <v>48</v>
       </c>
       <c r="E190" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F190" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G190" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -4995,13 +4992,13 @@
         <v>50</v>
       </c>
       <c r="E191" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F191" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G191" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5015,13 +5012,13 @@
         <v>52</v>
       </c>
       <c r="E192" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F192" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G192" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5035,13 +5032,13 @@
         <v>54</v>
       </c>
       <c r="E193" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F193" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G193" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5055,13 +5052,13 @@
         <v>56</v>
       </c>
       <c r="E194" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F194" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G194" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5075,13 +5072,13 @@
         <v>58</v>
       </c>
       <c r="E195" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F195" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G195" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5095,13 +5092,13 @@
         <v>60</v>
       </c>
       <c r="E196" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F196" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G196" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5115,13 +5112,13 @@
         <v>62</v>
       </c>
       <c r="E197" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F197" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G197" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5135,13 +5132,13 @@
         <v>64</v>
       </c>
       <c r="E198" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F198" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G198" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5155,13 +5152,13 @@
         <v>66</v>
       </c>
       <c r="E199" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F199" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G199" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5175,13 +5172,13 @@
         <v>68</v>
       </c>
       <c r="E200" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F200" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G200" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5195,13 +5192,13 @@
         <v>70</v>
       </c>
       <c r="E201" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F201" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G201" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5218,13 +5215,13 @@
         <v>17</v>
       </c>
       <c r="E202" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F202" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G202" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5241,13 +5238,13 @@
         <v>19</v>
       </c>
       <c r="E203" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F203" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G203" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5264,13 +5261,13 @@
         <v>21</v>
       </c>
       <c r="E204" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F204" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G204" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5284,13 +5281,13 @@
         <v>28</v>
       </c>
       <c r="E205" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F205" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G205" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5304,13 +5301,13 @@
         <v>30</v>
       </c>
       <c r="E206" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F206" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G206" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5324,13 +5321,13 @@
         <v>32</v>
       </c>
       <c r="E207" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F207" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G207" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5344,13 +5341,13 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F208" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G208" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5364,13 +5361,13 @@
         <v>36</v>
       </c>
       <c r="E209" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F209" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G209" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5384,13 +5381,13 @@
         <v>38</v>
       </c>
       <c r="E210" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F210" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G210" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5404,13 +5401,13 @@
         <v>40</v>
       </c>
       <c r="E211" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F211" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G211" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5424,13 +5421,13 @@
         <v>42</v>
       </c>
       <c r="E212" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F212" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G212" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5444,13 +5441,13 @@
         <v>44</v>
       </c>
       <c r="E213" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F213" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G213" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5464,13 +5461,13 @@
         <v>46</v>
       </c>
       <c r="E214" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F214" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G214" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5484,13 +5481,13 @@
         <v>48</v>
       </c>
       <c r="E215" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F215" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G215" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5504,13 +5501,13 @@
         <v>50</v>
       </c>
       <c r="E216" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F216" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G216" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5524,13 +5521,13 @@
         <v>52</v>
       </c>
       <c r="E217" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F217" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G217" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5544,13 +5541,13 @@
         <v>54</v>
       </c>
       <c r="E218" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F218" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G218" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5564,13 +5561,13 @@
         <v>56</v>
       </c>
       <c r="E219" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F219" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G219" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5584,13 +5581,13 @@
         <v>58</v>
       </c>
       <c r="E220" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F220" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G220" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -5604,13 +5601,13 @@
         <v>60</v>
       </c>
       <c r="E221" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F221" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G221" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -5624,13 +5621,13 @@
         <v>62</v>
       </c>
       <c r="E222" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F222" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G222" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -5644,13 +5641,13 @@
         <v>64</v>
       </c>
       <c r="E223" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F223" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G223" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -5664,13 +5661,13 @@
         <v>66</v>
       </c>
       <c r="E224" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F224" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G224" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5684,13 +5681,13 @@
         <v>68</v>
       </c>
       <c r="E225" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F225" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G225" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5704,13 +5701,13 @@
         <v>70</v>
       </c>
       <c r="E226" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F226" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G226" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="245">
   <si>
     <t>الاسم</t>
   </si>
@@ -37,679 +37,679 @@
     <t>متوفر</t>
   </si>
   <si>
-    <t>منتج من الفواكه والخضار 1</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 2</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 3</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 4</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 5</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 6</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 7</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 8</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 9</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 10</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 11</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 12</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 13</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 14</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 15</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 16</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 17</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 18</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 19</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 20</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 21</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 22</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 23</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 24</t>
-  </si>
-  <si>
-    <t>منتج من الفواكه والخضار 25</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 1</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 2</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 3</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 4</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 5</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 6</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 7</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 8</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 9</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 10</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 11</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 12</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 13</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 14</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 15</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 16</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 17</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 18</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 19</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 20</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 21</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 22</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 23</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 24</t>
-  </si>
-  <si>
-    <t>منتج من التسالي والمكسرات 25</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 1</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 2</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 3</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 4</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 5</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 6</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 7</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 8</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 9</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 10</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 11</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 12</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 13</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 14</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 15</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 16</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 17</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 18</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 19</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 20</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 21</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 22</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 23</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 24</t>
-  </si>
-  <si>
-    <t>منتج من المشروبات 25</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 1</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 2</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 3</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 4</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 5</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 6</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 7</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 8</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 9</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 10</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 11</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 12</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 13</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 14</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 15</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 16</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 17</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 18</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 19</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 20</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 21</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 22</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 23</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 24</t>
-  </si>
-  <si>
-    <t>منتج من البقالة 25</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 1</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 2</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 3</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 4</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 5</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 6</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 7</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 8</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 9</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 10</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 11</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 12</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 13</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 14</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 15</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 16</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 17</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 18</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 19</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 20</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 21</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 22</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 23</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 24</t>
-  </si>
-  <si>
-    <t>منتج من الألبان 25</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 1</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 2</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 3</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 4</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 5</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 6</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 7</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 8</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 9</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 10</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 11</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 12</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 13</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 14</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 15</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 16</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 17</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 18</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 19</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 20</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 21</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 22</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 23</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 24</t>
-  </si>
-  <si>
-    <t>منتج من المخبوزات 25</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 1</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 2</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 3</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 4</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 5</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 6</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 7</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 8</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 9</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 10</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 11</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 12</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 13</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 14</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 15</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 16</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 17</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 18</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 19</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 20</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 21</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 22</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 23</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 24</t>
-  </si>
-  <si>
-    <t>منتج من التوابل والبهارات 25</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 1</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 2</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 3</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 4</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 5</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 6</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 7</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 8</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 9</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 10</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 11</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 12</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 13</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 14</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 15</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 16</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 17</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 18</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 19</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 20</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 21</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 22</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 23</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 24</t>
-  </si>
-  <si>
-    <t>منتج من الحلويات والكاندي 25</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 1</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 2</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 3</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 4</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 5</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 6</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 7</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 8</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 9</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 10</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 11</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 12</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 13</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 14</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 15</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 16</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 17</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 18</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 19</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 20</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 21</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 22</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 23</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 24</t>
-  </si>
-  <si>
-    <t>منتج من المنظفات 25</t>
+    <t>طماطم بلدي</t>
+  </si>
+  <si>
+    <t>خيار طازج</t>
+  </si>
+  <si>
+    <t>بطاطس تقلية</t>
+  </si>
+  <si>
+    <t>بصل أحمر</t>
+  </si>
+  <si>
+    <t>جزر طازج</t>
+  </si>
+  <si>
+    <t>فلفل رومي</t>
+  </si>
+  <si>
+    <t>باذنجان رومي</t>
+  </si>
+  <si>
+    <t>ليمون أصفر</t>
+  </si>
+  <si>
+    <t>تفاح أمريكي</t>
+  </si>
+  <si>
+    <t>موز مستورد</t>
+  </si>
+  <si>
+    <t>برتقال أبو صير</t>
+  </si>
+  <si>
+    <t>فراولة طازجة</t>
+  </si>
+  <si>
+    <t>مانجو زبدية</t>
+  </si>
+  <si>
+    <t>خوخ بلدي</t>
+  </si>
+  <si>
+    <t>عنب مرسلي</t>
+  </si>
+  <si>
+    <t>بطيخ أحمر</t>
+  </si>
+  <si>
+    <t>كنتالوب</t>
+  </si>
+  <si>
+    <t>أنناس</t>
+  </si>
+  <si>
+    <t>كيوي</t>
+  </si>
+  <si>
+    <t>بلح زغلول</t>
+  </si>
+  <si>
+    <t>كرنب أحمر</t>
+  </si>
+  <si>
+    <t>خس كابوتشا</t>
+  </si>
+  <si>
+    <t>بقدونس</t>
+  </si>
+  <si>
+    <t>كزبرة</t>
+  </si>
+  <si>
+    <t>شبت</t>
+  </si>
+  <si>
+    <t>لب محمص</t>
+  </si>
+  <si>
+    <t>لب سوبر</t>
+  </si>
+  <si>
+    <t>لب أبيض</t>
+  </si>
+  <si>
+    <t>سوداني مقشر</t>
+  </si>
+  <si>
+    <t>مكسرات مشكلة</t>
+  </si>
+  <si>
+    <t>فستق محمص</t>
+  </si>
+  <si>
+    <t>بندق محمص</t>
+  </si>
+  <si>
+    <t>كاجو محمص</t>
+  </si>
+  <si>
+    <t>لوز محمص</t>
+  </si>
+  <si>
+    <t>عين جمل</t>
+  </si>
+  <si>
+    <t>مقرمشات جبنة</t>
+  </si>
+  <si>
+    <t>مقرمشات حار</t>
+  </si>
+  <si>
+    <t>ذرة تبشير</t>
+  </si>
+  <si>
+    <t>فسدوق</t>
+  </si>
+  <si>
+    <t>مقرمشات مكسيكية</t>
+  </si>
+  <si>
+    <t>فول سوداني بالشوكولاتة</t>
+  </si>
+  <si>
+    <t>زبيب جولد</t>
+  </si>
+  <si>
+    <t>قراصيا مجففة</t>
+  </si>
+  <si>
+    <t>مشمشية</t>
+  </si>
+  <si>
+    <t>تين مجفف</t>
+  </si>
+  <si>
+    <t>تمر هندي</t>
+  </si>
+  <si>
+    <t>مقرمشات بالملح</t>
+  </si>
+  <si>
+    <t>لب سوري</t>
+  </si>
+  <si>
+    <t>لب تركي</t>
+  </si>
+  <si>
+    <t>مكسرات صيني</t>
+  </si>
+  <si>
+    <t>شاي العروسة</t>
+  </si>
+  <si>
+    <t>شاي ليبتون</t>
+  </si>
+  <si>
+    <t>نسكافيه كلاسيك</t>
+  </si>
+  <si>
+    <t>قهوة تركي مظبوط</t>
+  </si>
+  <si>
+    <t>عصير مانجو جهينة</t>
+  </si>
+  <si>
+    <t>عصير جوافة جهينة</t>
+  </si>
+  <si>
+    <t>مياه معدنية نستله</t>
+  </si>
+  <si>
+    <t>مياه بريل</t>
+  </si>
+  <si>
+    <t>بيبسي كانز</t>
+  </si>
+  <si>
+    <t>كوكا كولا كانز</t>
+  </si>
+  <si>
+    <t>سفن أب</t>
+  </si>
+  <si>
+    <t>ميرندا تفاح</t>
+  </si>
+  <si>
+    <t>شاي سبز</t>
+  </si>
+  <si>
+    <t>ينسون كابتن</t>
+  </si>
+  <si>
+    <t>نعناع هاني</t>
+  </si>
+  <si>
+    <t>كركديه أسواني</t>
+  </si>
+  <si>
+    <t>حلبة حصى</t>
+  </si>
+  <si>
+    <t>قهوة إسبرسو</t>
+  </si>
+  <si>
+    <t>مشروب طاقة ريد بول</t>
+  </si>
+  <si>
+    <t>عصير برتقال طبيعي</t>
+  </si>
+  <si>
+    <t>شاي مثلج</t>
+  </si>
+  <si>
+    <t>قهوة بالبندق</t>
+  </si>
+  <si>
+    <t>شاي أخضر بالياسمين</t>
+  </si>
+  <si>
+    <t>سحلب تركي</t>
+  </si>
+  <si>
+    <t>مشروب شوكولاتة ساخنة</t>
+  </si>
+  <si>
+    <t>أرز المصري</t>
+  </si>
+  <si>
+    <t>مكرونة الملكة</t>
+  </si>
+  <si>
+    <t>مكرونة الضحكة</t>
+  </si>
+  <si>
+    <t>زيت عافية ذرة</t>
+  </si>
+  <si>
+    <t>زيت سلايت عباد</t>
+  </si>
+  <si>
+    <t>سمنة روابي</t>
+  </si>
+  <si>
+    <t>عدس أصفر</t>
+  </si>
+  <si>
+    <t>عدس بجبة</t>
+  </si>
+  <si>
+    <t>فول تدميس</t>
+  </si>
+  <si>
+    <t>لوبيا خشک</t>
+  </si>
+  <si>
+    <t>فاصوليا وائت</t>
+  </si>
+  <si>
+    <t>ملح طعام</t>
+  </si>
+  <si>
+    <t>صلصة طماطم</t>
+  </si>
+  <si>
+    <t>تونة إيطالي</t>
+  </si>
+  <si>
+    <t>مرقة دجاج ماجي</t>
+  </si>
+  <si>
+    <t>خل عود</t>
+  </si>
+  <si>
+    <t>دقيق فاخر</t>
+  </si>
+  <si>
+    <t>نشا ذرة</t>
+  </si>
+  <si>
+    <t>برغل دقيق</t>
+  </si>
+  <si>
+    <t>فريك دقيق</t>
+  </si>
+  <si>
+    <t>حمص شام</t>
+  </si>
+  <si>
+    <t>ترمس حلو</t>
+  </si>
+  <si>
+    <t>مياه غازية</t>
+  </si>
+  <si>
+    <t>شعرية المطبخ</t>
+  </si>
+  <si>
+    <t>لسان عصفور</t>
+  </si>
+  <si>
+    <t>لبن جهينة طبيعي</t>
+  </si>
+  <si>
+    <t>لبن المراعي</t>
+  </si>
+  <si>
+    <t>جبنة فيتا طرية</t>
+  </si>
+  <si>
+    <t>جبنة رومي أقدم</t>
+  </si>
+  <si>
+    <t>جبنة شيدر مستورد</t>
+  </si>
+  <si>
+    <t>قشطة بلدي</t>
+  </si>
+  <si>
+    <t>زبادي المراعي</t>
+  </si>
+  <si>
+    <t>زبادي دانيت</t>
+  </si>
+  <si>
+    <t>زبدة نيوزلندي</t>
+  </si>
+  <si>
+    <t>موتزاريلا مبشورة</t>
+  </si>
+  <si>
+    <t>جبنة إسطنبولي</t>
+  </si>
+  <si>
+    <t>جبنة براميلي</t>
+  </si>
+  <si>
+    <t>جبنة مثلثات</t>
+  </si>
+  <si>
+    <t>لبن رايب</t>
+  </si>
+  <si>
+    <t>كريمة طهي</t>
+  </si>
+  <si>
+    <t>كريمة خفق</t>
+  </si>
+  <si>
+    <t>جبنة قريش</t>
+  </si>
+  <si>
+    <t>حليب مكثف محلى</t>
+  </si>
+  <si>
+    <t>زبادي فواكه</t>
+  </si>
+  <si>
+    <t>لبن جوز الهند</t>
+  </si>
+  <si>
+    <t>جبنة بلاستيك</t>
+  </si>
+  <si>
+    <t>شيدر مدخن</t>
+  </si>
+  <si>
+    <t>جبنة حلوم</t>
+  </si>
+  <si>
+    <t>حليب بودرة</t>
+  </si>
+  <si>
+    <t>لبن ماعز</t>
+  </si>
+  <si>
+    <t>عيش بلدي طازج</t>
+  </si>
+  <si>
+    <t>عيش فينو</t>
+  </si>
+  <si>
+    <t>قرص بالصكوك</t>
+  </si>
+  <si>
+    <t>قرص عجوة</t>
+  </si>
+  <si>
+    <t>باتيه جبنة</t>
+  </si>
+  <si>
+    <t>باتيه شوكولاتة</t>
+  </si>
+  <si>
+    <t>كرواسون زبدة</t>
+  </si>
+  <si>
+    <t>كرواسون شوكولاتة</t>
+  </si>
+  <si>
+    <t>توست بر</t>
+  </si>
+  <si>
+    <t>توست أبيض</t>
+  </si>
+  <si>
+    <t>شابورة دايت</t>
+  </si>
+  <si>
+    <t>بقسماط بالسمسم</t>
+  </si>
+  <si>
+    <t>كيك شوكولاتة</t>
+  </si>
+  <si>
+    <t>كب كيك</t>
+  </si>
+  <si>
+    <t>تارت فراولة</t>
+  </si>
+  <si>
+    <t>بسكويت سادة</t>
+  </si>
+  <si>
+    <t>بسكويت بالشوكولاتة</t>
+  </si>
+  <si>
+    <t>فطير مشلتت</t>
+  </si>
+  <si>
+    <t>عيش سوري</t>
+  </si>
+  <si>
+    <t>عيش شامي</t>
+  </si>
+  <si>
+    <t>بسكويت دايجستف</t>
+  </si>
+  <si>
+    <t>قرص سادة</t>
+  </si>
+  <si>
+    <t>كوكيز بالشوكولاتة</t>
+  </si>
+  <si>
+    <t>خبز برجر</t>
+  </si>
+  <si>
+    <t>خبز توست أسمر</t>
+  </si>
+  <si>
+    <t>فلفل أسود مطحون</t>
+  </si>
+  <si>
+    <t>كمون بلدي</t>
+  </si>
+  <si>
+    <t>كزبرة خشکة</t>
+  </si>
+  <si>
+    <t>بهارات مشكلة</t>
+  </si>
+  <si>
+    <t>قرفة مطحونة</t>
+  </si>
+  <si>
+    <t>هيل (حبهان)</t>
+  </si>
+  <si>
+    <t>قرنفل صحيح</t>
+  </si>
+  <si>
+    <t>كركم آصلي</t>
+  </si>
+  <si>
+    <t>كاري هندي</t>
+  </si>
+  <si>
+    <t>بابريكا سموكي</t>
+  </si>
+  <si>
+    <t>زعتر بري</t>
+  </si>
+  <si>
+    <t>روزماري</t>
+  </si>
+  <si>
+    <t>ورق لورا</t>
+  </si>
+  <si>
+    <t>ملح ليمون</t>
+  </si>
+  <si>
+    <t>ثوم بودرة</t>
+  </si>
+  <si>
+    <t>بصل بودرة</t>
+  </si>
+  <si>
+    <t>شطّة حارة</t>
+  </si>
+  <si>
+    <t>جنزبيل مطحون</t>
+  </si>
+  <si>
+    <t>سماق تركي</t>
+  </si>
+  <si>
+    <t>جوزة الطيب</t>
+  </si>
+  <si>
+    <t>بهارات لحمة</t>
+  </si>
+  <si>
+    <t>بهارات فراخ</t>
+  </si>
+  <si>
+    <t>زعفران</t>
+  </si>
+  <si>
+    <t>كمون حاص</t>
+  </si>
+  <si>
+    <t>فلفل أبيض</t>
+  </si>
+  <si>
+    <t>شوكولاتة جالاكسي</t>
+  </si>
+  <si>
+    <t>شوكولاتة كادبوري</t>
+  </si>
+  <si>
+    <t>شوكولاتة بيك اب</t>
+  </si>
+  <si>
+    <t>بسكويت أوريو</t>
+  </si>
+  <si>
+    <t>شوكولاتة مارس</t>
+  </si>
+  <si>
+    <t>شوكولاتة سنيكرز</t>
+  </si>
+  <si>
+    <t>جيلي فواكه</t>
+  </si>
+  <si>
+    <t>مصاصة كاندي</t>
+  </si>
+  <si>
+    <t>مللبس لوز</t>
+  </si>
+  <si>
+    <t>حلاوة طحينية</t>
+  </si>
+  <si>
+    <t>شوكولاتة كيت كات</t>
+  </si>
+  <si>
+    <t>بونبوني نعناع</t>
+  </si>
+  <si>
+    <t>علوة مستكة</t>
+  </si>
+  <si>
+    <t>شوكولاتة فريرو روشيه</t>
+  </si>
+  <si>
+    <t>حلوى جيلي كولا</t>
+  </si>
+  <si>
+    <t>شوكولاتة باونتي</t>
+  </si>
+  <si>
+    <t>توفي بقر</t>
+  </si>
+  <si>
+    <t>كراميل</t>
+  </si>
+  <si>
+    <t>شوكولاتة بالبندق</t>
+  </si>
+  <si>
+    <t>بسكويت لوتا</t>
+  </si>
+  <si>
+    <t>شوكولاتة ديربي</t>
+  </si>
+  <si>
+    <t>شوكولاتة بيمبو</t>
+  </si>
+  <si>
+    <t>بسكويت تومي</t>
+  </si>
+  <si>
+    <t>حلوى غزل البنات</t>
+  </si>
+  <si>
+    <t>شوكولاتة داكنة</t>
+  </si>
+  <si>
+    <t>مسحوق أريال أوتوماتيك</t>
+  </si>
+  <si>
+    <t>برسيل جل</t>
+  </si>
+  <si>
+    <t>دواني منعم ملابس</t>
+  </si>
+  <si>
+    <t>سائل غسيل أطباق فيري</t>
+  </si>
+  <si>
+    <t>كلوركس ابيض</t>
+  </si>
+  <si>
+    <t>كلوركس ألوان</t>
+  </si>
+  <si>
+    <t>ديتول مطهر</t>
+  </si>
+  <si>
+    <t>صابون بانيو</t>
+  </si>
+  <si>
+    <t>معطر جو فبريز</t>
+  </si>
+  <si>
+    <t>مناديل فاين</t>
+  </si>
+  <si>
+    <t>بكر تواليت سانيتا</t>
+  </si>
+  <si>
+    <t>اسفنج مواعين</t>
+  </si>
+  <si>
+    <t>فلاش تنظيف الحمامات</t>
+  </si>
+  <si>
+    <t>مسحوق تايد</t>
+  </si>
+  <si>
+    <t>جل استحمام شاور</t>
+  </si>
+  <si>
+    <t>شامبو صانسيلك</t>
+  </si>
+  <si>
+    <t>معجون اسنان كولجيت</t>
+  </si>
+  <si>
+    <t>فرشاة اسنان</t>
+  </si>
+  <si>
+    <t>مبيد حشرات ريد</t>
+  </si>
+  <si>
+    <t>أكياس قمامة</t>
+  </si>
+  <si>
+    <t>مسحوق برسيل اليدوي</t>
+  </si>
+  <si>
+    <t>صابون سائل لليدين</t>
+  </si>
+  <si>
+    <t>منظف زجاج</t>
+  </si>
+  <si>
+    <t>كلور فلاش</t>
+  </si>
+  <si>
+    <t>معطر تفصيل</t>
   </si>
   <si>
     <t>الفواكه والخضار</t>
@@ -737,6 +737,9 @@
   </si>
   <si>
     <t>المنظفات</t>
+  </si>
+  <si>
+    <t>كيلو</t>
   </si>
   <si>
     <t>قطعة</t>
@@ -1146,10 +1149,10 @@
         <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1169,10 +1172,10 @@
         <v>241</v>
       </c>
       <c r="F3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1192,10 +1195,10 @@
         <v>241</v>
       </c>
       <c r="F4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1212,10 +1215,10 @@
         <v>241</v>
       </c>
       <c r="F5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1232,10 +1235,10 @@
         <v>241</v>
       </c>
       <c r="F6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1252,10 +1255,10 @@
         <v>241</v>
       </c>
       <c r="F7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1272,10 +1275,10 @@
         <v>241</v>
       </c>
       <c r="F8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1292,10 +1295,10 @@
         <v>241</v>
       </c>
       <c r="F9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1312,10 +1315,10 @@
         <v>241</v>
       </c>
       <c r="F10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1332,10 +1335,10 @@
         <v>241</v>
       </c>
       <c r="F11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1352,10 +1355,10 @@
         <v>241</v>
       </c>
       <c r="F12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1372,10 +1375,10 @@
         <v>241</v>
       </c>
       <c r="F13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1392,10 +1395,10 @@
         <v>241</v>
       </c>
       <c r="F14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1412,10 +1415,10 @@
         <v>241</v>
       </c>
       <c r="F15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1432,10 +1435,10 @@
         <v>241</v>
       </c>
       <c r="F16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1452,10 +1455,10 @@
         <v>241</v>
       </c>
       <c r="F17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1472,10 +1475,10 @@
         <v>241</v>
       </c>
       <c r="F18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1492,10 +1495,10 @@
         <v>241</v>
       </c>
       <c r="F19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1512,10 +1515,10 @@
         <v>241</v>
       </c>
       <c r="F20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1532,10 +1535,10 @@
         <v>241</v>
       </c>
       <c r="F21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1552,10 +1555,10 @@
         <v>241</v>
       </c>
       <c r="F22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G22" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1572,10 +1575,10 @@
         <v>241</v>
       </c>
       <c r="F23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G23" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1592,10 +1595,10 @@
         <v>241</v>
       </c>
       <c r="F24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G24" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1612,10 +1615,10 @@
         <v>241</v>
       </c>
       <c r="F25" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1632,10 +1635,10 @@
         <v>241</v>
       </c>
       <c r="F26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G26" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1652,13 +1655,13 @@
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F27" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G27" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1675,13 +1678,13 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F28" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G28" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1698,13 +1701,13 @@
         <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G29" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1718,13 +1721,13 @@
         <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1738,13 +1741,13 @@
         <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G31" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1758,13 +1761,13 @@
         <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1778,13 +1781,13 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G33" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1798,13 +1801,13 @@
         <v>36</v>
       </c>
       <c r="E34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G34" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1818,13 +1821,13 @@
         <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F35" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1838,13 +1841,13 @@
         <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F36" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G36" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1858,13 +1861,13 @@
         <v>42</v>
       </c>
       <c r="E37" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F37" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G37" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1878,13 +1881,13 @@
         <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F38" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1898,13 +1901,13 @@
         <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F39" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G39" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1918,13 +1921,13 @@
         <v>48</v>
       </c>
       <c r="E40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F40" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G40" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1938,13 +1941,13 @@
         <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G41" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1958,13 +1961,13 @@
         <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F42" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G42" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1978,13 +1981,13 @@
         <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F43" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G43" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1998,13 +2001,13 @@
         <v>56</v>
       </c>
       <c r="E44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F44" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2018,13 +2021,13 @@
         <v>58</v>
       </c>
       <c r="E45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2038,13 +2041,13 @@
         <v>60</v>
       </c>
       <c r="E46" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G46" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2058,13 +2061,13 @@
         <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G47" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2078,13 +2081,13 @@
         <v>64</v>
       </c>
       <c r="E48" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2098,13 +2101,13 @@
         <v>66</v>
       </c>
       <c r="E49" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F49" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G49" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2118,13 +2121,13 @@
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G50" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2138,13 +2141,13 @@
         <v>70</v>
       </c>
       <c r="E51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G51" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2161,13 +2164,13 @@
         <v>17</v>
       </c>
       <c r="E52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F52" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G52" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2184,13 +2187,13 @@
         <v>19</v>
       </c>
       <c r="E53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F53" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G53" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2207,13 +2210,13 @@
         <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G54" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2227,13 +2230,13 @@
         <v>28</v>
       </c>
       <c r="E55" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F55" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G55" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2247,13 +2250,13 @@
         <v>30</v>
       </c>
       <c r="E56" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F56" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G56" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2267,13 +2270,13 @@
         <v>32</v>
       </c>
       <c r="E57" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F57" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2287,13 +2290,13 @@
         <v>34</v>
       </c>
       <c r="E58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F58" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G58" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2307,13 +2310,13 @@
         <v>36</v>
       </c>
       <c r="E59" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2327,13 +2330,13 @@
         <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F60" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G60" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2347,13 +2350,13 @@
         <v>40</v>
       </c>
       <c r="E61" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F61" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G61" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2367,13 +2370,13 @@
         <v>42</v>
       </c>
       <c r="E62" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F62" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G62" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2387,13 +2390,13 @@
         <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G63" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2407,13 +2410,13 @@
         <v>46</v>
       </c>
       <c r="E64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G64" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2427,13 +2430,13 @@
         <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F65" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2447,13 +2450,13 @@
         <v>50</v>
       </c>
       <c r="E66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F66" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G66" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2467,13 +2470,13 @@
         <v>52</v>
       </c>
       <c r="E67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G67" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2487,13 +2490,13 @@
         <v>54</v>
       </c>
       <c r="E68" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2507,13 +2510,13 @@
         <v>56</v>
       </c>
       <c r="E69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F69" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G69" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2527,13 +2530,13 @@
         <v>58</v>
       </c>
       <c r="E70" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G70" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2547,13 +2550,13 @@
         <v>60</v>
       </c>
       <c r="E71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F71" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2567,13 +2570,13 @@
         <v>62</v>
       </c>
       <c r="E72" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F72" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2587,13 +2590,13 @@
         <v>64</v>
       </c>
       <c r="E73" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F73" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G73" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2607,13 +2610,13 @@
         <v>66</v>
       </c>
       <c r="E74" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2627,13 +2630,13 @@
         <v>68</v>
       </c>
       <c r="E75" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F75" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G75" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2647,13 +2650,13 @@
         <v>70</v>
       </c>
       <c r="E76" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G76" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2673,10 +2676,10 @@
         <v>241</v>
       </c>
       <c r="F77" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G77" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2696,10 +2699,10 @@
         <v>241</v>
       </c>
       <c r="F78" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G78" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2719,10 +2722,10 @@
         <v>241</v>
       </c>
       <c r="F79" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G79" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2739,10 +2742,10 @@
         <v>241</v>
       </c>
       <c r="F80" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G80" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2759,10 +2762,10 @@
         <v>241</v>
       </c>
       <c r="F81" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G81" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2779,10 +2782,10 @@
         <v>241</v>
       </c>
       <c r="F82" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G82" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2799,10 +2802,10 @@
         <v>241</v>
       </c>
       <c r="F83" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2819,10 +2822,10 @@
         <v>241</v>
       </c>
       <c r="F84" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G84" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2839,10 +2842,10 @@
         <v>241</v>
       </c>
       <c r="F85" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G85" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2859,10 +2862,10 @@
         <v>241</v>
       </c>
       <c r="F86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G86" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2879,10 +2882,10 @@
         <v>241</v>
       </c>
       <c r="F87" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G87" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2899,10 +2902,10 @@
         <v>241</v>
       </c>
       <c r="F88" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G88" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2919,10 +2922,10 @@
         <v>241</v>
       </c>
       <c r="F89" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G89" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2939,10 +2942,10 @@
         <v>241</v>
       </c>
       <c r="F90" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G90" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2959,10 +2962,10 @@
         <v>241</v>
       </c>
       <c r="F91" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G91" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2979,10 +2982,10 @@
         <v>241</v>
       </c>
       <c r="F92" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G92" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2999,10 +3002,10 @@
         <v>241</v>
       </c>
       <c r="F93" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G93" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3019,10 +3022,10 @@
         <v>241</v>
       </c>
       <c r="F94" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G94" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3039,10 +3042,10 @@
         <v>241</v>
       </c>
       <c r="F95" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G95" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3059,10 +3062,10 @@
         <v>241</v>
       </c>
       <c r="F96" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G96" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3079,10 +3082,10 @@
         <v>241</v>
       </c>
       <c r="F97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G97" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3099,10 +3102,10 @@
         <v>241</v>
       </c>
       <c r="F98" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G98" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3119,10 +3122,10 @@
         <v>241</v>
       </c>
       <c r="F99" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G99" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3139,10 +3142,10 @@
         <v>241</v>
       </c>
       <c r="F100" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G100" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3159,10 +3162,10 @@
         <v>241</v>
       </c>
       <c r="F101" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G101" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3182,10 +3185,10 @@
         <v>241</v>
       </c>
       <c r="F102" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G102" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3205,10 +3208,10 @@
         <v>241</v>
       </c>
       <c r="F103" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G103" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3228,10 +3231,10 @@
         <v>241</v>
       </c>
       <c r="F104" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G104" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3248,10 +3251,10 @@
         <v>241</v>
       </c>
       <c r="F105" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G105" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3268,10 +3271,10 @@
         <v>241</v>
       </c>
       <c r="F106" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G106" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3288,10 +3291,10 @@
         <v>241</v>
       </c>
       <c r="F107" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G107" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3308,10 +3311,10 @@
         <v>241</v>
       </c>
       <c r="F108" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G108" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3328,10 +3331,10 @@
         <v>241</v>
       </c>
       <c r="F109" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G109" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3348,10 +3351,10 @@
         <v>241</v>
       </c>
       <c r="F110" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G110" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3368,10 +3371,10 @@
         <v>241</v>
       </c>
       <c r="F111" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G111" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3388,10 +3391,10 @@
         <v>241</v>
       </c>
       <c r="F112" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G112" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -3408,10 +3411,10 @@
         <v>241</v>
       </c>
       <c r="F113" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G113" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -3428,10 +3431,10 @@
         <v>241</v>
       </c>
       <c r="F114" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G114" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -3448,10 +3451,10 @@
         <v>241</v>
       </c>
       <c r="F115" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G115" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3468,10 +3471,10 @@
         <v>241</v>
       </c>
       <c r="F116" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G116" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3488,10 +3491,10 @@
         <v>241</v>
       </c>
       <c r="F117" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G117" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -3508,10 +3511,10 @@
         <v>241</v>
       </c>
       <c r="F118" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G118" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -3528,10 +3531,10 @@
         <v>241</v>
       </c>
       <c r="F119" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G119" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -3548,10 +3551,10 @@
         <v>241</v>
       </c>
       <c r="F120" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G120" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -3568,10 +3571,10 @@
         <v>241</v>
       </c>
       <c r="F121" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G121" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -3588,10 +3591,10 @@
         <v>241</v>
       </c>
       <c r="F122" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G122" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3608,10 +3611,10 @@
         <v>241</v>
       </c>
       <c r="F123" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G123" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3628,10 +3631,10 @@
         <v>241</v>
       </c>
       <c r="F124" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G124" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -3648,10 +3651,10 @@
         <v>241</v>
       </c>
       <c r="F125" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G125" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3668,10 +3671,10 @@
         <v>241</v>
       </c>
       <c r="F126" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G126" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -3688,13 +3691,13 @@
         <v>17</v>
       </c>
       <c r="E127" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F127" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G127" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -3711,13 +3714,13 @@
         <v>19</v>
       </c>
       <c r="E128" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F128" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G128" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -3734,13 +3737,13 @@
         <v>21</v>
       </c>
       <c r="E129" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F129" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G129" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3754,13 +3757,13 @@
         <v>28</v>
       </c>
       <c r="E130" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F130" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G130" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -3774,13 +3777,13 @@
         <v>30</v>
       </c>
       <c r="E131" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F131" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G131" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -3794,13 +3797,13 @@
         <v>32</v>
       </c>
       <c r="E132" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F132" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G132" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3814,13 +3817,13 @@
         <v>34</v>
       </c>
       <c r="E133" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F133" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G133" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -3834,13 +3837,13 @@
         <v>36</v>
       </c>
       <c r="E134" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F134" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G134" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -3854,13 +3857,13 @@
         <v>38</v>
       </c>
       <c r="E135" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F135" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G135" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -3874,13 +3877,13 @@
         <v>40</v>
       </c>
       <c r="E136" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F136" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G136" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -3894,13 +3897,13 @@
         <v>42</v>
       </c>
       <c r="E137" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F137" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G137" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -3914,13 +3917,13 @@
         <v>44</v>
       </c>
       <c r="E138" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F138" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G138" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -3934,13 +3937,13 @@
         <v>46</v>
       </c>
       <c r="E139" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F139" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G139" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -3954,13 +3957,13 @@
         <v>48</v>
       </c>
       <c r="E140" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F140" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G140" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -3974,13 +3977,13 @@
         <v>50</v>
       </c>
       <c r="E141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F141" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G141" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -3994,13 +3997,13 @@
         <v>52</v>
       </c>
       <c r="E142" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F142" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G142" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4014,13 +4017,13 @@
         <v>54</v>
       </c>
       <c r="E143" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F143" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G143" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4034,13 +4037,13 @@
         <v>56</v>
       </c>
       <c r="E144" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F144" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G144" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4054,13 +4057,13 @@
         <v>58</v>
       </c>
       <c r="E145" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F145" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G145" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4074,13 +4077,13 @@
         <v>60</v>
       </c>
       <c r="E146" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F146" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G146" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4094,13 +4097,13 @@
         <v>62</v>
       </c>
       <c r="E147" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F147" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G147" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4114,13 +4117,13 @@
         <v>64</v>
       </c>
       <c r="E148" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F148" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G148" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4134,13 +4137,13 @@
         <v>66</v>
       </c>
       <c r="E149" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F149" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G149" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4154,13 +4157,13 @@
         <v>68</v>
       </c>
       <c r="E150" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F150" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G150" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4174,13 +4177,13 @@
         <v>70</v>
       </c>
       <c r="E151" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F151" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G151" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4200,10 +4203,10 @@
         <v>241</v>
       </c>
       <c r="F152" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G152" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4223,10 +4226,10 @@
         <v>241</v>
       </c>
       <c r="F153" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G153" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4246,10 +4249,10 @@
         <v>241</v>
       </c>
       <c r="F154" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G154" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4266,10 +4269,10 @@
         <v>241</v>
       </c>
       <c r="F155" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G155" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4286,10 +4289,10 @@
         <v>241</v>
       </c>
       <c r="F156" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G156" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4306,10 +4309,10 @@
         <v>241</v>
       </c>
       <c r="F157" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G157" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -4326,10 +4329,10 @@
         <v>241</v>
       </c>
       <c r="F158" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G158" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -4346,10 +4349,10 @@
         <v>241</v>
       </c>
       <c r="F159" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G159" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -4366,10 +4369,10 @@
         <v>241</v>
       </c>
       <c r="F160" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G160" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -4386,10 +4389,10 @@
         <v>241</v>
       </c>
       <c r="F161" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G161" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -4406,10 +4409,10 @@
         <v>241</v>
       </c>
       <c r="F162" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G162" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -4426,10 +4429,10 @@
         <v>241</v>
       </c>
       <c r="F163" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G163" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -4446,10 +4449,10 @@
         <v>241</v>
       </c>
       <c r="F164" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G164" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -4466,10 +4469,10 @@
         <v>241</v>
       </c>
       <c r="F165" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G165" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -4486,10 +4489,10 @@
         <v>241</v>
       </c>
       <c r="F166" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G166" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -4506,10 +4509,10 @@
         <v>241</v>
       </c>
       <c r="F167" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G167" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -4526,10 +4529,10 @@
         <v>241</v>
       </c>
       <c r="F168" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G168" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -4546,10 +4549,10 @@
         <v>241</v>
       </c>
       <c r="F169" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G169" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -4566,10 +4569,10 @@
         <v>241</v>
       </c>
       <c r="F170" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G170" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -4586,10 +4589,10 @@
         <v>241</v>
       </c>
       <c r="F171" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G171" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -4606,10 +4609,10 @@
         <v>241</v>
       </c>
       <c r="F172" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G172" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -4626,10 +4629,10 @@
         <v>241</v>
       </c>
       <c r="F173" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G173" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -4646,10 +4649,10 @@
         <v>241</v>
       </c>
       <c r="F174" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G174" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -4666,10 +4669,10 @@
         <v>241</v>
       </c>
       <c r="F175" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G175" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -4686,10 +4689,10 @@
         <v>241</v>
       </c>
       <c r="F176" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G176" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -4706,13 +4709,13 @@
         <v>17</v>
       </c>
       <c r="E177" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F177" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G177" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -4729,13 +4732,13 @@
         <v>19</v>
       </c>
       <c r="E178" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F178" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G178" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -4752,13 +4755,13 @@
         <v>21</v>
       </c>
       <c r="E179" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F179" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G179" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -4772,13 +4775,13 @@
         <v>28</v>
       </c>
       <c r="E180" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F180" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G180" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -4792,13 +4795,13 @@
         <v>30</v>
       </c>
       <c r="E181" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F181" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G181" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -4812,13 +4815,13 @@
         <v>32</v>
       </c>
       <c r="E182" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F182" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G182" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -4832,13 +4835,13 @@
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F183" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G183" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -4852,13 +4855,13 @@
         <v>36</v>
       </c>
       <c r="E184" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F184" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G184" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -4872,13 +4875,13 @@
         <v>38</v>
       </c>
       <c r="E185" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F185" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G185" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -4892,13 +4895,13 @@
         <v>40</v>
       </c>
       <c r="E186" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F186" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G186" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -4912,13 +4915,13 @@
         <v>42</v>
       </c>
       <c r="E187" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F187" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G187" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -4932,13 +4935,13 @@
         <v>44</v>
       </c>
       <c r="E188" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F188" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G188" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -4952,13 +4955,13 @@
         <v>46</v>
       </c>
       <c r="E189" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F189" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G189" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -4972,13 +4975,13 @@
         <v>48</v>
       </c>
       <c r="E190" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F190" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G190" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -4992,13 +4995,13 @@
         <v>50</v>
       </c>
       <c r="E191" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F191" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G191" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5012,13 +5015,13 @@
         <v>52</v>
       </c>
       <c r="E192" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F192" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G192" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5032,13 +5035,13 @@
         <v>54</v>
       </c>
       <c r="E193" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F193" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G193" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5052,13 +5055,13 @@
         <v>56</v>
       </c>
       <c r="E194" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F194" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G194" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5072,13 +5075,13 @@
         <v>58</v>
       </c>
       <c r="E195" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F195" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G195" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5092,13 +5095,13 @@
         <v>60</v>
       </c>
       <c r="E196" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F196" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G196" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5112,13 +5115,13 @@
         <v>62</v>
       </c>
       <c r="E197" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F197" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G197" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5132,13 +5135,13 @@
         <v>64</v>
       </c>
       <c r="E198" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F198" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G198" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5152,13 +5155,13 @@
         <v>66</v>
       </c>
       <c r="E199" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F199" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G199" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5172,13 +5175,13 @@
         <v>68</v>
       </c>
       <c r="E200" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F200" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G200" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5192,13 +5195,13 @@
         <v>70</v>
       </c>
       <c r="E201" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F201" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G201" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -5215,13 +5218,13 @@
         <v>17</v>
       </c>
       <c r="E202" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F202" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G202" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -5238,13 +5241,13 @@
         <v>19</v>
       </c>
       <c r="E203" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F203" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G203" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -5261,13 +5264,13 @@
         <v>21</v>
       </c>
       <c r="E204" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F204" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G204" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -5281,13 +5284,13 @@
         <v>28</v>
       </c>
       <c r="E205" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F205" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G205" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -5301,13 +5304,13 @@
         <v>30</v>
       </c>
       <c r="E206" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F206" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G206" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -5321,13 +5324,13 @@
         <v>32</v>
       </c>
       <c r="E207" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F207" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G207" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -5341,13 +5344,13 @@
         <v>34</v>
       </c>
       <c r="E208" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F208" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G208" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -5361,13 +5364,13 @@
         <v>36</v>
       </c>
       <c r="E209" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F209" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G209" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -5381,13 +5384,13 @@
         <v>38</v>
       </c>
       <c r="E210" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F210" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G210" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -5401,13 +5404,13 @@
         <v>40</v>
       </c>
       <c r="E211" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F211" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G211" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -5421,13 +5424,13 @@
         <v>42</v>
       </c>
       <c r="E212" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F212" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G212" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5441,13 +5444,13 @@
         <v>44</v>
       </c>
       <c r="E213" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F213" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G213" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -5461,13 +5464,13 @@
         <v>46</v>
       </c>
       <c r="E214" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F214" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G214" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -5481,13 +5484,13 @@
         <v>48</v>
       </c>
       <c r="E215" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F215" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G215" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -5501,13 +5504,13 @@
         <v>50</v>
       </c>
       <c r="E216" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F216" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G216" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -5521,13 +5524,13 @@
         <v>52</v>
       </c>
       <c r="E217" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F217" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G217" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -5541,13 +5544,13 @@
         <v>54</v>
       </c>
       <c r="E218" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F218" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G218" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -5561,13 +5564,13 @@
         <v>56</v>
       </c>
       <c r="E219" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F219" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G219" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -5581,13 +5584,13 @@
         <v>58</v>
       </c>
       <c r="E220" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F220" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G220" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -5601,13 +5604,13 @@
         <v>60</v>
       </c>
       <c r="E221" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F221" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G221" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -5621,13 +5624,13 @@
         <v>62</v>
       </c>
       <c r="E222" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F222" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G222" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -5641,13 +5644,13 @@
         <v>64</v>
       </c>
       <c r="E223" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F223" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G223" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -5661,13 +5664,13 @@
         <v>66</v>
       </c>
       <c r="E224" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F224" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G224" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -5681,13 +5684,13 @@
         <v>68</v>
       </c>
       <c r="E225" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F225" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G225" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -5701,13 +5704,13 @@
         <v>70</v>
       </c>
       <c r="E226" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F226" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G226" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
